--- a/outputs/lynch_watchlist_20260804/watchlist_lynch_2026-08-04.xlsx
+++ b/outputs/lynch_watchlist_20260804/watchlist_lynch_2026-08-04.xlsx
@@ -2,15 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" r:id="R35504a2d3c3441c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="2" r:id="Ra1cbff37318c401a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Lynch" sheetId="3" r:id="R61125d6b96684bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="4" r:id="R996c6a35350d4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plantilla_Ficha" sheetId="5" r:id="R3f1dc346de8d4b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes_Audit" sheetId="6" r:id="R24a33709ac444d91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="7" r:id="R32c8aa88db314e64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descartadas" sheetId="8" r:id="Re8b605f3ec8c41d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" r:id="R4818b216d4aa4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" r:id="R933ffba50cdf41d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Watchlist" sheetId="2" r:id="R8d391570c49b4fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analisis_Prioritario" sheetId="3" r:id="Rda6451a198c94590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ranking_10Bagger" sheetId="4" r:id="R0ff83303a5e6485e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist_Lynch" sheetId="5" r:id="Rc6a088aeb4424bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="6" r:id="R9ed67dad764a48e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plantilla_Ficha" sheetId="7" r:id="R8fe4a356856f4eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes_Audit" sheetId="8" r:id="Rc7b82b2bbbe94e02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="9" r:id="Rf1bd4611ec064d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descartadas" sheetId="10" r:id="Rf931ee80861f43e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="11" r:id="Rd0a5044f601f4161"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -124,7 +126,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="108">
+  <x:cellXfs count="131">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -275,10 +277,83 @@
     <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
     <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
@@ -303,9 +378,6 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
@@ -317,8 +389,6 @@
     </x:xf>
     <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="205" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -350,19 +420,12 @@
     <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="203" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -383,7 +446,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="9">
+  <x:dxfs count="15">
     <x:dxf>
       <x:fill>
         <x:patternFill patternType="solid">
@@ -395,6 +458,48 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF4CCCC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -452,7 +557,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QuickView" displayName="QuickView" ref="A11:H23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="QuickView" displayName="QuickView" ref="A11:H33" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="Empresa"/>
     <x:tableColumn id="2" name="Ticker"/>
@@ -467,8 +572,20 @@
 </x:table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="ChecksTable" displayName="ChecksTable" ref="A4:D14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="Comprobación"/>
+    <x:tableColumn id="2" name="Valor"/>
+    <x:tableColumn id="3" name="Estado"/>
+    <x:tableColumn id="4" name="Qué significa"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A4:AB16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WatchlistTable" displayName="WatchlistTable" ref="A4:AB26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="28">
     <x:tableColumn id="1" name="Empresa"/>
     <x:tableColumn id="2" name="Ticker"/>
@@ -504,7 +621,64 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ChecklistTable" displayName="ChecklistTable" ref="A4:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PriorityAnalysisTable" displayName="PriorityAnalysisTable" ref="A4:V8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="22">
+    <x:tableColumn id="1" name="Empresa"/>
+    <x:tableColumn id="2" name="Ticker"/>
+    <x:tableColumn id="3" name="Precio actual (GBX)"/>
+    <x:tableColumn id="4" name="EPS referencia (GBX)"/>
+    <x:tableColumn id="5" name="PER actual"/>
+    <x:tableColumn id="6" name="EPS bajo"/>
+    <x:tableColumn id="7" name="EPS base"/>
+    <x:tableColumn id="8" name="EPS alto"/>
+    <x:tableColumn id="9" name="PER bajo"/>
+    <x:tableColumn id="10" name="PER base"/>
+    <x:tableColumn id="11" name="PER alto"/>
+    <x:tableColumn id="12" name="Precio razonable bajo (GBX)"/>
+    <x:tableColumn id="13" name="Precio razonable base (GBX)"/>
+    <x:tableColumn id="14" name="Precio razonable alto (GBX)"/>
+    <x:tableColumn id="15" name="Margen seguridad"/>
+    <x:tableColumn id="16" name="Precio entrada base (GBX)"/>
+    <x:tableColumn id="17" name="Upside base"/>
+    <x:tableColumn id="18" name="Catalizador / qué comprobar"/>
+    <x:tableColumn id="19" name="Invalidación"/>
+    <x:tableColumn id="20" name="Decisión provisional"/>
+    <x:tableColumn id="21" name="Próxima revisión"/>
+    <x:tableColumn id="22" name="Fuentes"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Ranking10BaggerTable" displayName="Ranking10BaggerTable" ref="A4:S26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="19">
+    <x:tableColumn id="1" name="Orden"/>
+    <x:tableColumn id="2" name="Empresa"/>
+    <x:tableColumn id="3" name="Ticker"/>
+    <x:tableColumn id="4" name="Tipo Lynch"/>
+    <x:tableColumn id="5" name="Capitalización (m)"/>
+    <x:tableColumn id="6" name="PER"/>
+    <x:tableColumn id="7" name="Score Lynch /16"/>
+    <x:tableColumn id="8" name="Crecimiento / runway (0-5)"/>
+    <x:tableColumn id="9" name="Valoración (0-5)"/>
+    <x:tableColumn id="10" name="Balance / caja (0-4)"/>
+    <x:tableColumn id="11" name="Tamaño / escala (0-4)"/>
+    <x:tableColumn id="12" name="Catalizador / palanca (0-4)"/>
+    <x:tableColumn id="13" name="Score 10Bagger /22"/>
+    <x:tableColumn id="14" name="Capitalización x10 (m)"/>
+    <x:tableColumn id="15" name="Rating relativo"/>
+    <x:tableColumn id="16" name="Motivo principal / freno"/>
+    <x:tableColumn id="17" name="Próxima revisión"/>
+    <x:tableColumn id="18" name="Fuentes"/>
+    <x:tableColumn id="19" name="Veredicto actual"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ChecklistTable" displayName="ChecklistTable" ref="A4:O26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="Empresa"/>
     <x:tableColumn id="2" name="Ticker"/>
@@ -526,8 +700,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="HistoryTable" displayName="HistoryTable" ref="A4:P25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="HistoryTable" displayName="HistoryTable" ref="A4:P35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Empresa"/>
     <x:tableColumn id="2" name="Ticker"/>
@@ -550,8 +724,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SourcesTable" displayName="SourcesTable" ref="A4:G54" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SourcesTable" displayName="SourcesTable" ref="A4:G85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Fuente ID"/>
     <x:tableColumn id="2" name="Empresa"/>
@@ -565,8 +739,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="FollowUpTable" displayName="FollowUpTable" ref="A4:L16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="FollowUpTable" displayName="FollowUpTable" ref="A4:L26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Empresa"/>
     <x:tableColumn id="2" name="Ticker"/>
@@ -585,8 +759,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="RejectedTable" displayName="RejectedTable" ref="A4:J5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="RejectedTable" displayName="RejectedTable" ref="A4:J5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="Empresa"/>
     <x:tableColumn id="2" name="Ticker"/>
@@ -598,18 +772,6 @@
     <x:tableColumn id="8" name="Crec. ventas"/>
     <x:tableColumn id="9" name="FCF FY25 (m)"/>
     <x:tableColumn id="10" name="Motivo de no selección"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="ChecksTable" displayName="ChecksTable" ref="A4:D13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="4">
-    <x:tableColumn id="1" name="Comprobación"/>
-    <x:tableColumn id="2" name="Valor"/>
-    <x:tableColumn id="3" name="Estado"/>
-    <x:tableColumn id="4" name="Qué significa"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -938,12 +1100,12 @@
       <x:c r="G7" s="33"/>
       <x:c r="H7" s="33"/>
     </x:row>
-    <x:row r="8" ht="184.8000030517578" hidden="0" customHeight="1">
+    <x:row r="8" ht="224.39999389648438" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="str">
         <x:v>Universo actual</x:v>
       </x:c>
       <x:c r="B8" s="28" t="str">
-        <x:v>12 compañías: 7 ya estudiadas y 5 incorporaciones nuevas. Usa Seguimiento para saber qué revisar y cuándo.</x:v>
+        <x:v>22 compañías: 7 ya estudiadas, 5 incorporaciones previas y 10 candidatas nuevas. Usa Seguimiento para saber qué revisar y cuándo.</x:v>
       </x:c>
       <x:c r="C8" s="33"/>
       <x:c r="D8" s="33"/>
@@ -1362,152 +1524,869 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="33"/>
-      <x:c r="B24" s="33"/>
-      <x:c r="C24" s="33"/>
-      <x:c r="D24" s="33"/>
-      <x:c r="E24" s="33"/>
-      <x:c r="F24" s="33"/>
-      <x:c r="G24" s="33"/>
-      <x:c r="H24" s="33"/>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="33"/>
-      <x:c r="B25" s="33"/>
-      <x:c r="C25" s="33"/>
-      <x:c r="D25" s="33"/>
-      <x:c r="E25" s="33"/>
-      <x:c r="F25" s="33"/>
-      <x:c r="G25" s="33"/>
-      <x:c r="H25" s="33"/>
-    </x:row>
-    <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="36" t="str">
+    <x:row r="24" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A24" s="33" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="B24" s="33" t="str">
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="C24" s="33" t="str">
+        <x:v>Calidad / marketplace</x:v>
+      </x:c>
+      <x:c r="D24" s="37" t="n">
+        <x:v>474.8</x:v>
+      </x:c>
+      <x:c r="E24" s="38" t="n">
+        <x:v>16.9</x:v>
+      </x:c>
+      <x:c r="F24" s="39" t="n">
+        <x:f>'Watchlist'!AA17</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G24" s="40" t="str">
+        <x:f>'Watchlist'!V17</x:f>
+        <x:v>Esperar / calidad, no perseguir precio</x:v>
+      </x:c>
+      <x:c r="H24" s="40" t="n">
+        <x:f>'Watchlist'!W17</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A25" s="33" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="B25" s="33" t="str">
+        <x:v>GAW</x:v>
+      </x:c>
+      <x:c r="C25" s="33" t="str">
+        <x:v>Calidad / IP y nicho</x:v>
+      </x:c>
+      <x:c r="D25" s="37" t="n">
+        <x:v>19940</x:v>
+      </x:c>
+      <x:c r="E25" s="38" t="n">
+        <x:v>33.52</x:v>
+      </x:c>
+      <x:c r="F25" s="39" t="n">
+        <x:f>'Watchlist'!AA18</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G25" s="40" t="str">
+        <x:f>'Watchlist'!V18</x:f>
+        <x:v>Vigilar / negocio excelente, precio exigente</x:v>
+      </x:c>
+      <x:c r="H25" s="40" t="n">
+        <x:f>'Watchlist'!W18</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A26" s="33" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="B26" s="33" t="str">
+        <x:v>CCC</x:v>
+      </x:c>
+      <x:c r="C26" s="33" t="str">
+        <x:v>Crecimiento / servicios IT</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="n">
+        <x:v>4818</x:v>
+      </x:c>
+      <x:c r="E26" s="38" t="n">
+        <x:v>32.89</x:v>
+      </x:c>
+      <x:c r="F26" s="39" t="n">
+        <x:f>'Watchlist'!AA19</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G26" s="40" t="str">
+        <x:f>'Watchlist'!V19</x:f>
+        <x:v>Vigilar / crecimiento con riesgo de margen</x:v>
+      </x:c>
+      <x:c r="H26" s="40" t="n">
+        <x:f>'Watchlist'!W19</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A27" s="33" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="B27" s="33" t="str">
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="C27" s="33" t="str">
+        <x:v>Calidad / cíclica</x:v>
+      </x:c>
+      <x:c r="D27" s="37" t="n">
+        <x:v>821.5</x:v>
+      </x:c>
+      <x:c r="E27" s="38" t="n">
+        <x:v>16.7</x:v>
+      </x:c>
+      <x:c r="F27" s="39" t="n">
+        <x:f>'Watchlist'!AA20</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G27" s="40" t="str">
+        <x:f>'Watchlist'!V20</x:f>
+        <x:v>Vigilar / solo con margen</x:v>
+      </x:c>
+      <x:c r="H27" s="40" t="n">
+        <x:f>'Watchlist'!W20</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A28" s="33" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="B28" s="33" t="str">
+        <x:v>DOM</x:v>
+      </x:c>
+      <x:c r="C28" s="33" t="str">
+        <x:v>Madura / recuperable</x:v>
+      </x:c>
+      <x:c r="D28" s="37" t="n">
+        <x:v>201.6</x:v>
+      </x:c>
+      <x:c r="E28" s="38" t="n">
+        <x:v>13.35</x:v>
+      </x:c>
+      <x:c r="F28" s="39" t="n">
+        <x:f>'Watchlist'!AA21</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G28" s="40" t="str">
+        <x:f>'Watchlist'!V21</x:f>
+        <x:v>Esperar resultados / turnaround condicional</x:v>
+      </x:c>
+      <x:c r="H28" s="40" t="n">
+        <x:f>'Watchlist'!W21</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A29" s="33" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="B29" s="33" t="str">
+        <x:v>BWY</x:v>
+      </x:c>
+      <x:c r="C29" s="33" t="str">
+        <x:v>Existente / cíclica</x:v>
+      </x:c>
+      <x:c r="D29" s="37" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="E29" s="38" t="n">
+        <x:v>14.73</x:v>
+      </x:c>
+      <x:c r="F29" s="39" t="n">
+        <x:f>'Watchlist'!AA22</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" s="40" t="str">
+        <x:f>'Watchlist'!V22</x:f>
+        <x:v>Vigilar / oportunidad cíclica</x:v>
+      </x:c>
+      <x:c r="H29" s="40" t="n">
+        <x:f>'Watchlist'!W22</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A30" s="33" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="B30" s="33" t="str">
+        <x:v>BAB</x:v>
+      </x:c>
+      <x:c r="C30" s="33" t="str">
+        <x:v>Defensa / turnaround</x:v>
+      </x:c>
+      <x:c r="D30" s="37" t="n">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="E30" s="38" t="n">
+        <x:v>18.53</x:v>
+      </x:c>
+      <x:c r="F30" s="39" t="n">
+        <x:f>'Watchlist'!AA23</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G30" s="40" t="str">
+        <x:f>'Watchlist'!V23</x:f>
+        <x:v>Vigilar / recuperación con caja</x:v>
+      </x:c>
+      <x:c r="H30" s="40" t="n">
+        <x:f>'Watchlist'!W23</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A31" s="33" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="B31" s="33" t="str">
+        <x:v>OXIG</x:v>
+      </x:c>
+      <x:c r="C31" s="33" t="str">
+        <x:v>Nicho / tecnología</x:v>
+      </x:c>
+      <x:c r="D31" s="37" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+      <x:c r="E31" s="38" t="n">
+        <x:v>33.81</x:v>
+      </x:c>
+      <x:c r="F31" s="39" t="n">
+        <x:f>'Watchlist'!AA24</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G31" s="40" t="str">
+        <x:f>'Watchlist'!V24</x:f>
+        <x:v>Vigilar / esperar conversión de pedidos</x:v>
+      </x:c>
+      <x:c r="H31" s="40" t="n">
+        <x:f>'Watchlist'!W24</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A32" s="33" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="B32" s="33" t="str">
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="C32" s="33" t="str">
+        <x:v>Madura / calidad con descuento</x:v>
+      </x:c>
+      <x:c r="D32" s="37" t="n">
+        <x:v>4390</x:v>
+      </x:c>
+      <x:c r="E32" s="38" t="n">
+        <x:v>14.62</x:v>
+      </x:c>
+      <x:c r="F32" s="39" t="n">
+        <x:f>'Watchlist'!AA25</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G32" s="40" t="str">
+        <x:f>'Watchlist'!V25</x:f>
+        <x:v>Esperar H1 / no perseguir precio</x:v>
+      </x:c>
+      <x:c r="H32" s="40" t="n">
+        <x:f>'Watchlist'!W25</x:f>
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A33" s="33" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="B33" s="33" t="str">
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="C33" s="33" t="str">
+        <x:v>Cíclica / crecimiento</x:v>
+      </x:c>
+      <x:c r="D33" s="37" t="n">
+        <x:v>1540</x:v>
+      </x:c>
+      <x:c r="E33" s="38" t="n">
+        <x:v>7.29</x:v>
+      </x:c>
+      <x:c r="F33" s="39" t="n">
+        <x:f>'Watchlist'!AA26</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G33" s="40" t="str">
+        <x:f>'Watchlist'!V26</x:f>
+        <x:v>Compra escalonada solo con margen</x:v>
+      </x:c>
+      <x:c r="H33" s="40" t="n">
+        <x:f>'Watchlist'!W26</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="33"/>
+      <x:c r="B34" s="33"/>
+      <x:c r="C34" s="33"/>
+      <x:c r="D34" s="33"/>
+      <x:c r="E34" s="33"/>
+      <x:c r="F34" s="33"/>
+      <x:c r="G34" s="33"/>
+      <x:c r="H34" s="33"/>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="33"/>
+      <x:c r="B35" s="33"/>
+      <x:c r="C35" s="33"/>
+      <x:c r="D35" s="33"/>
+      <x:c r="E35" s="33"/>
+      <x:c r="F35" s="33"/>
+      <x:c r="G35" s="33"/>
+      <x:c r="H35" s="33"/>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="B26" s="36" t="str">
+      <x:c r="B36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="C26" s="36" t="str">
+      <x:c r="C36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="D26" s="36" t="str">
+      <x:c r="D36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="E26" s="36" t="str">
+      <x:c r="E36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="F26" s="36" t="str">
+      <x:c r="F36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="G26" s="36" t="str">
+      <x:c r="G36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
-      <x:c r="H26" s="36" t="str">
+      <x:c r="H36" s="36" t="str">
         <x:v>Cómo interpretar la puntuación</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A27" s="35" t="str">
+    <x:row r="37" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A37" s="35" t="str">
         <x:v>12–16</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="str">
+      <x:c r="B37" s="33" t="str">
         <x:v>Candidato: merece profundizar y definir precio de entrada.</x:v>
       </x:c>
-      <x:c r="C27" s="33"/>
-      <x:c r="D27" s="35" t="str">
+      <x:c r="C37" s="33"/>
+      <x:c r="D37" s="35" t="str">
         <x:v>Hoja</x:v>
       </x:c>
-      <x:c r="E27" s="35" t="str">
+      <x:c r="E37" s="35" t="str">
         <x:v>Uso</x:v>
       </x:c>
-      <x:c r="F27" s="33" t="str"/>
-      <x:c r="G27" s="33" t="str"/>
-      <x:c r="H27" s="33" t="str"/>
-    </x:row>
-    <x:row r="28" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="F37" s="33" t="str"/>
+      <x:c r="G37" s="33" t="str"/>
+      <x:c r="H37" s="33" t="str"/>
+    </x:row>
+    <x:row r="38" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A38" s="35" t="str">
         <x:v>9–11</x:v>
       </x:c>
-      <x:c r="B28" s="33" t="str">
+      <x:c r="B38" s="33" t="str">
         <x:v>Vigilancia: hay algo interesante, pero falta confirmar una pieza.</x:v>
       </x:c>
-      <x:c r="C28" s="33"/>
-      <x:c r="D28" s="33" t="str">
+      <x:c r="C38" s="33"/>
+      <x:c r="D38" s="33" t="str">
         <x:v>Watchlist</x:v>
       </x:c>
-      <x:c r="E28" s="33" t="str">
+      <x:c r="E38" s="33" t="str">
         <x:v>Panel principal y datos de mercado/resultados.</x:v>
       </x:c>
-      <x:c r="F28" s="33" t="str"/>
-      <x:c r="G28" s="33" t="str"/>
-      <x:c r="H28" s="33" t="str"/>
-    </x:row>
-    <x:row r="29" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A29" s="35" t="str">
+      <x:c r="F38" s="33" t="str"/>
+      <x:c r="G38" s="33" t="str"/>
+      <x:c r="H38" s="33" t="str"/>
+    </x:row>
+    <x:row r="39" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A39" s="35" t="str">
         <x:v>0–8</x:v>
       </x:c>
-      <x:c r="B29" s="33" t="str">
+      <x:c r="B39" s="33" t="str">
         <x:v>Revisar: no hay suficiente margen de seguridad o claridad.</x:v>
       </x:c>
-      <x:c r="C29" s="33"/>
-      <x:c r="D29" s="33" t="str">
+      <x:c r="C39" s="33"/>
+      <x:c r="D39" s="33" t="str">
         <x:v>Checklist_Lynch</x:v>
       </x:c>
-      <x:c r="E29" s="33" t="str">
+      <x:c r="E39" s="33" t="str">
         <x:v>Puntuación y preguntas pendientes.</x:v>
       </x:c>
-      <x:c r="F29" s="33" t="str"/>
-      <x:c r="G29" s="33" t="str"/>
-      <x:c r="H29" s="33" t="str"/>
-    </x:row>
-    <x:row r="30" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="F39" s="33" t="str"/>
+      <x:c r="G39" s="33" t="str"/>
+      <x:c r="H39" s="33" t="str"/>
+    </x:row>
+    <x:row r="40" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A40" s="35" t="str">
         <x:v>Importante</x:v>
       </x:c>
-      <x:c r="B30" s="33" t="str">
+      <x:c r="B40" s="33" t="str">
         <x:v>La puntuación es una ayuda de proceso creada para esta hoja; no es una escala oficial de Peter Lynch.</x:v>
       </x:c>
-      <x:c r="C30" s="33"/>
-      <x:c r="D30" s="33" t="str">
+      <x:c r="C40" s="33"/>
+      <x:c r="D40" s="33" t="str">
         <x:v>Historial / Fuentes_Audit</x:v>
       </x:c>
-      <x:c r="E30" s="33" t="str">
+      <x:c r="E40" s="33" t="str">
         <x:v>Series y trazabilidad de cada afirmación.</x:v>
       </x:c>
-      <x:c r="F30" s="33" t="str"/>
-      <x:c r="G30" s="33" t="str"/>
-      <x:c r="H30" s="33" t="str"/>
-    </x:row>
-    <x:row r="31" ht="171.60000610351562" hidden="0" customHeight="1">
-      <x:c r="A31" s="35" t="str">
+      <x:c r="F40" s="33" t="str"/>
+      <x:c r="G40" s="33" t="str"/>
+      <x:c r="H40" s="33" t="str"/>
+    </x:row>
+    <x:row r="41" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A41" s="35" t="str">
         <x:v>Siguiente paso</x:v>
       </x:c>
-      <x:c r="B31" s="33" t="str">
+      <x:c r="B41" s="33" t="str">
         <x:v>Ve a Seguimiento: compara precio, PER, crecimiento, FCF, deuda y el dato que puede invalidar la tesis.</x:v>
       </x:c>
-      <x:c r="C31" s="33"/>
-      <x:c r="D31" s="33" t="str">
+      <x:c r="C41" s="33"/>
+      <x:c r="D41" s="33" t="str">
         <x:v>Seguimiento</x:v>
       </x:c>
-      <x:c r="E31" s="33" t="str">
+      <x:c r="E41" s="33" t="str">
         <x:v>Próxima revisión, métricas a comparar y condición de invalidación.</x:v>
       </x:c>
-      <x:c r="F31" s="33" t="str"/>
-      <x:c r="G31" s="33" t="str"/>
-      <x:c r="H31" s="33" t="str"/>
+      <x:c r="F41" s="33" t="str"/>
+      <x:c r="G41" s="33" t="str"/>
+      <x:c r="H41" s="33" t="str"/>
+    </x:row>
+    <x:row r="42" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A42" s="33"/>
+      <x:c r="B42" s="33"/>
+      <x:c r="C42" s="33"/>
+      <x:c r="D42" s="33" t="str">
+        <x:v>Analisis_Prioritario</x:v>
+      </x:c>
+      <x:c r="E42" s="33" t="str">
+        <x:v>Escenarios de valoración y precio de entrada para las 4 prioridades.</x:v>
+      </x:c>
+      <x:c r="F42" s="33" t="str"/>
+      <x:c r="G42" s="33" t="str"/>
+      <x:c r="H42" s="33" t="str"/>
+    </x:row>
+    <x:row r="43" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A43" s="33"/>
+      <x:c r="B43" s="33"/>
+      <x:c r="C43" s="33"/>
+      <x:c r="D43" s="33" t="str">
+        <x:v>Ranking_10Bagger</x:v>
+      </x:c>
+      <x:c r="E43" s="33" t="str">
+        <x:v>Orden relativo por runway, crecimiento, valoración, balance, tamaño y catalizadores.</x:v>
+      </x:c>
+      <x:c r="F43" s="33" t="str"/>
+      <x:c r="G43" s="33" t="str"/>
+      <x:c r="H43" s="33" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A10:H10"/>
-    <x:mergeCell ref="A26:H26"/>
+    <x:mergeCell ref="A36:H36"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9c48849af4e472c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f246fb5927f4fae"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="66" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="B1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="C1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="D1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="E1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="F1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="G1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="H1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="I1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+      <x:c r="J1" s="34" t="str">
+        <x:v>Ideas cribadas pero no seleccionadas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" hidden="0" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="I2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
+      <x:c r="I3" s="33"/>
+      <x:c r="J3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="36" hidden="0" customHeight="1">
+      <x:c r="A4" s="20" t="str">
+        <x:v>Empresa</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>Fecha salida</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>Precio</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>Rent. 1 año</x:v>
+      </x:c>
+      <x:c r="G4" s="20" t="str">
+        <x:v>Ventas FY25 (m)</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="str">
+        <x:v>Crec. ventas</x:v>
+      </x:c>
+      <x:c r="I4" s="20" t="str">
+        <x:v>FCF FY25 (m)</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="str">
+        <x:v>Motivo de no selección</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="250.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A5" s="58" t="str">
+        <x:v>Applied Nutrition</x:v>
+      </x:c>
+      <x:c r="B5" s="58" t="str">
+        <x:v>APN</x:v>
+      </x:c>
+      <x:c r="C5" s="59" t="n">
+        <x:v>45589</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="n">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="E5" s="62" t="n">
+        <x:v>39.17</x:v>
+      </x:c>
+      <x:c r="F5" s="63" t="n">
+        <x:v>1.4962</x:v>
+      </x:c>
+      <x:c r="G5" s="58" t="n">
+        <x:v>107.1</x:v>
+      </x:c>
+      <x:c r="H5" s="63" t="n">
+        <x:v>0.242</x:v>
+      </x:c>
+      <x:c r="I5" s="58" t="n">
+        <x:v>16.5</x:v>
+      </x:c>
+      <x:c r="J5" s="58" t="str">
+        <x:v>Crecimiento y caja interesantes, pero el precio ya descuenta mucho: +150% en un año, PER ~39x y sin dividendo. Volver a mirar si el crecimiento acelera o corrige la cotización.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R254d7ef1fe5547e6"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>Checks del modelo</x:v>
+      </x:c>
+      <x:c r="B1" s="34" t="str">
+        <x:v>Checks del modelo</x:v>
+      </x:c>
+      <x:c r="C1" s="34" t="str">
+        <x:v>Checks del modelo</x:v>
+      </x:c>
+      <x:c r="D1" s="34" t="str">
+        <x:v>Checks del modelo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="48" hidden="0" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="24" hidden="0" customHeight="1">
+      <x:c r="A4" s="20" t="str">
+        <x:v>Comprobación</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>Valor</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>Estado</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>Qué significa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A5" s="35" t="str">
+        <x:v>Filas de watchlist</x:v>
+      </x:c>
+      <x:c r="B5" s="28" t="n">
+        <x:f>COUNTA('Watchlist'!A5:A26)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C5" s="126" t="str">
+        <x:f>IF(B5=22,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D5" s="33" t="str">
+        <x:v>Debe haber 22 compañías seleccionadas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A6" s="35" t="str">
+        <x:v>Totales de checklist</x:v>
+      </x:c>
+      <x:c r="B6" s="28" t="n">
+        <x:f>COUNT('Checklist_Lynch'!L5:L26)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C6" s="126" t="str">
+        <x:f>IF(B6=22,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>Cada empresa debe tener un total calculado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A7" s="35" t="str">
+        <x:v>Fuentes de mercado y resultados</x:v>
+      </x:c>
+      <x:c r="B7" s="28" t="n">
+        <x:f>COUNTIF('Watchlist'!Y5:Y26,"&lt;&gt;")+COUNTIF('Watchlist'!Z5:Z26,"&lt;&gt;")</x:f>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C7" s="126" t="str">
+        <x:f>IF(B7=44,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D7" s="33" t="str">
+        <x:v>Cada fila principal debe tener ambos IDs.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A8" s="35" t="str">
+        <x:v>Celdas de score vacías</x:v>
+      </x:c>
+      <x:c r="B8" s="28" t="n">
+        <x:f>COUNTBLANK('Watchlist'!AA5:AA26)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="126" t="str">
+        <x:f>IF(B8=0,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D8" s="33" t="str">
+        <x:v>No debe faltar el enlace al total de Checklist_Lynch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A9" s="35" t="str">
+        <x:v>Escala máxima</x:v>
+      </x:c>
+      <x:c r="B9" s="28" t="n">
+        <x:f>MAX('Checklist_Lynch'!L5:L26)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="126" t="str">
+        <x:f>IF(B9&lt;=16,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="str">
+        <x:v>El máximo permitido por fila es 16.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A10" s="35" t="str">
+        <x:v>Modelo</x:v>
+      </x:c>
+      <x:c r="B10" s="28" t="n">
+        <x:f>COUNTIF(C5:C9,"REVISAR")+COUNTIF(C13:C14,"REVISAR")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="126" t="str">
+        <x:f>IF(B10=0,"MODELO OK","HAY QUE REVISAR")</x:f>
+        <x:v>MODELO OK</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>Resumen de las comprobaciones anteriores.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="66" hidden="0" customHeight="1">
+      <x:c r="A11" s="35" t="str">
+        <x:v>Fecha de corte</x:v>
+      </x:c>
+      <x:c r="B11" s="130" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C11" s="126" t="str">
+        <x:f>IF(B11=DATE(2026,8,4),"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D11" s="33" t="str">
+        <x:v>Actualiza esta fecha cuando refresques los datos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A12" s="35" t="str">
+        <x:v>Recordatorio</x:v>
+      </x:c>
+      <x:c r="B12" s="28" t="str">
+        <x:v>No es recomendación</x:v>
+      </x:c>
+      <x:c r="C12" s="126" t="str">
+        <x:v>INFO</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="str">
+        <x:v>Verifica siempre fuentes, precio, impuestos, divisa y tu perfil de riesgo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A13" s="35" t="str">
+        <x:v>Filas de seguimiento</x:v>
+      </x:c>
+      <x:c r="B13" s="28" t="n">
+        <x:f>COUNTA('Seguimiento'!A5:A26)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C13" s="126" t="str">
+        <x:f>IF(B13=22,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D13" s="33" t="str">
+        <x:v>Cada compañía debe tener una próxima revisión.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A14" s="35" t="str">
+        <x:v>Filas de ranking 10-bagger</x:v>
+      </x:c>
+      <x:c r="B14" s="28" t="n">
+        <x:f>COUNTA('Ranking_10Bagger'!B5:B26)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C14" s="126" t="str">
+        <x:f>IF(B14=22,"OK","REVISAR")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="str">
+        <x:v>El ranking debe cubrir las 22 compañías y conservar sus enlaces.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="C5:C14">
+    <x:cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="OK"/>
+    <x:cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="REVISAR"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re57ca6ca3a24421c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2862,275 +3741,3989 @@
         <x:v>Alta prioridad</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="33"/>
-      <x:c r="B17" s="33"/>
-      <x:c r="C17" s="33"/>
-      <x:c r="D17" s="33"/>
-      <x:c r="E17" s="33"/>
-      <x:c r="F17" s="33"/>
-      <x:c r="G17" s="33"/>
-      <x:c r="H17" s="33"/>
-      <x:c r="I17" s="33"/>
-      <x:c r="J17" s="33"/>
-      <x:c r="K17" s="33"/>
-      <x:c r="L17" s="33"/>
-      <x:c r="M17" s="33"/>
-      <x:c r="N17" s="33"/>
-      <x:c r="O17" s="33"/>
-      <x:c r="P17" s="33"/>
-      <x:c r="Q17" s="33"/>
-      <x:c r="R17" s="33"/>
-      <x:c r="S17" s="33"/>
-      <x:c r="T17" s="33"/>
-      <x:c r="U17" s="33"/>
-      <x:c r="V17" s="33"/>
-      <x:c r="W17" s="33"/>
-      <x:c r="X17" s="33"/>
-      <x:c r="Y17" s="33"/>
-      <x:c r="Z17" s="33"/>
-      <x:c r="AA17" s="33"/>
-      <x:c r="AB17" s="33"/>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="33"/>
-      <x:c r="B18" s="33"/>
-      <x:c r="C18" s="33"/>
-      <x:c r="D18" s="33"/>
-      <x:c r="E18" s="33"/>
-      <x:c r="F18" s="33"/>
-      <x:c r="G18" s="33"/>
-      <x:c r="H18" s="33"/>
-      <x:c r="I18" s="33"/>
-      <x:c r="J18" s="33"/>
-      <x:c r="K18" s="33"/>
-      <x:c r="L18" s="33"/>
-      <x:c r="M18" s="33"/>
-      <x:c r="N18" s="33"/>
-      <x:c r="O18" s="33"/>
-      <x:c r="P18" s="33"/>
-      <x:c r="Q18" s="33"/>
-      <x:c r="R18" s="33"/>
-      <x:c r="S18" s="33"/>
-      <x:c r="T18" s="33"/>
-      <x:c r="U18" s="33"/>
-      <x:c r="V18" s="33"/>
-      <x:c r="W18" s="33"/>
-      <x:c r="X18" s="33"/>
-      <x:c r="Y18" s="33"/>
-      <x:c r="Z18" s="33"/>
-      <x:c r="AA18" s="33"/>
-      <x:c r="AB18" s="33"/>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="36" t="str">
+    <x:row r="17" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A17" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="B17" s="58" t="str">
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="C17" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D17" s="58" t="str">
+        <x:v>Calidad / marketplace</x:v>
+      </x:c>
+      <x:c r="E17" s="59"/>
+      <x:c r="F17" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G17" s="60" t="n">
+        <x:v>474.8</x:v>
+      </x:c>
+      <x:c r="H17" s="61" t="n">
+        <x:v>3520</x:v>
+      </x:c>
+      <x:c r="I17" s="62" t="n">
+        <x:v>16.8968</x:v>
+      </x:c>
+      <x:c r="J17" s="60" t="n">
+        <x:v>28.1</x:v>
+      </x:c>
+      <x:c r="K17" s="60" t="n">
+        <x:v>10.15</x:v>
+      </x:c>
+      <x:c r="L17" s="63" t="n">
+        <x:v>0.02138</x:v>
+      </x:c>
+      <x:c r="M17" s="61" t="n">
+        <x:v>425.1</x:v>
+      </x:c>
+      <x:c r="N17" s="63" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="O17" s="63" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="P17" s="61"/>
+      <x:c r="Q17" s="61" t="n">
+        <x:v>-29.6</x:v>
+      </x:c>
+      <x:c r="R17" s="64" t="n">
+        <x:f>IF(AND(I17&gt;0,O17&gt;0),I17/(O17*100),"")</x:f>
+        <x:v>1.877422222222222</x:v>
+      </x:c>
+      <x:c r="S17" s="58" t="str">
+        <x:v>Network effect, consenso FY26: EPS 30.02p y guía 2026 de ingresos +8–10%; áreas estratégicas en crecimiento.</x:v>
+      </x:c>
+      <x:c r="T17" s="58" t="str">
+        <x:v>Propiedad cíclica, presión de agentes/competencia, litigio/riesgo regulatorio y gasto en innovación.</x:v>
+      </x:c>
+      <x:c r="U17" s="58" t="str">
+        <x:v>H1 2026 publicado 2026-07-31; revisión post-resultados 2026-08-31</x:v>
+      </x:c>
+      <x:c r="V17" s="58" t="str">
+        <x:v>Esperar / calidad, no perseguir precio</x:v>
+      </x:c>
+      <x:c r="W17" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X17" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y17" s="58" t="str">
+        <x:v>RMV-MKT</x:v>
+      </x:c>
+      <x:c r="Z17" s="58" t="str">
+        <x:v>RMV-FY25</x:v>
+      </x:c>
+      <x:c r="AA17" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L17,"")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AB17" s="28" t="str">
+        <x:f>IF(AA17&gt;=12,"Alta prioridad",IF(AA17&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A18" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="B18" s="58" t="str">
+        <x:v>GAW</x:v>
+      </x:c>
+      <x:c r="C18" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D18" s="58" t="str">
+        <x:v>Calidad / IP y nicho</x:v>
+      </x:c>
+      <x:c r="E18" s="59"/>
+      <x:c r="F18" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G18" s="60" t="n">
+        <x:v>19940</x:v>
+      </x:c>
+      <x:c r="H18" s="61" t="n">
+        <x:v>6590</x:v>
+      </x:c>
+      <x:c r="I18" s="62" t="n">
+        <x:v>33.518</x:v>
+      </x:c>
+      <x:c r="J18" s="60" t="n">
+        <x:v>594.9</x:v>
+      </x:c>
+      <x:c r="K18" s="60" t="n">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="L18" s="63" t="n">
+        <x:v>0.02432</x:v>
+      </x:c>
+      <x:c r="M18" s="61" t="n">
+        <x:v>659.7</x:v>
+      </x:c>
+      <x:c r="N18" s="63" t="n">
+        <x:v>0.068</x:v>
+      </x:c>
+      <x:c r="O18" s="63" t="n">
+        <x:v>0.052</x:v>
+      </x:c>
+      <x:c r="P18" s="61" t="n">
+        <x:v>210.3</x:v>
+      </x:c>
+      <x:c r="Q18" s="61"/>
+      <x:c r="R18" s="64" t="n">
+        <x:f>IF(AND(I18&gt;0,O18&gt;0),I18/(O18*100),"")</x:f>
+        <x:v>6.445769230769231</x:v>
+      </x:c>
+      <x:c r="S18" s="58" t="str">
+        <x:v>Warhammer/IP, ingresos core +10.9%, balance sin deuda y caja creciendo antes de dividendos.</x:v>
+      </x:c>
+      <x:c r="T18" s="58" t="str">
+        <x:v>PER exigente, dependencia de ejecución/licencias y riesgo de que el crecimiento se normalice.</x:v>
+      </x:c>
+      <x:c r="U18" s="58" t="str">
+        <x:v>Revisión de trading pre-interinos: tentativa 2026-11-05</x:v>
+      </x:c>
+      <x:c r="V18" s="58" t="str">
+        <x:v>Vigilar / negocio excelente, precio exigente</x:v>
+      </x:c>
+      <x:c r="W18" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X18" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y18" s="58" t="str">
+        <x:v>GAW-MKT</x:v>
+      </x:c>
+      <x:c r="Z18" s="58" t="str">
+        <x:v>GAW-FY26</x:v>
+      </x:c>
+      <x:c r="AA18" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L18,"")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AB18" s="28" t="str">
+        <x:f>IF(AA18&gt;=12,"Alta prioridad",IF(AA18&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A19" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="B19" s="58" t="str">
+        <x:v>CCC</x:v>
+      </x:c>
+      <x:c r="C19" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D19" s="58" t="str">
+        <x:v>Crecimiento / servicios IT</x:v>
+      </x:c>
+      <x:c r="E19" s="59"/>
+      <x:c r="F19" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G19" s="60" t="n">
+        <x:v>4818</x:v>
+      </x:c>
+      <x:c r="H19" s="61" t="n">
+        <x:v>5060</x:v>
+      </x:c>
+      <x:c r="I19" s="62" t="n">
+        <x:v>32.887</x:v>
+      </x:c>
+      <x:c r="J19" s="60" t="n">
+        <x:v>146.5</x:v>
+      </x:c>
+      <x:c r="K19" s="60" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="L19" s="63" t="n">
+        <x:v>0.0155</x:v>
+      </x:c>
+      <x:c r="M19" s="61" t="n">
+        <x:v>9193.9</x:v>
+      </x:c>
+      <x:c r="N19" s="63" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="O19" s="63" t="n">
+        <x:v>0.113</x:v>
+      </x:c>
+      <x:c r="P19" s="61"/>
+      <x:c r="Q19" s="61" t="n">
+        <x:v>-606</x:v>
+      </x:c>
+      <x:c r="R19" s="64" t="n">
+        <x:f>IF(AND(I19&gt;0,O19&gt;0),I19/(O19*100),"")</x:f>
+        <x:v>2.910353982300885</x:v>
+      </x:c>
+      <x:c r="S19" s="58" t="str">
+        <x:v>Q1 2026 muy por encima de expectativas; Technology Sourcing fuerte y caja neta ajustada de £606m.</x:v>
+      </x:c>
+      <x:c r="T19" s="58" t="str">
+        <x:v>Margen bruto bajó a 12.4%, Managed Services débil y PER alto para una empresa de servicios.</x:v>
+      </x:c>
+      <x:c r="U19" s="58" t="str">
+        <x:v>Resultados H1 2026: 2026-09-08</x:v>
+      </x:c>
+      <x:c r="V19" s="58" t="str">
+        <x:v>Vigilar / crecimiento con riesgo de margen</x:v>
+      </x:c>
+      <x:c r="W19" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X19" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y19" s="58" t="str">
+        <x:v>CCC-MKT</x:v>
+      </x:c>
+      <x:c r="Z19" s="58" t="str">
+        <x:v>CCC-Q1-26</x:v>
+      </x:c>
+      <x:c r="AA19" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L19,"")</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AB19" s="28" t="str">
+        <x:f>IF(AA19&gt;=12,"Alta prioridad",IF(AA19&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A20" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="B20" s="58" t="str">
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="C20" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D20" s="58" t="str">
+        <x:v>Calidad / cíclica</x:v>
+      </x:c>
+      <x:c r="E20" s="59"/>
+      <x:c r="F20" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G20" s="60" t="n">
+        <x:v>821.5</x:v>
+      </x:c>
+      <x:c r="H20" s="61" t="n">
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="I20" s="62" t="n">
+        <x:v>16.69715</x:v>
+      </x:c>
+      <x:c r="J20" s="60" t="n">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="K20" s="60" t="n">
+        <x:v>21.3</x:v>
+      </x:c>
+      <x:c r="L20" s="63" t="n">
+        <x:v>0.02593</x:v>
+      </x:c>
+      <x:c r="M20" s="61" t="n">
+        <x:v>1030.6</x:v>
+      </x:c>
+      <x:c r="N20" s="63" t="n">
+        <x:v>0.033</x:v>
+      </x:c>
+      <x:c r="O20" s="63" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="P20" s="61"/>
+      <x:c r="Q20" s="61" t="n">
+        <x:v>-332.8</x:v>
+      </x:c>
+      <x:c r="R20" s="64" t="n">
+        <x:f>IF(AND(I20&gt;0,O20&gt;0),I20/(O20*100),"")</x:f>
+        <x:v>3.0358454545454547</x:v>
+      </x:c>
+      <x:c r="S20" s="58" t="str">
+        <x:v>Modelo trade-only, margen bruto H1 62.8%, EBIT subyacente +5.5% y recompra de £100m en 2026.</x:v>
+      </x:c>
+      <x:c r="T20" s="58" t="str">
+        <x:v>Sensibilidad a vivienda/remodelación, adquisición DIY Kitchens y valoración si el crecimiento se enfría.</x:v>
+      </x:c>
+      <x:c r="U20" s="58" t="str">
+        <x:v>Trading update: 2026-11-05</x:v>
+      </x:c>
+      <x:c r="V20" s="58" t="str">
+        <x:v>Vigilar / solo con margen</x:v>
+      </x:c>
+      <x:c r="W20" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X20" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y20" s="58" t="str">
+        <x:v>HWDN-MKT</x:v>
+      </x:c>
+      <x:c r="Z20" s="58" t="str">
+        <x:v>HWDN-H1-26</x:v>
+      </x:c>
+      <x:c r="AA20" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L20,"")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AB20" s="28" t="str">
+        <x:f>IF(AA20&gt;=12,"Alta prioridad",IF(AA20&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A21" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="B21" s="58" t="str">
+        <x:v>DOM</x:v>
+      </x:c>
+      <x:c r="C21" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D21" s="58" t="str">
+        <x:v>Madura / recuperable</x:v>
+      </x:c>
+      <x:c r="E21" s="59"/>
+      <x:c r="F21" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G21" s="60" t="n">
+        <x:v>201.6</x:v>
+      </x:c>
+      <x:c r="H21" s="61" t="n">
+        <x:v>768.41</x:v>
+      </x:c>
+      <x:c r="I21" s="62" t="n">
+        <x:v>13.35099</x:v>
+      </x:c>
+      <x:c r="J21" s="60" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="K21" s="60" t="n">
+        <x:v>11.1</x:v>
+      </x:c>
+      <x:c r="L21" s="63" t="n">
+        <x:v>0.05506</x:v>
+      </x:c>
+      <x:c r="M21" s="61" t="n">
+        <x:v>685.4</x:v>
+      </x:c>
+      <x:c r="N21" s="63" t="n">
+        <x:v>0.031</x:v>
+      </x:c>
+      <x:c r="O21" s="63" t="n">
+        <x:v>-0.066</x:v>
+      </x:c>
+      <x:c r="P21" s="61"/>
+      <x:c r="Q21" s="61"/>
+      <x:c r="R21" s="64" t="str">
+        <x:f>IF(AND(I21&gt;0,O21&gt;0),I21/(O21*100),"")</x:f>
+      </x:c>
+      <x:c r="S21" s="58" t="str">
+        <x:v>Franquicia/brand comprensible, dividendo 5.5% y momentum positivo en las primeras 9 semanas de 2026.</x:v>
+      </x:c>
+      <x:c r="T21" s="58" t="str">
+        <x:v>EBITDA y PBT FY25 cayeron; presión promocional, activismo y necesidad de demostrar la estrategia.</x:v>
+      </x:c>
+      <x:c r="U21" s="58" t="str">
+        <x:v>Resultados H1 2026: 2026-08-04; revisión 2026-08-05</x:v>
+      </x:c>
+      <x:c r="V21" s="58" t="str">
+        <x:v>Esperar resultados / turnaround condicional</x:v>
+      </x:c>
+      <x:c r="W21" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X21" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y21" s="58" t="str">
+        <x:v>DOM-MKT</x:v>
+      </x:c>
+      <x:c r="Z21" s="58" t="str">
+        <x:v>DOM-FY25</x:v>
+      </x:c>
+      <x:c r="AA21" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L21,"")</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AB21" s="28" t="str">
+        <x:f>IF(AA21&gt;=12,"Alta prioridad",IF(AA21&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Vigilancia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A22" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="B22" s="58" t="str">
+        <x:v>BWY</x:v>
+      </x:c>
+      <x:c r="C22" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D22" s="58" t="str">
+        <x:v>Existente / cíclica</x:v>
+      </x:c>
+      <x:c r="E22" s="59"/>
+      <x:c r="F22" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G22" s="60" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="H22" s="61" t="n">
+        <x:v>2240</x:v>
+      </x:c>
+      <x:c r="I22" s="62" t="n">
+        <x:v>14.72892</x:v>
+      </x:c>
+      <x:c r="J22" s="60" t="n">
+        <x:v>132.8</x:v>
+      </x:c>
+      <x:c r="K22" s="60" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L22" s="63" t="n">
+        <x:v>0.03016</x:v>
+      </x:c>
+      <x:c r="M22" s="61" t="n">
+        <x:v>2782.8</x:v>
+      </x:c>
+      <x:c r="N22" s="63" t="n">
+        <x:v>0.169</x:v>
+      </x:c>
+      <x:c r="O22" s="63" t="n">
+        <x:v>0.178</x:v>
+      </x:c>
+      <x:c r="P22" s="61"/>
+      <x:c r="Q22" s="61" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="R22" s="64" t="n">
+        <x:f>IF(AND(I22&gt;0,O22&gt;0),I22/(O22*100),"")</x:f>
+        <x:v>0.8274674157303371</x:v>
+      </x:c>
+      <x:c r="S22" s="58" t="str">
+        <x:v>Orderbook de £1.57bn, beneficio operativo FY26 guiado a £320–330m y potencial de normalización de vivienda.</x:v>
+      </x:c>
+      <x:c r="T22" s="58" t="str">
+        <x:v>Tipos hipotecarios, demanda moderada, costes de construcción y carácter cíclico del beneficio.</x:v>
+      </x:c>
+      <x:c r="U22" s="58" t="str">
+        <x:v>Trading update: 2026-08-11</x:v>
+      </x:c>
+      <x:c r="V22" s="58" t="str">
+        <x:v>Vigilar / oportunidad cíclica</x:v>
+      </x:c>
+      <x:c r="W22" s="65" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X22" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y22" s="58" t="str">
+        <x:v>BWY-MKT</x:v>
+      </x:c>
+      <x:c r="Z22" s="58" t="str">
+        <x:v>BWY-TRD</x:v>
+      </x:c>
+      <x:c r="AA22" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L22,"")</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AB22" s="28" t="str">
+        <x:f>IF(AA22&gt;=12,"Alta prioridad",IF(AA22&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="198" hidden="0" customHeight="1">
+      <x:c r="A23" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="B23" s="58" t="str">
+        <x:v>BAB</x:v>
+      </x:c>
+      <x:c r="C23" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D23" s="58" t="str">
+        <x:v>Defensa / turnaround</x:v>
+      </x:c>
+      <x:c r="E23" s="59"/>
+      <x:c r="F23" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G23" s="60" t="n">
+        <x:v>1121</x:v>
+      </x:c>
+      <x:c r="H23" s="61" t="n">
+        <x:v>5510</x:v>
+      </x:c>
+      <x:c r="I23" s="62" t="n">
+        <x:v>18.52893</x:v>
+      </x:c>
+      <x:c r="J23" s="60" t="n">
+        <x:v>60.5</x:v>
+      </x:c>
+      <x:c r="K23" s="60" t="n">
+        <x:v>7.5</x:v>
+      </x:c>
+      <x:c r="L23" s="63" t="n">
+        <x:v>0.00669</x:v>
+      </x:c>
+      <x:c r="M23" s="61" t="n">
+        <x:v>5273</x:v>
+      </x:c>
+      <x:c r="N23" s="63" t="n">
+        <x:v>0.0915</x:v>
+      </x:c>
+      <x:c r="O23" s="63" t="n">
+        <x:v>0.192</x:v>
+      </x:c>
+      <x:c r="P23" s="61" t="n">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="Q23" s="61" t="n">
+        <x:v>-23</x:v>
+      </x:c>
+      <x:c r="R23" s="64" t="n">
+        <x:f>IF(AND(I23&gt;0,O23&gt;0),I23/(O23*100),"")</x:f>
+        <x:v>0.9650484375</x:v>
+      </x:c>
+      <x:c r="S23" s="58" t="str">
+        <x:v>Backlog £9.8bn, FCF +£109m, balance en caja neta y recompra FY27 de £200m.</x:v>
+      </x:c>
+      <x:c r="T23" s="58" t="str">
+        <x:v>Cargo extraordinario Type 31, ejecución de contratos y diferencia entre beneficio subyacente y estatutario.</x:v>
+      </x:c>
+      <x:c r="U23" s="58" t="str">
+        <x:v>Revisión H1 FY27: tentativa 2026-11-20</x:v>
+      </x:c>
+      <x:c r="V23" s="58" t="str">
+        <x:v>Vigilar / recuperación con caja</x:v>
+      </x:c>
+      <x:c r="W23" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X23" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y23" s="58" t="str">
+        <x:v>BAB-MKT</x:v>
+      </x:c>
+      <x:c r="Z23" s="58" t="str">
+        <x:v>BAB-FY26</x:v>
+      </x:c>
+      <x:c r="AA23" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L23,"")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AB23" s="28" t="str">
+        <x:f>IF(AA23&gt;=12,"Alta prioridad",IF(AA23&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A24" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="B24" s="58" t="str">
+        <x:v>OXIG</x:v>
+      </x:c>
+      <x:c r="C24" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D24" s="58" t="str">
+        <x:v>Nicho / tecnología</x:v>
+      </x:c>
+      <x:c r="E24" s="59"/>
+      <x:c r="F24" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G24" s="60" t="n">
+        <x:v>2860</x:v>
+      </x:c>
+      <x:c r="H24" s="61" t="n">
+        <x:v>1570</x:v>
+      </x:c>
+      <x:c r="I24" s="62" t="n">
+        <x:v>33.806</x:v>
+      </x:c>
+      <x:c r="J24" s="60" t="n">
+        <x:v>84.6</x:v>
+      </x:c>
+      <x:c r="K24" s="60" t="n">
+        <x:v>22.5</x:v>
+      </x:c>
+      <x:c r="L24" s="63" t="n">
+        <x:v>0.00787</x:v>
+      </x:c>
+      <x:c r="M24" s="61" t="n">
+        <x:v>423.2</x:v>
+      </x:c>
+      <x:c r="N24" s="63" t="n">
+        <x:v>-0.046</x:v>
+      </x:c>
+      <x:c r="O24" s="63" t="n">
+        <x:v>-0.073</x:v>
+      </x:c>
+      <x:c r="P24" s="61"/>
+      <x:c r="Q24" s="61" t="n">
+        <x:v>-94</x:v>
+      </x:c>
+      <x:c r="R24" s="64" t="str">
+        <x:f>IF(AND(I24&gt;0,O24&gt;0),I24/(O24*100),"")</x:f>
+      </x:c>
+      <x:c r="S24" s="58" t="str">
+        <x:v>Order intake +6.4%, book-to-bill 1.067 y caja neta £94m; exposición a semiconductores/ciencia aplicada.</x:v>
+      </x:c>
+      <x:c r="T24" s="58" t="str">
+        <x:v>Ingresos FY26 a la baja, presión de margen ajustado y PER alto mientras convierte pedidos en ventas.</x:v>
+      </x:c>
+      <x:c r="U24" s="58" t="str">
+        <x:v>Revisión de interinos: tentativa 2026-11-12</x:v>
+      </x:c>
+      <x:c r="V24" s="58" t="str">
+        <x:v>Vigilar / esperar conversión de pedidos</x:v>
+      </x:c>
+      <x:c r="W24" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X24" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y24" s="58" t="str">
+        <x:v>OXIG-MKT</x:v>
+      </x:c>
+      <x:c r="Z24" s="58" t="str">
+        <x:v>OXIG-FY26</x:v>
+      </x:c>
+      <x:c r="AA24" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L24,"")</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AB24" s="28" t="str">
+        <x:f>IF(AA24&gt;=12,"Alta prioridad",IF(AA24&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A25" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="B25" s="58" t="str">
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="C25" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D25" s="58" t="str">
+        <x:v>Madura / calidad con descuento</x:v>
+      </x:c>
+      <x:c r="E25" s="59"/>
+      <x:c r="F25" s="58" t="str">
+        <x:v>GBX / USD</x:v>
+      </x:c>
+      <x:c r="G25" s="60" t="n">
+        <x:v>4390</x:v>
+      </x:c>
+      <x:c r="H25" s="61" t="n">
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="I25" s="62" t="n">
+        <x:v>14.61869</x:v>
+      </x:c>
+      <x:c r="J25" s="60" t="n">
+        <x:v>300.30057</x:v>
+      </x:c>
+      <x:c r="K25" s="60" t="n">
+        <x:v>183.8</x:v>
+      </x:c>
+      <x:c r="L25" s="63" t="n">
+        <x:v>0.04187</x:v>
+      </x:c>
+      <x:c r="M25" s="61" t="n">
+        <x:v>1346.8</x:v>
+      </x:c>
+      <x:c r="N25" s="63" t="n">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="O25" s="63" t="n">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="P25" s="61"/>
+      <x:c r="Q25" s="61" t="n">
+        <x:v>-132.8</x:v>
+      </x:c>
+      <x:c r="R25" s="64" t="str">
+        <x:f>IF(AND(I25&gt;0,O25&gt;0),I25/(O25*100),"")</x:f>
+      </x:c>
+      <x:c r="S25" s="58" t="str">
+        <x:v>Negocio directo con caja, clientes existentes estables y dividendo; mañana debe aclarar si el bache es temporal.</x:v>
+      </x:c>
+      <x:c r="T25" s="58" t="str">
+        <x:v>Pedidos -3%, nuevos pedidos -12%, aranceles y riesgo de que el descenso no sea transitorio.</x:v>
+      </x:c>
+      <x:c r="U25" s="58" t="str">
+        <x:v>Resultados H1 2026: 2026-08-05</x:v>
+      </x:c>
+      <x:c r="V25" s="58" t="str">
+        <x:v>Esperar H1 / no perseguir precio</x:v>
+      </x:c>
+      <x:c r="W25" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X25" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y25" s="58" t="str">
+        <x:v>FOUR-MKT</x:v>
+      </x:c>
+      <x:c r="Z25" s="58" t="str">
+        <x:v>FOUR-FY25</x:v>
+      </x:c>
+      <x:c r="AA25" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L25,"")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AB25" s="28" t="str">
+        <x:f>IF(AA25&gt;=12,"Alta prioridad",IF(AA25&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A26" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="B26" s="58" t="str">
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="C26" s="58" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D26" s="58" t="str">
+        <x:v>Cíclica / crecimiento</x:v>
+      </x:c>
+      <x:c r="E26" s="59"/>
+      <x:c r="F26" s="58" t="str">
+        <x:v>GBX / GBP</x:v>
+      </x:c>
+      <x:c r="G26" s="60" t="n">
+        <x:v>1540</x:v>
+      </x:c>
+      <x:c r="H26" s="61" t="n">
+        <x:v>2780</x:v>
+      </x:c>
+      <x:c r="I26" s="62" t="n">
+        <x:v>7.291667</x:v>
+      </x:c>
+      <x:c r="J26" s="60" t="n">
+        <x:v>211.2</x:v>
+      </x:c>
+      <x:c r="K26" s="60" t="n">
+        <x:v>15.1</x:v>
+      </x:c>
+      <x:c r="L26" s="63" t="n">
+        <x:v>0.00981</x:v>
+      </x:c>
+      <x:c r="M26" s="61" t="n">
+        <x:v>7482.1</x:v>
+      </x:c>
+      <x:c r="N26" s="63" t="n">
+        <x:v>0.043</x:v>
+      </x:c>
+      <x:c r="O26" s="63" t="n">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="P26" s="61"/>
+      <x:c r="Q26" s="61" t="n">
+        <x:v>-2012.9</x:v>
+      </x:c>
+      <x:c r="R26" s="64" t="str">
+        <x:f>IF(AND(I26&gt;0,O26&gt;0),I26/(O26*100),"")</x:f>
+      </x:c>
+      <x:c r="S26" s="58" t="str">
+        <x:v>Pasajeros +5%, capacidad verano 2026 +7.7%, caja neta £2.0bn, Gatwick y recompra £250m.</x:v>
+      </x:c>
+      <x:c r="T26" s="58" t="str">
+        <x:v>Combustible, divisas, geopolítica, demanda de viajes y volatilidad normal del margen aéreo.</x:v>
+      </x:c>
+      <x:c r="U26" s="58" t="str">
+        <x:v>Revisión tras temporada de verano: tentativa 2026-11-17</x:v>
+      </x:c>
+      <x:c r="V26" s="58" t="str">
+        <x:v>Compra escalonada solo con margen</x:v>
+      </x:c>
+      <x:c r="W26" s="65" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X26" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="Y26" s="58" t="str">
+        <x:v>JET2-MKT</x:v>
+      </x:c>
+      <x:c r="Z26" s="58" t="str">
+        <x:v>JET2-FY26</x:v>
+      </x:c>
+      <x:c r="AA26" s="39" t="n">
+        <x:f>IFERROR('Checklist_Lynch'!L26,"")</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="AB26" s="28" t="str">
+        <x:f>IF(AA26&gt;=12,"Alta prioridad",IF(AA26&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Alta prioridad</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="33"/>
+      <x:c r="B27" s="33"/>
+      <x:c r="C27" s="33"/>
+      <x:c r="D27" s="33"/>
+      <x:c r="E27" s="33"/>
+      <x:c r="F27" s="33"/>
+      <x:c r="G27" s="33"/>
+      <x:c r="H27" s="33"/>
+      <x:c r="I27" s="33"/>
+      <x:c r="J27" s="33"/>
+      <x:c r="K27" s="33"/>
+      <x:c r="L27" s="33"/>
+      <x:c r="M27" s="33"/>
+      <x:c r="N27" s="33"/>
+      <x:c r="O27" s="33"/>
+      <x:c r="P27" s="33"/>
+      <x:c r="Q27" s="33"/>
+      <x:c r="R27" s="33"/>
+      <x:c r="S27" s="33"/>
+      <x:c r="T27" s="33"/>
+      <x:c r="U27" s="33"/>
+      <x:c r="V27" s="33"/>
+      <x:c r="W27" s="33"/>
+      <x:c r="X27" s="33"/>
+      <x:c r="Y27" s="33"/>
+      <x:c r="Z27" s="33"/>
+      <x:c r="AA27" s="33"/>
+      <x:c r="AB27" s="33"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="33"/>
+      <x:c r="B28" s="33"/>
+      <x:c r="C28" s="33"/>
+      <x:c r="D28" s="33"/>
+      <x:c r="E28" s="33"/>
+      <x:c r="F28" s="33"/>
+      <x:c r="G28" s="33"/>
+      <x:c r="H28" s="33"/>
+      <x:c r="I28" s="33"/>
+      <x:c r="J28" s="33"/>
+      <x:c r="K28" s="33"/>
+      <x:c r="L28" s="33"/>
+      <x:c r="M28" s="33"/>
+      <x:c r="N28" s="33"/>
+      <x:c r="O28" s="33"/>
+      <x:c r="P28" s="33"/>
+      <x:c r="Q28" s="33"/>
+      <x:c r="R28" s="33"/>
+      <x:c r="S28" s="33"/>
+      <x:c r="T28" s="33"/>
+      <x:c r="U28" s="33"/>
+      <x:c r="V28" s="33"/>
+      <x:c r="W28" s="33"/>
+      <x:c r="X28" s="33"/>
+      <x:c r="Y28" s="33"/>
+      <x:c r="Z28" s="33"/>
+      <x:c r="AA28" s="33"/>
+      <x:c r="AB28" s="33"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="B19" s="36" t="str">
+      <x:c r="B29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="C19" s="36" t="str">
+      <x:c r="C29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="D19" s="36" t="str">
+      <x:c r="D29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="E19" s="36" t="str">
+      <x:c r="E29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="F19" s="36" t="str">
+      <x:c r="F29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="G19" s="36" t="str">
+      <x:c r="G29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="H19" s="36" t="str">
+      <x:c r="H29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="I19" s="36" t="str">
+      <x:c r="I29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="J19" s="36" t="str">
+      <x:c r="J29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="K19" s="36" t="str">
+      <x:c r="K29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="L19" s="36" t="str">
+      <x:c r="L29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="M19" s="36" t="str">
+      <x:c r="M29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="N19" s="36" t="str">
+      <x:c r="N29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="O19" s="36" t="str">
+      <x:c r="O29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="P19" s="36" t="str">
+      <x:c r="P29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="Q19" s="36" t="str">
+      <x:c r="Q29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="R19" s="36" t="str">
+      <x:c r="R29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="S19" s="36" t="str">
+      <x:c r="S29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="T19" s="36" t="str">
+      <x:c r="T29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="U19" s="36" t="str">
+      <x:c r="U29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="V19" s="36" t="str">
+      <x:c r="V29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="W19" s="36" t="str">
+      <x:c r="W29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="X19" s="36" t="str">
+      <x:c r="X29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="Y19" s="36" t="str">
+      <x:c r="Y29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="Z19" s="36" t="str">
+      <x:c r="Z29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="AA19" s="36" t="str">
+      <x:c r="AA29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
-      <x:c r="AB19" s="36" t="str">
+      <x:c r="AB29" s="36" t="str">
         <x:v>Notas de uso</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+    <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A30" s="35" t="str">
         <x:v>* PEG heurístico</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="str">
+      <x:c r="B30" s="33" t="str">
         <x:v>PER dividido por el crecimiento porcentual del EBITDA/beneficio. No usar con pérdidas, cíclicas, periodos mezclados o divisas distintas.</x:v>
       </x:c>
-      <x:c r="C20" s="33"/>
-      <x:c r="D20" s="33"/>
-      <x:c r="E20" s="33"/>
-      <x:c r="F20" s="33"/>
-      <x:c r="G20" s="33"/>
-      <x:c r="H20" s="33"/>
-      <x:c r="I20" s="33"/>
-      <x:c r="J20" s="33"/>
-      <x:c r="K20" s="33"/>
-      <x:c r="L20" s="33"/>
-      <x:c r="M20" s="33"/>
-      <x:c r="N20" s="33"/>
-      <x:c r="O20" s="33"/>
-      <x:c r="P20" s="33"/>
-      <x:c r="Q20" s="33"/>
-      <x:c r="R20" s="33"/>
-      <x:c r="S20" s="33"/>
-      <x:c r="T20" s="33"/>
-      <x:c r="U20" s="33"/>
-      <x:c r="V20" s="33"/>
-      <x:c r="W20" s="33"/>
-      <x:c r="X20" s="33"/>
-      <x:c r="Y20" s="33"/>
-      <x:c r="Z20" s="33"/>
-      <x:c r="AA20" s="33"/>
-      <x:c r="AB20" s="33"/>
-    </x:row>
-    <x:row r="21" ht="26.399999618530273" hidden="0" customHeight="1">
-      <x:c r="A21" s="35" t="str">
+      <x:c r="C30" s="33"/>
+      <x:c r="D30" s="33"/>
+      <x:c r="E30" s="33"/>
+      <x:c r="F30" s="33"/>
+      <x:c r="G30" s="33"/>
+      <x:c r="H30" s="33"/>
+      <x:c r="I30" s="33"/>
+      <x:c r="J30" s="33"/>
+      <x:c r="K30" s="33"/>
+      <x:c r="L30" s="33"/>
+      <x:c r="M30" s="33"/>
+      <x:c r="N30" s="33"/>
+      <x:c r="O30" s="33"/>
+      <x:c r="P30" s="33"/>
+      <x:c r="Q30" s="33"/>
+      <x:c r="R30" s="33"/>
+      <x:c r="S30" s="33"/>
+      <x:c r="T30" s="33"/>
+      <x:c r="U30" s="33"/>
+      <x:c r="V30" s="33"/>
+      <x:c r="W30" s="33"/>
+      <x:c r="X30" s="33"/>
+      <x:c r="Y30" s="33"/>
+      <x:c r="Z30" s="33"/>
+      <x:c r="AA30" s="33"/>
+      <x:c r="AB30" s="33"/>
+    </x:row>
+    <x:row r="31" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A31" s="35" t="str">
         <x:v>Datos mixtos</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="str">
+      <x:c r="B31" s="33" t="str">
         <x:v>Para no inventar, algunas filas usan FY2025/FY2026 y otras el último trimestre disponible. La hoja Historial separa los periodos.</x:v>
       </x:c>
-      <x:c r="C21" s="33"/>
-      <x:c r="D21" s="33"/>
-      <x:c r="E21" s="33"/>
-      <x:c r="F21" s="33"/>
-      <x:c r="G21" s="33"/>
-      <x:c r="H21" s="33"/>
-      <x:c r="I21" s="33"/>
-      <x:c r="J21" s="33"/>
-      <x:c r="K21" s="33"/>
-      <x:c r="L21" s="33"/>
-      <x:c r="M21" s="33"/>
-      <x:c r="N21" s="33"/>
-      <x:c r="O21" s="33"/>
-      <x:c r="P21" s="33"/>
-      <x:c r="Q21" s="33"/>
-      <x:c r="R21" s="33"/>
-      <x:c r="S21" s="33"/>
-      <x:c r="T21" s="33"/>
-      <x:c r="U21" s="33"/>
-      <x:c r="V21" s="33"/>
-      <x:c r="W21" s="33"/>
-      <x:c r="X21" s="33"/>
-      <x:c r="Y21" s="33"/>
-      <x:c r="Z21" s="33"/>
-      <x:c r="AA21" s="33"/>
-      <x:c r="AB21" s="33"/>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="C31" s="33"/>
+      <x:c r="D31" s="33"/>
+      <x:c r="E31" s="33"/>
+      <x:c r="F31" s="33"/>
+      <x:c r="G31" s="33"/>
+      <x:c r="H31" s="33"/>
+      <x:c r="I31" s="33"/>
+      <x:c r="J31" s="33"/>
+      <x:c r="K31" s="33"/>
+      <x:c r="L31" s="33"/>
+      <x:c r="M31" s="33"/>
+      <x:c r="N31" s="33"/>
+      <x:c r="O31" s="33"/>
+      <x:c r="P31" s="33"/>
+      <x:c r="Q31" s="33"/>
+      <x:c r="R31" s="33"/>
+      <x:c r="S31" s="33"/>
+      <x:c r="T31" s="33"/>
+      <x:c r="U31" s="33"/>
+      <x:c r="V31" s="33"/>
+      <x:c r="W31" s="33"/>
+      <x:c r="X31" s="33"/>
+      <x:c r="Y31" s="33"/>
+      <x:c r="Z31" s="33"/>
+      <x:c r="AA31" s="33"/>
+      <x:c r="AB31" s="33"/>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="35" t="str">
         <x:v>Estado</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="str">
+      <x:c r="B32" s="33" t="str">
         <x:v>La prioridad es una señal de trabajo, no una orden de compra. Define precio de entrada y condición de invalidación en Checklist_Lynch y Seguimiento.</x:v>
       </x:c>
-      <x:c r="C22" s="33"/>
-      <x:c r="D22" s="33"/>
-      <x:c r="E22" s="33"/>
-      <x:c r="F22" s="33"/>
-      <x:c r="G22" s="33"/>
-      <x:c r="H22" s="33"/>
-      <x:c r="I22" s="33"/>
-      <x:c r="J22" s="33"/>
-      <x:c r="K22" s="33"/>
-      <x:c r="L22" s="33"/>
-      <x:c r="M22" s="33"/>
-      <x:c r="N22" s="33"/>
-      <x:c r="O22" s="33"/>
-      <x:c r="P22" s="33"/>
-      <x:c r="Q22" s="33"/>
-      <x:c r="R22" s="33"/>
-      <x:c r="S22" s="33"/>
-      <x:c r="T22" s="33"/>
-      <x:c r="U22" s="33"/>
-      <x:c r="V22" s="33"/>
-      <x:c r="W22" s="33"/>
-      <x:c r="X22" s="33"/>
-      <x:c r="Y22" s="33"/>
-      <x:c r="Z22" s="33"/>
-      <x:c r="AA22" s="33"/>
-      <x:c r="AB22" s="33"/>
+      <x:c r="C32" s="33"/>
+      <x:c r="D32" s="33"/>
+      <x:c r="E32" s="33"/>
+      <x:c r="F32" s="33"/>
+      <x:c r="G32" s="33"/>
+      <x:c r="H32" s="33"/>
+      <x:c r="I32" s="33"/>
+      <x:c r="J32" s="33"/>
+      <x:c r="K32" s="33"/>
+      <x:c r="L32" s="33"/>
+      <x:c r="M32" s="33"/>
+      <x:c r="N32" s="33"/>
+      <x:c r="O32" s="33"/>
+      <x:c r="P32" s="33"/>
+      <x:c r="Q32" s="33"/>
+      <x:c r="R32" s="33"/>
+      <x:c r="S32" s="33"/>
+      <x:c r="T32" s="33"/>
+      <x:c r="U32" s="33"/>
+      <x:c r="V32" s="33"/>
+      <x:c r="W32" s="33"/>
+      <x:c r="X32" s="33"/>
+      <x:c r="Y32" s="33"/>
+      <x:c r="Z32" s="33"/>
+      <x:c r="AA32" s="33"/>
+      <x:c r="AB32" s="33"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:AB1"/>
     <x:mergeCell ref="A2:AB2"/>
-    <x:mergeCell ref="A19:AB19"/>
-    <x:mergeCell ref="B20:AB20"/>
-    <x:mergeCell ref="B21:AB21"/>
-    <x:mergeCell ref="B22:AB22"/>
+    <x:mergeCell ref="A29:AB29"/>
+    <x:mergeCell ref="B30:AB30"/>
+    <x:mergeCell ref="B31:AB31"/>
+    <x:mergeCell ref="B32:AB32"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:AB16">
+  <x:conditionalFormatting sqref="A5:AB26">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Alta prioridad"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Esperar"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56876d359aef4d6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2be6ee07d0e64d82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="12" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="42" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="14" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="30" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="B1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="C1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="D1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="E1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="F1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="G1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="H1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="I1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="J1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="K1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="L1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="M1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="N1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="O1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="P1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="Q1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="R1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="S1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="T1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="U1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+      <x:c r="V1" s="34" t="str">
+        <x:v>Análisis prioritario — valoración por escenarios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="I2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="K2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="L2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="M2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="N2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="O2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="P2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="Q2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="R2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="S2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="T2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="U2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+      <x:c r="V2" s="8" t="str">
+        <x:v>Cuatro candidatas para profundizar primero. Precios y EPS de referencia están en GBX/pence; los escenarios y PER objetivo son hipótesis de trabajo editables, no una recomendación automática.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
+      <x:c r="I3" s="33"/>
+      <x:c r="J3" s="33"/>
+      <x:c r="K3" s="33"/>
+      <x:c r="L3" s="33"/>
+      <x:c r="M3" s="33"/>
+      <x:c r="N3" s="33"/>
+      <x:c r="O3" s="33"/>
+      <x:c r="P3" s="33"/>
+      <x:c r="Q3" s="33"/>
+      <x:c r="R3" s="33"/>
+      <x:c r="S3" s="33"/>
+      <x:c r="T3" s="33"/>
+      <x:c r="U3" s="33"/>
+      <x:c r="V3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="36" hidden="0" customHeight="1">
+      <x:c r="A4" s="20" t="str">
+        <x:v>Empresa</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>Precio actual (GBX)</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>EPS referencia (GBX)</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>PER actual</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>EPS bajo</x:v>
+      </x:c>
+      <x:c r="G4" s="20" t="str">
+        <x:v>EPS base</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="str">
+        <x:v>EPS alto</x:v>
+      </x:c>
+      <x:c r="I4" s="20" t="str">
+        <x:v>PER bajo</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="str">
+        <x:v>PER base</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="str">
+        <x:v>PER alto</x:v>
+      </x:c>
+      <x:c r="L4" s="20" t="str">
+        <x:v>Precio razonable bajo (GBX)</x:v>
+      </x:c>
+      <x:c r="M4" s="20" t="str">
+        <x:v>Precio razonable base (GBX)</x:v>
+      </x:c>
+      <x:c r="N4" s="20" t="str">
+        <x:v>Precio razonable alto (GBX)</x:v>
+      </x:c>
+      <x:c r="O4" s="20" t="str">
+        <x:v>Margen seguridad</x:v>
+      </x:c>
+      <x:c r="P4" s="20" t="str">
+        <x:v>Precio entrada base (GBX)</x:v>
+      </x:c>
+      <x:c r="Q4" s="20" t="str">
+        <x:v>Upside base</x:v>
+      </x:c>
+      <x:c r="R4" s="20" t="str">
+        <x:v>Catalizador / qué comprobar</x:v>
+      </x:c>
+      <x:c r="S4" s="20" t="str">
+        <x:v>Invalidación</x:v>
+      </x:c>
+      <x:c r="T4" s="20" t="str">
+        <x:v>Decisión provisional</x:v>
+      </x:c>
+      <x:c r="U4" s="20" t="str">
+        <x:v>Próxima revisión</x:v>
+      </x:c>
+      <x:c r="V4" s="20" t="str">
+        <x:v>Fuentes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A5" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="B5" s="58" t="str">
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="C5" s="60" t="n">
+        <x:v>474.8</x:v>
+      </x:c>
+      <x:c r="D5" s="60" t="n">
+        <x:v>28.1</x:v>
+      </x:c>
+      <x:c r="E5" s="64" t="n">
+        <x:f>IFERROR(C5/D5,"")</x:f>
+        <x:v>16.89679715302491</x:v>
+      </x:c>
+      <x:c r="F5" s="60" t="n">
+        <x:v>28.1</x:v>
+      </x:c>
+      <x:c r="G5" s="60" t="n">
+        <x:v>30.02</x:v>
+      </x:c>
+      <x:c r="H5" s="60" t="n">
+        <x:v>31.09</x:v>
+      </x:c>
+      <x:c r="I5" s="62" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J5" s="62" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K5" s="62" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L5" s="71" t="n">
+        <x:f>F5*I5</x:f>
+        <x:v>393.40000000000003</x:v>
+      </x:c>
+      <x:c r="M5" s="71" t="n">
+        <x:f>G5*J5</x:f>
+        <x:v>510.34</x:v>
+      </x:c>
+      <x:c r="N5" s="71" t="n">
+        <x:f>H5*K5</x:f>
+        <x:v>590.71</x:v>
+      </x:c>
+      <x:c r="O5" s="63" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="P5" s="71" t="n">
+        <x:f>M5*(1-O5)</x:f>
+        <x:v>408.272</x:v>
+      </x:c>
+      <x:c r="Q5" s="72" t="n">
+        <x:f>IFERROR(M5/C5-1,"")</x:f>
+        <x:v>0.0748525695029485</x:v>
+      </x:c>
+      <x:c r="R5" s="58" t="str">
+        <x:v>H1 2026: comprobar EPS, membresía, ARPA, áreas estratégicas, LLM referrals y margen.</x:v>
+      </x:c>
+      <x:c r="S5" s="58" t="str">
+        <x:v>EPS sin crecimiento, membresía negativa, litigio/regulación o margen operativo &lt;65%.</x:v>
+      </x:c>
+      <x:c r="T5" s="58" t="str">
+        <x:v>Esperar: calidad alta, pero el escenario base ofrece poco margen al precio actual.</x:v>
+      </x:c>
+      <x:c r="U5" s="59" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="V5" s="40" t="str">
+        <x:v>RMV-MKT / RMV-FY25 / RMV-CONS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A6" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="B6" s="58" t="str">
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="C6" s="60" t="n">
+        <x:v>1540</x:v>
+      </x:c>
+      <x:c r="D6" s="60" t="n">
+        <x:v>211.2</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="n">
+        <x:f>IFERROR(C6/D6,"")</x:f>
+        <x:v>7.291666666666667</x:v>
+      </x:c>
+      <x:c r="F6" s="60" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G6" s="60" t="n">
+        <x:v>211.2</x:v>
+      </x:c>
+      <x:c r="H6" s="60" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="I6" s="62" t="n">
+        <x:v>6.5</x:v>
+      </x:c>
+      <x:c r="J6" s="62" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K6" s="62" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L6" s="71" t="n">
+        <x:f>F6*I6</x:f>
+        <x:v>1105</x:v>
+      </x:c>
+      <x:c r="M6" s="71" t="n">
+        <x:f>G6*J6</x:f>
+        <x:v>1900.8</x:v>
+      </x:c>
+      <x:c r="N6" s="71" t="n">
+        <x:f>H6*K6</x:f>
+        <x:v>2530</x:v>
+      </x:c>
+      <x:c r="O6" s="63" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="P6" s="71" t="n">
+        <x:f>M6*(1-O6)</x:f>
+        <x:v>1520.64</x:v>
+      </x:c>
+      <x:c r="Q6" s="72" t="n">
+        <x:f>IFERROR(M6/C6-1,"")</x:f>
+        <x:v>0.2342857142857142</x:v>
+      </x:c>
+      <x:c r="R6" s="58" t="str">
+        <x:v>Interinos: reservas, yield, combustible, capacidad, Gatwick, caja neta y recompra de £250m.</x:v>
+      </x:c>
+      <x:c r="S6" s="58" t="str">
+        <x:v>Caída de demanda o margen, combustible/divisa adversos, geopolítica o uso agresivo de la caja.</x:v>
+      </x:c>
+      <x:c r="T6" s="58" t="str">
+        <x:v>Compra escalonada solo si el precio vuelve a la zona de entrada y se acepta la ciclicidad.</x:v>
+      </x:c>
+      <x:c r="U6" s="59" t="n">
+        <x:v>46343</x:v>
+      </x:c>
+      <x:c r="V6" s="40" t="str">
+        <x:v>JET2-MKT / JET2-FY26 / JET2-CAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A7" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="B7" s="58" t="str">
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="C7" s="60" t="n">
+        <x:v>821.5</x:v>
+      </x:c>
+      <x:c r="D7" s="60" t="n">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="E7" s="64" t="n">
+        <x:f>IFERROR(C7/D7,"")</x:f>
+        <x:v>16.697154471544714</x:v>
+      </x:c>
+      <x:c r="F7" s="60" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G7" s="60" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H7" s="60" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I7" s="62" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J7" s="62" t="n">
+        <x:v>17.5</x:v>
+      </x:c>
+      <x:c r="K7" s="62" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L7" s="71" t="n">
+        <x:f>F7*I7</x:f>
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="M7" s="71" t="n">
+        <x:f>G7*J7</x:f>
+        <x:v>892.5</x:v>
+      </x:c>
+      <x:c r="N7" s="71" t="n">
+        <x:f>H7*K7</x:f>
+        <x:v>1045</x:v>
+      </x:c>
+      <x:c r="O7" s="63" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="P7" s="71" t="n">
+        <x:f>M7*(1-O7)</x:f>
+        <x:v>714</x:v>
+      </x:c>
+      <x:c r="Q7" s="72" t="n">
+        <x:f>IFERROR(M7/C7-1,"")</x:f>
+        <x:v>0.08642726719415705</x:v>
+      </x:c>
+      <x:c r="R7" s="58" t="str">
+        <x:v>Trading update: ventas comparables, margen bruto, DIY Kitchens, aperturas, vivienda y caja.</x:v>
+      </x:c>
+      <x:c r="S7" s="58" t="str">
+        <x:v>LFL negativo, margen decreciente, adquisición sin retorno o deuda/capex tensionan la caja.</x:v>
+      </x:c>
+      <x:c r="T7" s="58" t="str">
+        <x:v>Vigilar: interesante si ofrece al menos 20% de margen de seguridad sobre el caso base.</x:v>
+      </x:c>
+      <x:c r="U7" s="59" t="n">
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="V7" s="40" t="str">
+        <x:v>HWDN-MKT / HWDN-H1-26 / HWDN-CAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A8" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="B8" s="58" t="str">
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="C8" s="60" t="n">
+        <x:v>4390</x:v>
+      </x:c>
+      <x:c r="D8" s="60" t="n">
+        <x:v>300.30057</x:v>
+      </x:c>
+      <x:c r="E8" s="64" t="n">
+        <x:f>IFERROR(C8/D8,"")</x:f>
+        <x:v>14.61868687095732</x:v>
+      </x:c>
+      <x:c r="F8" s="60" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G8" s="60" t="n">
+        <x:v>300.30057</x:v>
+      </x:c>
+      <x:c r="H8" s="60" t="n">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="I8" s="62" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J8" s="62" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K8" s="62" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="L8" s="71" t="n">
+        <x:f>F8*I8</x:f>
+        <x:v>2750</x:v>
+      </x:c>
+      <x:c r="M8" s="71" t="n">
+        <x:f>G8*J8</x:f>
+        <x:v>4204.20798</x:v>
+      </x:c>
+      <x:c r="N8" s="71" t="n">
+        <x:f>H8*K8</x:f>
+        <x:v>5760</x:v>
+      </x:c>
+      <x:c r="O8" s="63" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="P8" s="71" t="n">
+        <x:f>M8*(1-O8)</x:f>
+        <x:v>3363.3663840000004</x:v>
+      </x:c>
+      <x:c r="Q8" s="72" t="n">
+        <x:f>IFERROR(M8/C8-1,"")</x:f>
+        <x:v>-0.04232164464692478</x:v>
+      </x:c>
+      <x:c r="R8" s="58" t="str">
+        <x:v>Resultados H1: pedidos nuevos/existentes, AOV, margen, aranceles, caja y guía.</x:v>
+      </x:c>
+      <x:c r="S8" s="58" t="str">
+        <x:v>Pedidos y margen siguen bajando, aranceles erosionan beneficio o la caja se consume.</x:v>
+      </x:c>
+      <x:c r="T8" s="58" t="str">
+        <x:v>Esperar H1: el precio actual exige recuperación; no comprar antes de confirmar pedidos.</x:v>
+      </x:c>
+      <x:c r="U8" s="59" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="V8" s="40" t="str">
+        <x:v>FOUR-MKT / FOUR-FY25 / FOUR-CAL</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="33"/>
+      <x:c r="B9" s="33"/>
+      <x:c r="C9" s="33"/>
+      <x:c r="D9" s="33"/>
+      <x:c r="E9" s="33"/>
+      <x:c r="F9" s="33"/>
+      <x:c r="G9" s="33"/>
+      <x:c r="H9" s="33"/>
+      <x:c r="I9" s="33"/>
+      <x:c r="J9" s="33"/>
+      <x:c r="K9" s="33"/>
+      <x:c r="L9" s="33"/>
+      <x:c r="M9" s="33"/>
+      <x:c r="N9" s="33"/>
+      <x:c r="O9" s="33"/>
+      <x:c r="P9" s="33"/>
+      <x:c r="Q9" s="33"/>
+      <x:c r="R9" s="33"/>
+      <x:c r="S9" s="33"/>
+      <x:c r="T9" s="33"/>
+      <x:c r="U9" s="33"/>
+      <x:c r="V9" s="33"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="33"/>
+      <x:c r="B10" s="33"/>
+      <x:c r="C10" s="33"/>
+      <x:c r="D10" s="33"/>
+      <x:c r="E10" s="33"/>
+      <x:c r="F10" s="33"/>
+      <x:c r="G10" s="33"/>
+      <x:c r="H10" s="33"/>
+      <x:c r="I10" s="33"/>
+      <x:c r="J10" s="33"/>
+      <x:c r="K10" s="33"/>
+      <x:c r="L10" s="33"/>
+      <x:c r="M10" s="33"/>
+      <x:c r="N10" s="33"/>
+      <x:c r="O10" s="33"/>
+      <x:c r="P10" s="33"/>
+      <x:c r="Q10" s="33"/>
+      <x:c r="R10" s="33"/>
+      <x:c r="S10" s="33"/>
+      <x:c r="T10" s="33"/>
+      <x:c r="U10" s="33"/>
+      <x:c r="V10" s="33"/>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="B11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="C11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="D11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="E11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="F11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="G11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="H11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="I11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="J11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="K11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="L11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="M11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="N11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="O11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="P11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="Q11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="R11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="S11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="T11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="U11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+      <x:c r="V11" s="36" t="str">
+        <x:v>Cómo leer y actualizar los escenarios</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A12" s="35" t="str">
+        <x:v>EPS bajo/base/alto</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>Supuestos editables; el caso base usa consenso solo en Rightmove y referencias FY26/H1 en el resto.</x:v>
+      </x:c>
+      <x:c r="C12" s="33"/>
+      <x:c r="D12" s="33"/>
+      <x:c r="E12" s="33"/>
+      <x:c r="F12" s="33"/>
+      <x:c r="G12" s="33"/>
+      <x:c r="H12" s="33"/>
+      <x:c r="I12" s="33"/>
+      <x:c r="J12" s="33"/>
+      <x:c r="K12" s="33"/>
+      <x:c r="L12" s="33"/>
+      <x:c r="M12" s="33"/>
+      <x:c r="N12" s="33"/>
+      <x:c r="O12" s="33"/>
+      <x:c r="P12" s="33"/>
+      <x:c r="Q12" s="33"/>
+      <x:c r="R12" s="33"/>
+      <x:c r="S12" s="33"/>
+      <x:c r="T12" s="33"/>
+      <x:c r="U12" s="33"/>
+      <x:c r="V12" s="33"/>
+    </x:row>
+    <x:row r="13" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A13" s="35" t="str">
+        <x:v>PER objetivo</x:v>
+      </x:c>
+      <x:c r="B13" s="33" t="str">
+        <x:v>Múltiplo de salida elegido por calidad, ciclicidad y riesgo; no es una predicción.</x:v>
+      </x:c>
+      <x:c r="C13" s="33"/>
+      <x:c r="D13" s="33"/>
+      <x:c r="E13" s="33"/>
+      <x:c r="F13" s="33"/>
+      <x:c r="G13" s="33"/>
+      <x:c r="H13" s="33"/>
+      <x:c r="I13" s="33"/>
+      <x:c r="J13" s="33"/>
+      <x:c r="K13" s="33"/>
+      <x:c r="L13" s="33"/>
+      <x:c r="M13" s="33"/>
+      <x:c r="N13" s="33"/>
+      <x:c r="O13" s="33"/>
+      <x:c r="P13" s="33"/>
+      <x:c r="Q13" s="33"/>
+      <x:c r="R13" s="33"/>
+      <x:c r="S13" s="33"/>
+      <x:c r="T13" s="33"/>
+      <x:c r="U13" s="33"/>
+      <x:c r="V13" s="33"/>
+    </x:row>
+    <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A14" s="35" t="str">
+        <x:v>Precio entrada base</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>Precio razonable base × (1 – margen de seguridad).</x:v>
+      </x:c>
+      <x:c r="C14" s="33"/>
+      <x:c r="D14" s="33"/>
+      <x:c r="E14" s="33"/>
+      <x:c r="F14" s="33"/>
+      <x:c r="G14" s="33"/>
+      <x:c r="H14" s="33"/>
+      <x:c r="I14" s="33"/>
+      <x:c r="J14" s="33"/>
+      <x:c r="K14" s="33"/>
+      <x:c r="L14" s="33"/>
+      <x:c r="M14" s="33"/>
+      <x:c r="N14" s="33"/>
+      <x:c r="O14" s="33"/>
+      <x:c r="P14" s="33"/>
+      <x:c r="Q14" s="33"/>
+      <x:c r="R14" s="33"/>
+      <x:c r="S14" s="33"/>
+      <x:c r="T14" s="33"/>
+      <x:c r="U14" s="33"/>
+      <x:c r="V14" s="33"/>
+    </x:row>
+    <x:row r="15" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A15" s="35" t="str">
+        <x:v>Disciplina Lynch</x:v>
+      </x:c>
+      <x:c r="B15" s="33" t="str">
+        <x:v>Cuando llegue la fecha de revisión, sustituye los escenarios por datos nuevos y cambia la decisión solo si cambia la evidencia.</x:v>
+      </x:c>
+      <x:c r="C15" s="33"/>
+      <x:c r="D15" s="33"/>
+      <x:c r="E15" s="33"/>
+      <x:c r="F15" s="33"/>
+      <x:c r="G15" s="33"/>
+      <x:c r="H15" s="33"/>
+      <x:c r="I15" s="33"/>
+      <x:c r="J15" s="33"/>
+      <x:c r="K15" s="33"/>
+      <x:c r="L15" s="33"/>
+      <x:c r="M15" s="33"/>
+      <x:c r="N15" s="33"/>
+      <x:c r="O15" s="33"/>
+      <x:c r="P15" s="33"/>
+      <x:c r="Q15" s="33"/>
+      <x:c r="R15" s="33"/>
+      <x:c r="S15" s="33"/>
+      <x:c r="T15" s="33"/>
+      <x:c r="U15" s="33"/>
+      <x:c r="V15" s="33"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:V1"/>
+    <x:mergeCell ref="A2:V2"/>
+    <x:mergeCell ref="A11:V11"/>
+    <x:mergeCell ref="B12:V12"/>
+    <x:mergeCell ref="B13:V13"/>
+    <x:mergeCell ref="B14:V14"/>
+    <x:mergeCell ref="B15:V15"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="Q5:Q8">
+    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
+      <x:formula>0.2</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd16b8b20772482f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="66" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="B1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="C1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="D1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="E1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="F1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="G1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="H1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="I1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="J1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="K1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="L1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="M1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="N1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="O1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="P1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="Q1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="R1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+      <x:c r="S1" s="34" t="str">
+        <x:v>Ranking Lynch — potencial relativo de 10-bagger</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="I2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="J2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="K2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="L2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="M2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="N2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="O2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="P2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="Q2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="R2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+      <x:c r="S2" s="8" t="str">
+        <x:v>Ranking relativo dentro de esta watchlist, con base de datos al 2026-08-04. No es una probabilidad estadística ni una recomendación: mide cuánto runway, crecimiento, valoración, caja, tamaño y catalizadores reúne cada tesis.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="33"/>
+      <x:c r="B3" s="33"/>
+      <x:c r="C3" s="33"/>
+      <x:c r="D3" s="33"/>
+      <x:c r="E3" s="33"/>
+      <x:c r="F3" s="33"/>
+      <x:c r="G3" s="33"/>
+      <x:c r="H3" s="33"/>
+      <x:c r="I3" s="33"/>
+      <x:c r="J3" s="33"/>
+      <x:c r="K3" s="33"/>
+      <x:c r="L3" s="33"/>
+      <x:c r="M3" s="33"/>
+      <x:c r="N3" s="33"/>
+      <x:c r="O3" s="33"/>
+      <x:c r="P3" s="33"/>
+      <x:c r="Q3" s="33"/>
+      <x:c r="R3" s="33"/>
+      <x:c r="S3" s="33"/>
+    </x:row>
+    <x:row r="4" ht="36" hidden="0" customHeight="1">
+      <x:c r="A4" s="20" t="str">
+        <x:v>Orden</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>Empresa</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>Ticker</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>Tipo Lynch</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>Capitalización (m)</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>PER</x:v>
+      </x:c>
+      <x:c r="G4" s="20" t="str">
+        <x:v>Score Lynch /16</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="str">
+        <x:v>Crecimiento / runway (0-5)</x:v>
+      </x:c>
+      <x:c r="I4" s="20" t="str">
+        <x:v>Valoración (0-5)</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="str">
+        <x:v>Balance / caja (0-4)</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="str">
+        <x:v>Tamaño / escala (0-4)</x:v>
+      </x:c>
+      <x:c r="L4" s="20" t="str">
+        <x:v>Catalizador / palanca (0-4)</x:v>
+      </x:c>
+      <x:c r="M4" s="20" t="str">
+        <x:v>Score 10Bagger /22</x:v>
+      </x:c>
+      <x:c r="N4" s="20" t="str">
+        <x:v>Capitalización x10 (m)</x:v>
+      </x:c>
+      <x:c r="O4" s="20" t="str">
+        <x:v>Rating relativo</x:v>
+      </x:c>
+      <x:c r="P4" s="20" t="str">
+        <x:v>Motivo principal / freno</x:v>
+      </x:c>
+      <x:c r="Q4" s="20" t="str">
+        <x:v>Próxima revisión</x:v>
+      </x:c>
+      <x:c r="R4" s="20" t="str">
+        <x:v>Fuentes</x:v>
+      </x:c>
+      <x:c r="S4" s="20" t="str">
+        <x:v>Veredicto actual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A5" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M5)+COUNTIF($M$5:M5,M5)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B5" s="40" t="str">
+        <x:f>'Watchlist'!A7</x:f>
+        <x:v>eToro</x:v>
+      </x:c>
+      <x:c r="C5" s="40" t="str">
+        <x:f>'Watchlist'!B7</x:f>
+        <x:v>ETOR</x:v>
+      </x:c>
+      <x:c r="D5" s="40" t="str">
+        <x:f>'Watchlist'!D7</x:f>
+        <x:v>Nueva / alto crecimiento</x:v>
+      </x:c>
+      <x:c r="E5" s="91" t="n">
+        <x:f>'Watchlist'!H7</x:f>
+        <x:v>3010</x:v>
+      </x:c>
+      <x:c r="F5" s="92" t="n">
+        <x:f>'Watchlist'!I7</x:f>
+        <x:v>15.47</x:v>
+      </x:c>
+      <x:c r="G5" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L7</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H5" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I5" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J5" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K5" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L5" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M5" s="94" t="n">
+        <x:f>SUM(H5:L5)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N5" s="95" t="n">
+        <x:f>E5*10</x:f>
+        <x:v>30100</x:v>
+      </x:c>
+      <x:c r="O5" s="28" t="str">
+        <x:f>IF(M5&gt;=18,"Alta",IF(M5&gt;=16,"Media-alta",IF(M5&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="P5" s="58" t="str">
+        <x:v>Plataforma con crecimiento de net contribution/EBITDA, caja y recompra; freno: sensibilidad cripto/trading, dual class e historial corto.</x:v>
+      </x:c>
+      <x:c r="Q5" s="96" t="n">
+        <x:f>'Seguimiento'!D7</x:f>
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="R5" s="40" t="str">
+        <x:f>'Watchlist'!Y7&amp;" / "&amp;'Watchlist'!Z7</x:f>
+        <x:v>ETOR-MKT / ETOR-Q1-26</x:v>
+      </x:c>
+      <x:c r="S5" s="40" t="str">
+        <x:f>'Watchlist'!V7</x:f>
+        <x:v>Vigilar / posible entrada pequeña</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A6" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M6)+COUNTIF($M$5:M6,M6)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="40" t="str">
+        <x:f>'Watchlist'!A15</x:f>
+        <x:v>Kainos Group</x:v>
+      </x:c>
+      <x:c r="C6" s="40" t="str">
+        <x:f>'Watchlist'!B15</x:f>
+        <x:v>KNOS</x:v>
+      </x:c>
+      <x:c r="D6" s="40" t="str">
+        <x:f>'Watchlist'!D15</x:f>
+        <x:v>Crecimiento / nicho</x:v>
+      </x:c>
+      <x:c r="E6" s="91" t="n">
+        <x:f>'Watchlist'!H15</x:f>
+        <x:v>945.42</x:v>
+      </x:c>
+      <x:c r="F6" s="92" t="n">
+        <x:f>'Watchlist'!I15</x:f>
+        <x:v>23.1</x:v>
+      </x:c>
+      <x:c r="G6" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L15</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H6" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I6" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J6" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K6" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L6" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M6" s="94" t="n">
+        <x:f>SUM(H6:L6)</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N6" s="95" t="n">
+        <x:f>E6*10</x:f>
+        <x:v>9454.199999999999</x:v>
+      </x:c>
+      <x:c r="O6" s="28" t="str">
+        <x:f>IF(M6&gt;=18,"Alta",IF(M6&gt;=16,"Media-alta",IF(M6&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="P6" s="58" t="str">
+        <x:v>Nicho Workday con ARR +23%, bookings +32%, backlog +18% y caja neta; freno: concentración y PER todavía exigente.</x:v>
+      </x:c>
+      <x:c r="Q6" s="96" t="n">
+        <x:f>'Seguimiento'!D15</x:f>
+        <x:v>46272</x:v>
+      </x:c>
+      <x:c r="R6" s="40" t="str">
+        <x:f>'Watchlist'!Y15&amp;" / "&amp;'Watchlist'!Z15</x:f>
+        <x:v>KNOS-MKT / KNOS-FY26</x:v>
+      </x:c>
+      <x:c r="S6" s="40" t="str">
+        <x:f>'Watchlist'!V15</x:f>
+        <x:v>Vigilar / posible entrada pequeña</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A7" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M7)+COUNTIF($M$5:M7,M7)</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="40" t="str">
+        <x:f>'Watchlist'!A5</x:f>
+        <x:v>Atalaya Mining</x:v>
+      </x:c>
+      <x:c r="C7" s="40" t="str">
+        <x:f>'Watchlist'!B5</x:f>
+        <x:v>ATYM</x:v>
+      </x:c>
+      <x:c r="D7" s="40" t="str">
+        <x:f>'Watchlist'!D5</x:f>
+        <x:v>Existente / cíclica</x:v>
+      </x:c>
+      <x:c r="E7" s="91" t="n">
+        <x:f>'Watchlist'!H5</x:f>
+        <x:v>1410</x:v>
+      </x:c>
+      <x:c r="F7" s="92" t="n">
+        <x:f>'Watchlist'!I5</x:f>
+        <x:v>17.29</x:v>
+      </x:c>
+      <x:c r="G7" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L5</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H7" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I7" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J7" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K7" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L7" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M7" s="94" t="n">
+        <x:f>SUM(H7:L7)</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N7" s="95" t="n">
+        <x:f>E7*10</x:f>
+        <x:v>14100</x:v>
+      </x:c>
+      <x:c r="O7" s="28" t="str">
+        <x:f>IF(M7&gt;=18,"Alta",IF(M7&gt;=16,"Media-alta",IF(M7&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Alta</x:v>
+      </x:c>
+      <x:c r="P7" s="58" t="str">
+        <x:v>Cobre, beneficio +171% y caja neta con opcionalidad Touro; freno: una mina, commodity y ejecución/capex.</x:v>
+      </x:c>
+      <x:c r="Q7" s="96" t="n">
+        <x:f>'Seguimiento'!D5</x:f>
+        <x:v>46328</x:v>
+      </x:c>
+      <x:c r="R7" s="40" t="str">
+        <x:f>'Watchlist'!Y5&amp;" / "&amp;'Watchlist'!Z5</x:f>
+        <x:v>ATYM-MKT / ATYM-FY25</x:v>
+      </x:c>
+      <x:c r="S7" s="40" t="str">
+        <x:f>'Watchlist'!V5</x:f>
+        <x:v>Esperar / vigilar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A8" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M8)+COUNTIF($M$5:M8,M8)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="40" t="str">
+        <x:f>'Watchlist'!A26</x:f>
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="C8" s="40" t="str">
+        <x:f>'Watchlist'!B26</x:f>
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="D8" s="40" t="str">
+        <x:f>'Watchlist'!D26</x:f>
+        <x:v>Cíclica / crecimiento</x:v>
+      </x:c>
+      <x:c r="E8" s="91" t="n">
+        <x:f>'Watchlist'!H26</x:f>
+        <x:v>2780</x:v>
+      </x:c>
+      <x:c r="F8" s="92" t="n">
+        <x:f>'Watchlist'!I26</x:f>
+        <x:v>7.291667</x:v>
+      </x:c>
+      <x:c r="G8" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L26</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H8" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I8" s="93" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J8" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K8" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L8" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M8" s="94" t="n">
+        <x:f>SUM(H8:L8)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="95" t="n">
+        <x:f>E8*10</x:f>
+        <x:v>27800</x:v>
+      </x:c>
+      <x:c r="O8" s="28" t="str">
+        <x:f>IF(M8&gt;=18,"Alta",IF(M8&gt;=16,"Media-alta",IF(M8&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P8" s="58" t="str">
+        <x:v>PER 7.3x, caja neta £2.0bn y capacidad creciendo; freno: aerolínea/turoperador muy cíclico y margen sensible a combustible/divisa.</x:v>
+      </x:c>
+      <x:c r="Q8" s="96" t="n">
+        <x:f>'Seguimiento'!D26</x:f>
+        <x:v>46343</x:v>
+      </x:c>
+      <x:c r="R8" s="40" t="str">
+        <x:f>'Watchlist'!Y26&amp;" / "&amp;'Watchlist'!Z26</x:f>
+        <x:v>JET2-MKT / JET2-FY26</x:v>
+      </x:c>
+      <x:c r="S8" s="40" t="str">
+        <x:f>'Watchlist'!V26</x:f>
+        <x:v>Compra escalonada solo con margen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A9" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M9)+COUNTIF($M$5:M9,M9)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B9" s="40" t="str">
+        <x:f>'Watchlist'!A8</x:f>
+        <x:v>HBX Group</x:v>
+      </x:c>
+      <x:c r="C9" s="40" t="str">
+        <x:f>'Watchlist'!B8</x:f>
+        <x:v>HBX</x:v>
+      </x:c>
+      <x:c r="D9" s="40" t="str">
+        <x:f>'Watchlist'!D8</x:f>
+        <x:v>Nueva / crecimiento-cíclica</x:v>
+      </x:c>
+      <x:c r="E9" s="91" t="n">
+        <x:f>'Watchlist'!H8</x:f>
+        <x:v>1860</x:v>
+      </x:c>
+      <x:c r="F9" s="92" t="n">
+        <x:f>'Watchlist'!I8</x:f>
+        <x:v>10.21</x:v>
+      </x:c>
+      <x:c r="G9" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L8</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H9" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I9" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J9" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L9" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M9" s="94" t="n">
+        <x:f>SUM(H9:L9)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N9" s="95" t="n">
+        <x:f>E9*10</x:f>
+        <x:v>18600</x:v>
+      </x:c>
+      <x:c r="O9" s="28" t="str">
+        <x:f>IF(M9&gt;=18,"Alta",IF(M9&gt;=16,"Media-alta",IF(M9&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P9" s="58" t="str">
+        <x:v>TTV +17% en moneda constante, recompra y descuento frente a IPO; freno: deuda, guía recortada y transición directiva.</x:v>
+      </x:c>
+      <x:c r="Q9" s="96" t="n">
+        <x:f>'Seguimiento'!D8</x:f>
+        <x:v>46351</x:v>
+      </x:c>
+      <x:c r="R9" s="40" t="str">
+        <x:f>'Watchlist'!Y8&amp;" / "&amp;'Watchlist'!Z8</x:f>
+        <x:v>HBX-MKT / HBX-H1-26</x:v>
+      </x:c>
+      <x:c r="S9" s="40" t="str">
+        <x:f>'Watchlist'!V8</x:f>
+        <x:v>Vigilar / oportunidad con margen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A10" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M10)+COUNTIF($M$5:M10,M10)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B10" s="40" t="str">
+        <x:f>'Watchlist'!A16</x:f>
+        <x:v>Plus500</x:v>
+      </x:c>
+      <x:c r="C10" s="40" t="str">
+        <x:f>'Watchlist'!B16</x:f>
+        <x:v>PLUS</x:v>
+      </x:c>
+      <x:c r="D10" s="40" t="str">
+        <x:f>'Watchlist'!D16</x:f>
+        <x:v>Madura / cíclica</x:v>
+      </x:c>
+      <x:c r="E10" s="91" t="n">
+        <x:f>'Watchlist'!H16</x:f>
+        <x:v>2580</x:v>
+      </x:c>
+      <x:c r="F10" s="92" t="n">
+        <x:f>'Watchlist'!I16</x:f>
+        <x:v>12.83602</x:v>
+      </x:c>
+      <x:c r="G10" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L16</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H10" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I10" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J10" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K10" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L10" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M10" s="94" t="n">
+        <x:f>SUM(H10:L10)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N10" s="95" t="n">
+        <x:f>E10*10</x:f>
+        <x:v>25800</x:v>
+      </x:c>
+      <x:c r="O10" s="28" t="str">
+        <x:f>IF(M10&gt;=18,"Alta",IF(M10&gt;=16,"Media-alta",IF(M10&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P10" s="58" t="str">
+        <x:v>Caja &gt;£850m, PER 12.8x y retorno de capital; freno: EBITDA casi plano, clientes a la baja y regulación/ciclicidad.</x:v>
+      </x:c>
+      <x:c r="Q10" s="96" t="n">
+        <x:f>'Seguimiento'!D16</x:f>
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="R10" s="40" t="str">
+        <x:f>'Watchlist'!Y16&amp;" / "&amp;'Watchlist'!Z16</x:f>
+        <x:v>PLUS-MKT / PLUS-H1-26</x:v>
+      </x:c>
+      <x:c r="S10" s="40" t="str">
+        <x:f>'Watchlist'!V16</x:f>
+        <x:v>Oportunidad especulativa / esperar H1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="198" hidden="0" customHeight="1">
+      <x:c r="A11" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M11)+COUNTIF($M$5:M11,M11)</x:f>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="40" t="str">
+        <x:f>'Watchlist'!A21</x:f>
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="C11" s="40" t="str">
+        <x:f>'Watchlist'!B21</x:f>
+        <x:v>DOM</x:v>
+      </x:c>
+      <x:c r="D11" s="40" t="str">
+        <x:f>'Watchlist'!D21</x:f>
+        <x:v>Madura / recuperable</x:v>
+      </x:c>
+      <x:c r="E11" s="91" t="n">
+        <x:f>'Watchlist'!H21</x:f>
+        <x:v>768.41</x:v>
+      </x:c>
+      <x:c r="F11" s="92" t="n">
+        <x:f>'Watchlist'!I21</x:f>
+        <x:v>13.35099</x:v>
+      </x:c>
+      <x:c r="G11" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L21</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H11" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I11" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J11" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K11" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L11" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M11" s="94" t="n">
+        <x:f>SUM(H11:L11)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N11" s="95" t="n">
+        <x:f>E11*10</x:f>
+        <x:v>7684.099999999999</x:v>
+      </x:c>
+      <x:c r="O11" s="28" t="str">
+        <x:f>IF(M11&gt;=18,"Alta",IF(M11&gt;=16,"Media-alta",IF(M11&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P11" s="58" t="str">
+        <x:v>Marca/franquicia comprensible, yield 5.5% y activismo que puede forzar recompras; freno: EBITDA/PBT FY25 descendentes.</x:v>
+      </x:c>
+      <x:c r="Q11" s="96" t="n">
+        <x:f>'Seguimiento'!D21</x:f>
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="R11" s="40" t="str">
+        <x:f>'Watchlist'!Y21&amp;" / "&amp;'Watchlist'!Z21</x:f>
+        <x:v>DOM-MKT / DOM-FY25</x:v>
+      </x:c>
+      <x:c r="S11" s="40" t="str">
+        <x:f>'Watchlist'!V21</x:f>
+        <x:v>Esperar resultados / turnaround condicional</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="198" hidden="0" customHeight="1">
+      <x:c r="A12" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M12)+COUNTIF($M$5:M12,M12)</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B12" s="40" t="str">
+        <x:f>'Watchlist'!A17</x:f>
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="C12" s="40" t="str">
+        <x:f>'Watchlist'!B17</x:f>
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="D12" s="40" t="str">
+        <x:f>'Watchlist'!D17</x:f>
+        <x:v>Calidad / marketplace</x:v>
+      </x:c>
+      <x:c r="E12" s="91" t="n">
+        <x:f>'Watchlist'!H17</x:f>
+        <x:v>3520</x:v>
+      </x:c>
+      <x:c r="F12" s="92" t="n">
+        <x:f>'Watchlist'!I17</x:f>
+        <x:v>16.8968</x:v>
+      </x:c>
+      <x:c r="G12" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L17</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H12" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I12" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J12" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K12" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L12" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M12" s="94" t="n">
+        <x:f>SUM(H12:L12)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N12" s="95" t="n">
+        <x:f>E12*10</x:f>
+        <x:v>35200</x:v>
+      </x:c>
+      <x:c r="O12" s="28" t="str">
+        <x:f>IF(M12&gt;=18,"Alta",IF(M12&gt;=16,"Media-alta",IF(M12&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P12" s="58" t="str">
+        <x:v>Marketplace con red, guía de ingresos +8–10% y áreas estratégicas; freno: £3.5bn de capitalización, regulación y margen ya alto.</x:v>
+      </x:c>
+      <x:c r="Q12" s="96" t="n">
+        <x:f>'Seguimiento'!D17</x:f>
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="R12" s="40" t="str">
+        <x:f>'Watchlist'!Y17&amp;" / "&amp;'Watchlist'!Z17</x:f>
+        <x:v>RMV-MKT / RMV-FY25</x:v>
+      </x:c>
+      <x:c r="S12" s="40" t="str">
+        <x:f>'Watchlist'!V17</x:f>
+        <x:v>Esperar / calidad, no perseguir precio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A13" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M13)+COUNTIF($M$5:M13,M13)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B13" s="40" t="str">
+        <x:f>'Watchlist'!A25</x:f>
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="C13" s="40" t="str">
+        <x:f>'Watchlist'!B25</x:f>
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="D13" s="40" t="str">
+        <x:f>'Watchlist'!D25</x:f>
+        <x:v>Madura / calidad con descuento</x:v>
+      </x:c>
+      <x:c r="E13" s="91" t="n">
+        <x:f>'Watchlist'!H25</x:f>
+        <x:v>1230</x:v>
+      </x:c>
+      <x:c r="F13" s="92" t="n">
+        <x:f>'Watchlist'!I25</x:f>
+        <x:v>14.61869</x:v>
+      </x:c>
+      <x:c r="G13" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L25</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H13" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I13" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J13" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K13" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L13" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M13" s="94" t="n">
+        <x:f>SUM(H13:L13)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N13" s="95" t="n">
+        <x:f>E13*10</x:f>
+        <x:v>12300</x:v>
+      </x:c>
+      <x:c r="O13" s="28" t="str">
+        <x:f>IF(M13&gt;=18,"Alta",IF(M13&gt;=16,"Media-alta",IF(M13&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P13" s="58" t="str">
+        <x:v>Empresa pequeña, caja y retención de clientes existentes; freno: pedidos nuevos -12% y H1 debe demostrar que el bache es temporal.</x:v>
+      </x:c>
+      <x:c r="Q13" s="96" t="n">
+        <x:f>'Seguimiento'!D25</x:f>
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="R13" s="40" t="str">
+        <x:f>'Watchlist'!Y25&amp;" / "&amp;'Watchlist'!Z25</x:f>
+        <x:v>FOUR-MKT / FOUR-FY25</x:v>
+      </x:c>
+      <x:c r="S13" s="40" t="str">
+        <x:f>'Watchlist'!V25</x:f>
+        <x:v>Esperar H1 / no perseguir precio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A14" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M14)+COUNTIF($M$5:M14,M14)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B14" s="40" t="str">
+        <x:f>'Watchlist'!A22</x:f>
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="C14" s="40" t="str">
+        <x:f>'Watchlist'!B22</x:f>
+        <x:v>BWY</x:v>
+      </x:c>
+      <x:c r="D14" s="40" t="str">
+        <x:f>'Watchlist'!D22</x:f>
+        <x:v>Existente / cíclica</x:v>
+      </x:c>
+      <x:c r="E14" s="91" t="n">
+        <x:f>'Watchlist'!H22</x:f>
+        <x:v>2240</x:v>
+      </x:c>
+      <x:c r="F14" s="92" t="n">
+        <x:f>'Watchlist'!I22</x:f>
+        <x:v>14.72892</x:v>
+      </x:c>
+      <x:c r="G14" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L22</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H14" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I14" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J14" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K14" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L14" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M14" s="94" t="n">
+        <x:f>SUM(H14:L14)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N14" s="95" t="n">
+        <x:f>E14*10</x:f>
+        <x:v>22400</x:v>
+      </x:c>
+      <x:c r="O14" s="28" t="str">
+        <x:f>IF(M14&gt;=18,"Alta",IF(M14&gt;=16,"Media-alta",IF(M14&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media-alta</x:v>
+      </x:c>
+      <x:c r="P14" s="58" t="str">
+        <x:v>Orderbook £1.57bn, guía de beneficio +17% y valoración razonable; freno: normalización de vivienda y margen cíclico.</x:v>
+      </x:c>
+      <x:c r="Q14" s="96" t="n">
+        <x:f>'Seguimiento'!D22</x:f>
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="R14" s="40" t="str">
+        <x:f>'Watchlist'!Y22&amp;" / "&amp;'Watchlist'!Z22</x:f>
+        <x:v>BWY-MKT / BWY-TRD</x:v>
+      </x:c>
+      <x:c r="S14" s="40" t="str">
+        <x:f>'Watchlist'!V22</x:f>
+        <x:v>Vigilar / oportunidad cíclica</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A15" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M15)+COUNTIF($M$5:M15,M15)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="40" t="str">
+        <x:f>'Watchlist'!A9</x:f>
+        <x:v>Figma</x:v>
+      </x:c>
+      <x:c r="C15" s="40" t="str">
+        <x:f>'Watchlist'!B9</x:f>
+        <x:v>FIG</x:v>
+      </x:c>
+      <x:c r="D15" s="40" t="str">
+        <x:f>'Watchlist'!D9</x:f>
+        <x:v>Nueva / alto crecimiento</x:v>
+      </x:c>
+      <x:c r="E15" s="91" t="n">
+        <x:f>'Watchlist'!H9</x:f>
+        <x:v>14270</x:v>
+      </x:c>
+      <x:c r="F15" s="92" t="n">
+        <x:f>'Watchlist'!I9</x:f>
+        <x:v>-6.78</x:v>
+      </x:c>
+      <x:c r="G15" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L9</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H15" s="93" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I15" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K15" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L15" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M15" s="94" t="n">
+        <x:f>SUM(H15:L15)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N15" s="95" t="n">
+        <x:f>E15*10</x:f>
+        <x:v>142700</x:v>
+      </x:c>
+      <x:c r="O15" s="28" t="str">
+        <x:f>IF(M15&gt;=18,"Alta",IF(M15&gt;=16,"Media-alta",IF(M15&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P15" s="58" t="str">
+        <x:v>Ingresos +41%, NDR alto y FCF; freno decisivo: capitalización $14.3bn, pérdida GAAP, SBC/dilución y ~10x ventas.</x:v>
+      </x:c>
+      <x:c r="Q15" s="96" t="n">
+        <x:f>'Seguimiento'!D9</x:f>
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="R15" s="40" t="str">
+        <x:f>'Watchlist'!Y9&amp;" / "&amp;'Watchlist'!Z9</x:f>
+        <x:v>FIG-MKT / FIG-Q1-26</x:v>
+      </x:c>
+      <x:c r="S15" s="40" t="str">
+        <x:f>'Watchlist'!V9</x:f>
+        <x:v>Esperar / no comprar antes de resultados</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A16" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M16)+COUNTIF($M$5:M16,M16)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B16" s="40" t="str">
+        <x:f>'Watchlist'!A10</x:f>
+        <x:v>JD Sports Fashion</x:v>
+      </x:c>
+      <x:c r="C16" s="40" t="str">
+        <x:f>'Watchlist'!B10</x:f>
+        <x:v>JD.</x:v>
+      </x:c>
+      <x:c r="D16" s="40" t="str">
+        <x:f>'Watchlist'!D10</x:f>
+        <x:v>Madura / crecimiento</x:v>
+      </x:c>
+      <x:c r="E16" s="91" t="n">
+        <x:f>'Watchlist'!H10</x:f>
+        <x:v>4120</x:v>
+      </x:c>
+      <x:c r="F16" s="92" t="n">
+        <x:f>'Watchlist'!I10</x:f>
+        <x:v>9.986</x:v>
+      </x:c>
+      <x:c r="G16" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L10</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H16" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I16" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J16" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K16" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L16" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M16" s="94" t="n">
+        <x:f>SUM(H16:L16)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N16" s="95" t="n">
+        <x:f>E16*10</x:f>
+        <x:v>41200</x:v>
+      </x:c>
+      <x:c r="O16" s="28" t="str">
+        <x:f>IF(M16&gt;=18,"Alta",IF(M16&gt;=16,"Media-alta",IF(M16&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P16" s="58" t="str">
+        <x:v>Ventas +10.5%, FCF +36%, recompra y PER 10x; freno: beneficio operativo -5.4%, inventario, EE. UU. y divisa.</x:v>
+      </x:c>
+      <x:c r="Q16" s="96" t="n">
+        <x:f>'Seguimiento'!D10</x:f>
+        <x:v>46254</x:v>
+      </x:c>
+      <x:c r="R16" s="40" t="str">
+        <x:f>'Watchlist'!Y10&amp;" / "&amp;'Watchlist'!Z10</x:f>
+        <x:v>JD-MKT / JD-FY26</x:v>
+      </x:c>
+      <x:c r="S16" s="40" t="str">
+        <x:f>'Watchlist'!V10</x:f>
+        <x:v>Oportunidad condicional / vigilar márgenes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A17" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M17)+COUNTIF($M$5:M17,M17)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B17" s="40" t="str">
+        <x:f>'Watchlist'!A23</x:f>
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="C17" s="40" t="str">
+        <x:f>'Watchlist'!B23</x:f>
+        <x:v>BAB</x:v>
+      </x:c>
+      <x:c r="D17" s="40" t="str">
+        <x:f>'Watchlist'!D23</x:f>
+        <x:v>Defensa / turnaround</x:v>
+      </x:c>
+      <x:c r="E17" s="91" t="n">
+        <x:f>'Watchlist'!H23</x:f>
+        <x:v>5510</x:v>
+      </x:c>
+      <x:c r="F17" s="92" t="n">
+        <x:f>'Watchlist'!I23</x:f>
+        <x:v>18.52893</x:v>
+      </x:c>
+      <x:c r="G17" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L23</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H17" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I17" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J17" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K17" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L17" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M17" s="94" t="n">
+        <x:f>SUM(H17:L17)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N17" s="95" t="n">
+        <x:f>E17*10</x:f>
+        <x:v>55100</x:v>
+      </x:c>
+      <x:c r="O17" s="28" t="str">
+        <x:f>IF(M17&gt;=18,"Alta",IF(M17&gt;=16,"Media-alta",IF(M17&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P17" s="58" t="str">
+        <x:v>Backlog £9.8bn, FCF +£109m y caja neta; freno: ejecución contractual y cargo Type 31 reducen la pureza de la historia.</x:v>
+      </x:c>
+      <x:c r="Q17" s="96" t="n">
+        <x:f>'Seguimiento'!D23</x:f>
+        <x:v>46346</x:v>
+      </x:c>
+      <x:c r="R17" s="40" t="str">
+        <x:f>'Watchlist'!Y23&amp;" / "&amp;'Watchlist'!Z23</x:f>
+        <x:v>BAB-MKT / BAB-FY26</x:v>
+      </x:c>
+      <x:c r="S17" s="40" t="str">
+        <x:f>'Watchlist'!V23</x:f>
+        <x:v>Vigilar / recuperación con caja</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A18" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M18)+COUNTIF($M$5:M18,M18)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B18" s="40" t="str">
+        <x:f>'Watchlist'!A24</x:f>
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="C18" s="40" t="str">
+        <x:f>'Watchlist'!B24</x:f>
+        <x:v>OXIG</x:v>
+      </x:c>
+      <x:c r="D18" s="40" t="str">
+        <x:f>'Watchlist'!D24</x:f>
+        <x:v>Nicho / tecnología</x:v>
+      </x:c>
+      <x:c r="E18" s="91" t="n">
+        <x:f>'Watchlist'!H24</x:f>
+        <x:v>1570</x:v>
+      </x:c>
+      <x:c r="F18" s="92" t="n">
+        <x:f>'Watchlist'!I24</x:f>
+        <x:v>33.806</x:v>
+      </x:c>
+      <x:c r="G18" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L24</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H18" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K18" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L18" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M18" s="94" t="n">
+        <x:f>SUM(H18:L18)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N18" s="95" t="n">
+        <x:f>E18*10</x:f>
+        <x:v>15700</x:v>
+      </x:c>
+      <x:c r="O18" s="28" t="str">
+        <x:f>IF(M18&gt;=18,"Alta",IF(M18&gt;=16,"Media-alta",IF(M18&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P18" s="58" t="str">
+        <x:v>Nicho científico, caja neta y book-to-bill 1.067; freno: ingresos/margen bajan y PER 33.8x espera la recuperación.</x:v>
+      </x:c>
+      <x:c r="Q18" s="96" t="n">
+        <x:f>'Seguimiento'!D24</x:f>
+        <x:v>46338</x:v>
+      </x:c>
+      <x:c r="R18" s="40" t="str">
+        <x:f>'Watchlist'!Y24&amp;" / "&amp;'Watchlist'!Z24</x:f>
+        <x:v>OXIG-MKT / OXIG-FY26</x:v>
+      </x:c>
+      <x:c r="S18" s="40" t="str">
+        <x:f>'Watchlist'!V24</x:f>
+        <x:v>Vigilar / esperar conversión de pedidos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A19" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M19)+COUNTIF($M$5:M19,M19)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B19" s="40" t="str">
+        <x:f>'Watchlist'!A13</x:f>
+        <x:v>Auto Trader</x:v>
+      </x:c>
+      <x:c r="C19" s="40" t="str">
+        <x:f>'Watchlist'!B13</x:f>
+        <x:v>AUTO</x:v>
+      </x:c>
+      <x:c r="D19" s="40" t="str">
+        <x:f>'Watchlist'!D13</x:f>
+        <x:v>Madura / crecimiento</x:v>
+      </x:c>
+      <x:c r="E19" s="91" t="n">
+        <x:f>'Watchlist'!H13</x:f>
+        <x:v>4170</x:v>
+      </x:c>
+      <x:c r="F19" s="92" t="n">
+        <x:f>'Watchlist'!I13</x:f>
+        <x:v>15.58092</x:v>
+      </x:c>
+      <x:c r="G19" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L13</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H19" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I19" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J19" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K19" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L19" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M19" s="94" t="n">
+        <x:f>SUM(H19:L19)</x:f>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N19" s="95" t="n">
+        <x:f>E19*10</x:f>
+        <x:v>41700</x:v>
+      </x:c>
+      <x:c r="O19" s="28" t="str">
+        <x:f>IF(M19&gt;=18,"Alta",IF(M19&gt;=16,"Media-alta",IF(M19&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P19" s="58" t="str">
+        <x:v>Marketplace dominante, margen 63% y PER 15.6x; freno: crecimiento solo 4%, Deal Builder y deuda nueva.</x:v>
+      </x:c>
+      <x:c r="Q19" s="96" t="n">
+        <x:f>'Seguimiento'!D13</x:f>
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="R19" s="40" t="str">
+        <x:f>'Watchlist'!Y13&amp;" / "&amp;'Watchlist'!Z13</x:f>
+        <x:v>AUTO-MKT / AUTO-FY26</x:v>
+      </x:c>
+      <x:c r="S19" s="40" t="str">
+        <x:f>'Watchlist'!V13</x:f>
+        <x:v>Oportunidad condicional / vigilar Deal Builder</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A20" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M20)+COUNTIF($M$5:M20,M20)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B20" s="40" t="str">
+        <x:f>'Watchlist'!A12</x:f>
+        <x:v>Wise</x:v>
+      </x:c>
+      <x:c r="C20" s="40" t="str">
+        <x:f>'Watchlist'!B12</x:f>
+        <x:v>WISE</x:v>
+      </x:c>
+      <x:c r="D20" s="40" t="str">
+        <x:f>'Watchlist'!D12</x:f>
+        <x:v>Alto crecimiento / calidad</x:v>
+      </x:c>
+      <x:c r="E20" s="91" t="n">
+        <x:f>'Watchlist'!H12</x:f>
+        <x:v>8940</x:v>
+      </x:c>
+      <x:c r="F20" s="92" t="n">
+        <x:f>'Watchlist'!I12</x:f>
+        <x:v>24.38446</x:v>
+      </x:c>
+      <x:c r="G20" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L12</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H20" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I20" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K20" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L20" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M20" s="94" t="n">
+        <x:f>SUM(H20:L20)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N20" s="95" t="n">
+        <x:f>E20*10</x:f>
+        <x:v>89400</x:v>
+      </x:c>
+      <x:c r="O20" s="28" t="str">
+        <x:f>IF(M20&gt;=18,"Alta",IF(M20&gt;=16,"Media-alta",IF(M20&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P20" s="58" t="str">
+        <x:v>Volumen/net revenue crecen y el modelo escala; freno: PER 24.4x, take rate/tipos y capitalización £8.9bn.</x:v>
+      </x:c>
+      <x:c r="Q20" s="96" t="n">
+        <x:f>'Seguimiento'!D12</x:f>
+        <x:v>46310</x:v>
+      </x:c>
+      <x:c r="R20" s="40" t="str">
+        <x:f>'Watchlist'!Y12&amp;" / "&amp;'Watchlist'!Z12</x:f>
+        <x:v>WISE-MKT / WISE-Q1-27</x:v>
+      </x:c>
+      <x:c r="S20" s="40" t="str">
+        <x:f>'Watchlist'!V12</x:f>
+        <x:v>Vigilar / crecimiento con precio exigente</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A21" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M21)+COUNTIF($M$5:M21,M21)</x:f>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B21" s="40" t="str">
+        <x:f>'Watchlist'!A19</x:f>
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="C21" s="40" t="str">
+        <x:f>'Watchlist'!B19</x:f>
+        <x:v>CCC</x:v>
+      </x:c>
+      <x:c r="D21" s="40" t="str">
+        <x:f>'Watchlist'!D19</x:f>
+        <x:v>Crecimiento / servicios IT</x:v>
+      </x:c>
+      <x:c r="E21" s="91" t="n">
+        <x:f>'Watchlist'!H19</x:f>
+        <x:v>5060</x:v>
+      </x:c>
+      <x:c r="F21" s="92" t="n">
+        <x:f>'Watchlist'!I19</x:f>
+        <x:v>32.887</x:v>
+      </x:c>
+      <x:c r="G21" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L19</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H21" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I21" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K21" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L21" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M21" s="94" t="n">
+        <x:f>SUM(H21:L21)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="N21" s="95" t="n">
+        <x:f>E21*10</x:f>
+        <x:v>50600</x:v>
+      </x:c>
+      <x:c r="O21" s="28" t="str">
+        <x:f>IF(M21&gt;=18,"Alta",IF(M21&gt;=16,"Media-alta",IF(M21&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Media</x:v>
+      </x:c>
+      <x:c r="P21" s="58" t="str">
+        <x:v>Ingresos FY25 +32% y caja neta; freno: PER 32.9x y margen bruto/Managed Services cuestionan la calidad del crecimiento.</x:v>
+      </x:c>
+      <x:c r="Q21" s="96" t="n">
+        <x:f>'Seguimiento'!D19</x:f>
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="R21" s="40" t="str">
+        <x:f>'Watchlist'!Y19&amp;" / "&amp;'Watchlist'!Z19</x:f>
+        <x:v>CCC-MKT / CCC-Q1-26</x:v>
+      </x:c>
+      <x:c r="S21" s="40" t="str">
+        <x:f>'Watchlist'!V19</x:f>
+        <x:v>Vigilar / crecimiento con riesgo de margen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="211.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A22" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M22)+COUNTIF($M$5:M22,M22)</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B22" s="40" t="str">
+        <x:f>'Watchlist'!A20</x:f>
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="C22" s="40" t="str">
+        <x:f>'Watchlist'!B20</x:f>
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="D22" s="40" t="str">
+        <x:f>'Watchlist'!D20</x:f>
+        <x:v>Calidad / cíclica</x:v>
+      </x:c>
+      <x:c r="E22" s="91" t="n">
+        <x:f>'Watchlist'!H20</x:f>
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="F22" s="92" t="n">
+        <x:f>'Watchlist'!I20</x:f>
+        <x:v>16.69715</x:v>
+      </x:c>
+      <x:c r="G22" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L20</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H22" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I22" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J22" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K22" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L22" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M22" s="94" t="n">
+        <x:f>SUM(H22:L22)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N22" s="95" t="n">
+        <x:f>E22*10</x:f>
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="O22" s="28" t="str">
+        <x:f>IF(M22&gt;=18,"Alta",IF(M22&gt;=16,"Media-alta",IF(M22&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Baja</x:v>
+      </x:c>
+      <x:c r="P22" s="58" t="str">
+        <x:v>Modelo trade-only, margen bruto 62.8% y EBIT +5.5%; freno: vivienda/remodelación, tamaño y crecimiento moderado.</x:v>
+      </x:c>
+      <x:c r="Q22" s="96" t="n">
+        <x:f>'Seguimiento'!D20</x:f>
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="R22" s="40" t="str">
+        <x:f>'Watchlist'!Y20&amp;" / "&amp;'Watchlist'!Z20</x:f>
+        <x:v>HWDN-MKT / HWDN-H1-26</x:v>
+      </x:c>
+      <x:c r="S22" s="40" t="str">
+        <x:f>'Watchlist'!V20</x:f>
+        <x:v>Vigilar / solo con margen</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A23" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M23)+COUNTIF($M$5:M23,M23)</x:f>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B23" s="40" t="str">
+        <x:f>'Watchlist'!A18</x:f>
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="C23" s="40" t="str">
+        <x:f>'Watchlist'!B18</x:f>
+        <x:v>GAW</x:v>
+      </x:c>
+      <x:c r="D23" s="40" t="str">
+        <x:f>'Watchlist'!D18</x:f>
+        <x:v>Calidad / IP y nicho</x:v>
+      </x:c>
+      <x:c r="E23" s="91" t="n">
+        <x:f>'Watchlist'!H18</x:f>
+        <x:v>6590</x:v>
+      </x:c>
+      <x:c r="F23" s="92" t="n">
+        <x:f>'Watchlist'!I18</x:f>
+        <x:v>33.518</x:v>
+      </x:c>
+      <x:c r="G23" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L18</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H23" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I23" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K23" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L23" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M23" s="94" t="n">
+        <x:f>SUM(H23:L23)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N23" s="95" t="n">
+        <x:f>E23*10</x:f>
+        <x:v>65900</x:v>
+      </x:c>
+      <x:c r="O23" s="28" t="str">
+        <x:f>IF(M23&gt;=18,"Alta",IF(M23&gt;=16,"Media-alta",IF(M23&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Baja</x:v>
+      </x:c>
+      <x:c r="P23" s="58" t="str">
+        <x:v>IP Warhammer, sin deuda y caja/dividendos; freno: PER 33.5x y capitalización £6.6bn limitan el 10x.</x:v>
+      </x:c>
+      <x:c r="Q23" s="96" t="n">
+        <x:f>'Seguimiento'!D18</x:f>
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="R23" s="40" t="str">
+        <x:f>'Watchlist'!Y18&amp;" / "&amp;'Watchlist'!Z18</x:f>
+        <x:v>GAW-MKT / GAW-FY26</x:v>
+      </x:c>
+      <x:c r="S23" s="40" t="str">
+        <x:f>'Watchlist'!V18</x:f>
+        <x:v>Vigilar / negocio excelente, precio exigente</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A24" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M24)+COUNTIF($M$5:M24,M24)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B24" s="40" t="str">
+        <x:f>'Watchlist'!A11</x:f>
+        <x:v>PayPal</x:v>
+      </x:c>
+      <x:c r="C24" s="40" t="str">
+        <x:f>'Watchlist'!B11</x:f>
+        <x:v>PYPL</x:v>
+      </x:c>
+      <x:c r="D24" s="40" t="str">
+        <x:f>'Watchlist'!D11</x:f>
+        <x:v>Madura / recuperable</x:v>
+      </x:c>
+      <x:c r="E24" s="91" t="n">
+        <x:f>'Watchlist'!H11</x:f>
+        <x:v>51451</x:v>
+      </x:c>
+      <x:c r="F24" s="92" t="n">
+        <x:f>'Watchlist'!I11</x:f>
+        <x:v>11.027</x:v>
+      </x:c>
+      <x:c r="G24" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L11</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H24" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I24" s="93" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J24" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K24" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L24" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M24" s="94" t="n">
+        <x:f>SUM(H24:L24)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N24" s="95" t="n">
+        <x:f>E24*10</x:f>
+        <x:v>514510</x:v>
+      </x:c>
+      <x:c r="O24" s="28" t="str">
+        <x:f>IF(M24&gt;=18,"Alta",IF(M24&gt;=16,"Media-alta",IF(M24&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Baja</x:v>
+      </x:c>
+      <x:c r="P24" s="58" t="str">
+        <x:v>PER 11x, FCF y recompras; freno: $51bn de capitalización, cuentas activas planas y branded checkout solo +2%.</x:v>
+      </x:c>
+      <x:c r="Q24" s="96" t="n">
+        <x:f>'Seguimiento'!D11</x:f>
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="R24" s="40" t="str">
+        <x:f>'Watchlist'!Y11&amp;" / "&amp;'Watchlist'!Z11</x:f>
+        <x:v>PYPL-MKT / PYPL-Q1-26</x:v>
+      </x:c>
+      <x:c r="S24" s="40" t="str">
+        <x:f>'Watchlist'!V11</x:f>
+        <x:v>Oportunidad especulativa / vigilar ejecución</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A25" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M25)+COUNTIF($M$5:M25,M25)</x:f>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B25" s="40" t="str">
+        <x:f>'Watchlist'!A14</x:f>
+        <x:v>B&amp;M European Value Retail</x:v>
+      </x:c>
+      <x:c r="C25" s="40" t="str">
+        <x:f>'Watchlist'!B14</x:f>
+        <x:v>BME</x:v>
+      </x:c>
+      <x:c r="D25" s="40" t="str">
+        <x:f>'Watchlist'!D14</x:f>
+        <x:v>Recuperable / cíclica</x:v>
+      </x:c>
+      <x:c r="E25" s="91" t="n">
+        <x:f>'Watchlist'!H14</x:f>
+        <x:v>2230</x:v>
+      </x:c>
+      <x:c r="F25" s="92" t="n">
+        <x:f>'Watchlist'!I14</x:f>
+        <x:v>13.85</x:v>
+      </x:c>
+      <x:c r="G25" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L14</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H25" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I25" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J25" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K25" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L25" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="M25" s="94" t="n">
+        <x:f>SUM(H25:L25)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N25" s="95" t="n">
+        <x:f>E25*10</x:f>
+        <x:v>22300</x:v>
+      </x:c>
+      <x:c r="O25" s="28" t="str">
+        <x:f>IF(M25&gt;=18,"Alta",IF(M25&gt;=16,"Media-alta",IF(M25&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Baja</x:v>
+      </x:c>
+      <x:c r="P25" s="58" t="str">
+        <x:v>Turnaround de margen y tiendas con dividendo; freno: beneficio -26%, LFL UK negativo y deuda neta £656m.</x:v>
+      </x:c>
+      <x:c r="Q25" s="96" t="n">
+        <x:f>'Seguimiento'!D14</x:f>
+        <x:v>46338</x:v>
+      </x:c>
+      <x:c r="R25" s="40" t="str">
+        <x:f>'Watchlist'!Y14&amp;" / "&amp;'Watchlist'!Z14</x:f>
+        <x:v>BME-MKT / BME-Q1-27</x:v>
+      </x:c>
+      <x:c r="S25" s="40" t="str">
+        <x:f>'Watchlist'!V14</x:f>
+        <x:v>Oportunidad de turnaround / esperar confirmación</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="184.8000030517578" hidden="0" customHeight="1">
+      <x:c r="A26" s="90" t="n">
+        <x:f>COUNTIF($M$5:$M$26,"&gt;"&amp;M26)+COUNTIF($M$5:M26,M26)</x:f>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B26" s="40" t="str">
+        <x:f>'Watchlist'!A6</x:f>
+        <x:v>Rio Tinto</x:v>
+      </x:c>
+      <x:c r="C26" s="40" t="str">
+        <x:f>'Watchlist'!B6</x:f>
+        <x:v>RIO</x:v>
+      </x:c>
+      <x:c r="D26" s="40" t="str">
+        <x:f>'Watchlist'!D6</x:f>
+        <x:v>Existente / cíclica</x:v>
+      </x:c>
+      <x:c r="E26" s="91" t="n">
+        <x:f>'Watchlist'!H6</x:f>
+        <x:v>118930</x:v>
+      </x:c>
+      <x:c r="F26" s="92" t="n">
+        <x:f>'Watchlist'!I6</x:f>
+        <x:v>16.05</x:v>
+      </x:c>
+      <x:c r="G26" s="39" t="n">
+        <x:f>'Checklist_Lynch'!L6</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H26" s="93" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" s="93" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J26" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K26" s="93" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" s="93" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M26" s="94" t="n">
+        <x:f>SUM(H26:L26)</x:f>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N26" s="95" t="n">
+        <x:f>E26*10</x:f>
+        <x:v>1189300</x:v>
+      </x:c>
+      <x:c r="O26" s="28" t="str">
+        <x:f>IF(M26&gt;=18,"Alta",IF(M26&gt;=16,"Media-alta",IF(M26&gt;=14,"Media","Baja")))</x:f>
+        <x:v>Baja</x:v>
+      </x:c>
+      <x:c r="P26" s="58" t="str">
+        <x:v>Cobre/dividendo y escala defensiva; freno decisivo: capitalización ~$119bn hace extremadamente improbable un 10x.</x:v>
+      </x:c>
+      <x:c r="Q26" s="96" t="n">
+        <x:f>'Seguimiento'!D6</x:f>
+        <x:v>46328</x:v>
+      </x:c>
+      <x:c r="R26" s="40" t="str">
+        <x:f>'Watchlist'!Y6&amp;" / "&amp;'Watchlist'!Z6</x:f>
+        <x:v>RIO-MKT / RIO-H1-26</x:v>
+      </x:c>
+      <x:c r="S26" s="40" t="str">
+        <x:f>'Watchlist'!V6</x:f>
+        <x:v>Compra escalonada / vigilar precio</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="33"/>
+      <x:c r="B27" s="33"/>
+      <x:c r="C27" s="33"/>
+      <x:c r="D27" s="33"/>
+      <x:c r="E27" s="33"/>
+      <x:c r="F27" s="33"/>
+      <x:c r="G27" s="33"/>
+      <x:c r="H27" s="33"/>
+      <x:c r="I27" s="33"/>
+      <x:c r="J27" s="33"/>
+      <x:c r="K27" s="33"/>
+      <x:c r="L27" s="33"/>
+      <x:c r="M27" s="33"/>
+      <x:c r="N27" s="33"/>
+      <x:c r="O27" s="33"/>
+      <x:c r="P27" s="33"/>
+      <x:c r="Q27" s="33"/>
+      <x:c r="R27" s="33"/>
+      <x:c r="S27" s="33"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="33"/>
+      <x:c r="B28" s="33"/>
+      <x:c r="C28" s="33"/>
+      <x:c r="D28" s="33"/>
+      <x:c r="E28" s="33"/>
+      <x:c r="F28" s="33"/>
+      <x:c r="G28" s="33"/>
+      <x:c r="H28" s="33"/>
+      <x:c r="I28" s="33"/>
+      <x:c r="J28" s="33"/>
+      <x:c r="K28" s="33"/>
+      <x:c r="L28" s="33"/>
+      <x:c r="M28" s="33"/>
+      <x:c r="N28" s="33"/>
+      <x:c r="O28" s="33"/>
+      <x:c r="P28" s="33"/>
+      <x:c r="Q28" s="33"/>
+      <x:c r="R28" s="33"/>
+      <x:c r="S28" s="33"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="B29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="C29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="D29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="E29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="F29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="G29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="H29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="I29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="J29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="K29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="L29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="M29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="N29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="O29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="P29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="Q29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="R29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+      <x:c r="S29" s="36" t="str">
+        <x:v>Cómo leer el ranking</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="35" t="str">
+        <x:v>Qué mide</x:v>
+      </x:c>
+      <x:c r="B30" s="33" t="str">
+        <x:v>El score pondera la posibilidad relativa de que el negocio pueda multiplicar mucho desde su tamaño actual; no intenta convertir una hipótesis en una probabilidad matemática.</x:v>
+      </x:c>
+      <x:c r="C30" s="33"/>
+      <x:c r="D30" s="33"/>
+      <x:c r="E30" s="33"/>
+      <x:c r="F30" s="33"/>
+      <x:c r="G30" s="33"/>
+      <x:c r="H30" s="33"/>
+      <x:c r="I30" s="33"/>
+      <x:c r="J30" s="33"/>
+      <x:c r="K30" s="33"/>
+      <x:c r="L30" s="33"/>
+      <x:c r="M30" s="33"/>
+      <x:c r="N30" s="33"/>
+      <x:c r="O30" s="33"/>
+      <x:c r="P30" s="33"/>
+      <x:c r="Q30" s="33"/>
+      <x:c r="R30" s="33"/>
+      <x:c r="S30" s="33"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="35" t="str">
+        <x:v>Runway</x:v>
+      </x:c>
+      <x:c r="B31" s="33" t="str">
+        <x:v>Crecimiento visible, mercado direccionable, cuota y capacidad de reinversión. La calidad sin runway no basta para un 10-bagger.</x:v>
+      </x:c>
+      <x:c r="C31" s="33"/>
+      <x:c r="D31" s="33"/>
+      <x:c r="E31" s="33"/>
+      <x:c r="F31" s="33"/>
+      <x:c r="G31" s="33"/>
+      <x:c r="H31" s="33"/>
+      <x:c r="I31" s="33"/>
+      <x:c r="J31" s="33"/>
+      <x:c r="K31" s="33"/>
+      <x:c r="L31" s="33"/>
+      <x:c r="M31" s="33"/>
+      <x:c r="N31" s="33"/>
+      <x:c r="O31" s="33"/>
+      <x:c r="P31" s="33"/>
+      <x:c r="Q31" s="33"/>
+      <x:c r="R31" s="33"/>
+      <x:c r="S31" s="33"/>
+    </x:row>
+    <x:row r="32" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A32" s="35" t="str">
+        <x:v>Tamaño x10</x:v>
+      </x:c>
+      <x:c r="B32" s="33" t="str">
+        <x:v>Capitalización actual ×10 para hacer tangible la barrera. Las divisas de la watchlist son mixtas: úsalo como orden de magnitud, no como comparación exacta.</x:v>
+      </x:c>
+      <x:c r="C32" s="33"/>
+      <x:c r="D32" s="33"/>
+      <x:c r="E32" s="33"/>
+      <x:c r="F32" s="33"/>
+      <x:c r="G32" s="33"/>
+      <x:c r="H32" s="33"/>
+      <x:c r="I32" s="33"/>
+      <x:c r="J32" s="33"/>
+      <x:c r="K32" s="33"/>
+      <x:c r="L32" s="33"/>
+      <x:c r="M32" s="33"/>
+      <x:c r="N32" s="33"/>
+      <x:c r="O32" s="33"/>
+      <x:c r="P32" s="33"/>
+      <x:c r="Q32" s="33"/>
+      <x:c r="R32" s="33"/>
+      <x:c r="S32" s="33"/>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="35" t="str">
+        <x:v>Orden</x:v>
+      </x:c>
+      <x:c r="B33" s="33" t="str">
+        <x:v>La columna Orden se recalcula si cambias H:L, pero las filas no se reordenan solas: ordena la tabla por Score 10Bagger descendente después de editar.</x:v>
+      </x:c>
+      <x:c r="C33" s="33"/>
+      <x:c r="D33" s="33"/>
+      <x:c r="E33" s="33"/>
+      <x:c r="F33" s="33"/>
+      <x:c r="G33" s="33"/>
+      <x:c r="H33" s="33"/>
+      <x:c r="I33" s="33"/>
+      <x:c r="J33" s="33"/>
+      <x:c r="K33" s="33"/>
+      <x:c r="L33" s="33"/>
+      <x:c r="M33" s="33"/>
+      <x:c r="N33" s="33"/>
+      <x:c r="O33" s="33"/>
+      <x:c r="P33" s="33"/>
+      <x:c r="Q33" s="33"/>
+      <x:c r="R33" s="33"/>
+      <x:c r="S33" s="33"/>
+    </x:row>
+    <x:row r="34" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A34" s="35" t="str">
+        <x:v>Disciplina Lynch</x:v>
+      </x:c>
+      <x:c r="B34" s="33" t="str">
+        <x:v>Una puntuación alta exige todavía leer resultados, comprobar deuda/dilución y definir un precio de entrada con margen de seguridad.</x:v>
+      </x:c>
+      <x:c r="C34" s="33"/>
+      <x:c r="D34" s="33"/>
+      <x:c r="E34" s="33"/>
+      <x:c r="F34" s="33"/>
+      <x:c r="G34" s="33"/>
+      <x:c r="H34" s="33"/>
+      <x:c r="I34" s="33"/>
+      <x:c r="J34" s="33"/>
+      <x:c r="K34" s="33"/>
+      <x:c r="L34" s="33"/>
+      <x:c r="M34" s="33"/>
+      <x:c r="N34" s="33"/>
+      <x:c r="O34" s="33"/>
+      <x:c r="P34" s="33"/>
+      <x:c r="Q34" s="33"/>
+      <x:c r="R34" s="33"/>
+      <x:c r="S34" s="33"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:S1"/>
+    <x:mergeCell ref="A2:S2"/>
+    <x:mergeCell ref="A29:S29"/>
+    <x:mergeCell ref="B30:S30"/>
+    <x:mergeCell ref="B31:S31"/>
+    <x:mergeCell ref="B32:S32"/>
+    <x:mergeCell ref="B33:S33"/>
+    <x:mergeCell ref="B34:S34"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="M5:M26">
+    <x:cfRule type="cellIs" dxfId="4" priority="1" operator="greaterThanOrEqual">
+      <x:formula>17</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
+      <x:formula>13</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="O5:O26">
+    <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Alta"/>
+    <x:cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="Baja"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05f55f980a374639"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3316,34 +7909,34 @@
       <x:c r="B5" s="58" t="str">
         <x:v>ATYM</x:v>
       </x:c>
-      <x:c r="C5" s="75" t="n">
+      <x:c r="C5" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D5" s="75" t="n">
+      <x:c r="D5" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" s="75" t="n">
+      <x:c r="E5" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F5" s="75" t="n">
+      <x:c r="F5" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="75" t="n">
+      <x:c r="G5" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H5" s="75" t="n">
+      <x:c r="H5" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I5" s="75" t="n">
+      <x:c r="I5" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="75" t="n">
+      <x:c r="J5" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K5" s="75" t="n">
+      <x:c r="K5" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L5" s="76" t="n">
+      <x:c r="L5" s="94" t="n">
         <x:f>SUM(C5:K5)</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -3365,34 +7958,34 @@
       <x:c r="B6" s="58" t="str">
         <x:v>RIO</x:v>
       </x:c>
-      <x:c r="C6" s="75" t="n">
+      <x:c r="C6" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D6" s="75" t="n">
+      <x:c r="D6" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E6" s="75" t="n">
+      <x:c r="E6" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" s="75" t="n">
+      <x:c r="F6" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G6" s="75" t="n">
+      <x:c r="G6" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H6" s="75" t="n">
+      <x:c r="H6" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I6" s="75" t="n">
+      <x:c r="I6" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="75" t="n">
+      <x:c r="J6" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K6" s="75" t="n">
+      <x:c r="K6" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L6" s="76" t="n">
+      <x:c r="L6" s="94" t="n">
         <x:f>SUM(C6:K6)</x:f>
         <x:v>14</x:v>
       </x:c>
@@ -3414,34 +8007,34 @@
       <x:c r="B7" s="58" t="str">
         <x:v>ETOR</x:v>
       </x:c>
-      <x:c r="C7" s="75" t="n">
+      <x:c r="C7" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="75" t="n">
+      <x:c r="D7" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E7" s="75" t="n">
+      <x:c r="E7" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F7" s="75" t="n">
+      <x:c r="F7" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="75" t="n">
+      <x:c r="G7" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H7" s="75" t="n">
+      <x:c r="H7" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I7" s="75" t="n">
+      <x:c r="I7" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J7" s="75" t="n">
+      <x:c r="J7" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K7" s="75" t="n">
+      <x:c r="K7" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L7" s="76" t="n">
+      <x:c r="L7" s="94" t="n">
         <x:f>SUM(C7:K7)</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -3463,34 +8056,34 @@
       <x:c r="B8" s="58" t="str">
         <x:v>HBX</x:v>
       </x:c>
-      <x:c r="C8" s="75" t="n">
+      <x:c r="C8" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D8" s="75" t="n">
+      <x:c r="D8" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E8" s="75" t="n">
+      <x:c r="E8" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F8" s="75" t="n">
+      <x:c r="F8" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G8" s="75" t="n">
+      <x:c r="G8" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H8" s="75" t="n">
+      <x:c r="H8" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I8" s="75" t="n">
+      <x:c r="I8" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="75" t="n">
+      <x:c r="J8" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="75" t="n">
+      <x:c r="K8" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L8" s="76" t="n">
+      <x:c r="L8" s="94" t="n">
         <x:f>SUM(C8:K8)</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -3512,34 +8105,34 @@
       <x:c r="B9" s="58" t="str">
         <x:v>FIG</x:v>
       </x:c>
-      <x:c r="C9" s="75" t="n">
+      <x:c r="C9" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D9" s="75" t="n">
+      <x:c r="D9" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E9" s="75" t="n">
+      <x:c r="E9" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F9" s="75" t="n">
+      <x:c r="F9" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G9" s="75" t="n">
+      <x:c r="G9" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H9" s="75" t="n">
+      <x:c r="H9" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I9" s="75" t="n">
+      <x:c r="I9" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J9" s="75" t="n">
+      <x:c r="J9" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K9" s="75" t="n">
+      <x:c r="K9" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L9" s="76" t="n">
+      <x:c r="L9" s="94" t="n">
         <x:f>SUM(C9:K9)</x:f>
         <x:v>10</x:v>
       </x:c>
@@ -3561,34 +8154,34 @@
       <x:c r="B10" s="58" t="str">
         <x:v>JD.</x:v>
       </x:c>
-      <x:c r="C10" s="75" t="n">
+      <x:c r="C10" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D10" s="75" t="n">
+      <x:c r="D10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E10" s="75" t="n">
+      <x:c r="E10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F10" s="75" t="n">
+      <x:c r="F10" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G10" s="75" t="n">
+      <x:c r="G10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H10" s="75" t="n">
+      <x:c r="H10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="75" t="n">
+      <x:c r="I10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J10" s="75" t="n">
+      <x:c r="J10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" s="75" t="n">
+      <x:c r="K10" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L10" s="76" t="n">
+      <x:c r="L10" s="94" t="n">
         <x:f>SUM(C10:K10)</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -3610,34 +8203,34 @@
       <x:c r="B11" s="58" t="str">
         <x:v>PYPL</x:v>
       </x:c>
-      <x:c r="C11" s="75" t="n">
+      <x:c r="C11" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D11" s="75" t="n">
+      <x:c r="D11" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E11" s="75" t="n">
+      <x:c r="E11" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F11" s="75" t="n">
+      <x:c r="F11" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G11" s="75" t="n">
+      <x:c r="G11" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H11" s="75" t="n">
+      <x:c r="H11" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I11" s="75" t="n">
+      <x:c r="I11" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="75" t="n">
+      <x:c r="J11" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K11" s="75" t="n">
+      <x:c r="K11" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L11" s="76" t="n">
+      <x:c r="L11" s="94" t="n">
         <x:f>SUM(C11:K11)</x:f>
         <x:v>11</x:v>
       </x:c>
@@ -3659,34 +8252,34 @@
       <x:c r="B12" s="58" t="str">
         <x:v>WISE</x:v>
       </x:c>
-      <x:c r="C12" s="75" t="n">
+      <x:c r="C12" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D12" s="75" t="n">
+      <x:c r="D12" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E12" s="75" t="n">
+      <x:c r="E12" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F12" s="75" t="n">
+      <x:c r="F12" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G12" s="75" t="n">
+      <x:c r="G12" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H12" s="75" t="n">
+      <x:c r="H12" s="104" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="75" t="n">
+      <x:c r="I12" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J12" s="75" t="n">
+      <x:c r="J12" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K12" s="75" t="n">
+      <x:c r="K12" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L12" s="76" t="n">
+      <x:c r="L12" s="94" t="n">
         <x:f>SUM(C12:K12)</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -3708,34 +8301,34 @@
       <x:c r="B13" s="58" t="str">
         <x:v>AUTO</x:v>
       </x:c>
-      <x:c r="C13" s="75" t="n">
+      <x:c r="C13" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D13" s="75" t="n">
+      <x:c r="D13" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E13" s="75" t="n">
+      <x:c r="E13" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F13" s="75" t="n">
+      <x:c r="F13" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G13" s="75" t="n">
+      <x:c r="G13" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H13" s="75" t="n">
+      <x:c r="H13" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I13" s="75" t="n">
+      <x:c r="I13" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="75" t="n">
+      <x:c r="J13" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" s="75" t="n">
+      <x:c r="K13" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L13" s="76" t="n">
+      <x:c r="L13" s="94" t="n">
         <x:f>SUM(C13:K13)</x:f>
         <x:v>13</x:v>
       </x:c>
@@ -3757,34 +8350,34 @@
       <x:c r="B14" s="58" t="str">
         <x:v>BME</x:v>
       </x:c>
-      <x:c r="C14" s="75" t="n">
+      <x:c r="C14" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D14" s="75" t="n">
+      <x:c r="D14" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E14" s="75" t="n">
+      <x:c r="E14" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F14" s="75" t="n">
+      <x:c r="F14" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G14" s="75" t="n">
+      <x:c r="G14" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H14" s="75" t="n">
+      <x:c r="H14" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" s="75" t="n">
+      <x:c r="I14" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14" s="75" t="n">
+      <x:c r="J14" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K14" s="75" t="n">
+      <x:c r="K14" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L14" s="76" t="n">
+      <x:c r="L14" s="94" t="n">
         <x:f>SUM(C14:K14)</x:f>
         <x:v>12</x:v>
       </x:c>
@@ -3806,34 +8399,34 @@
       <x:c r="B15" s="58" t="str">
         <x:v>KNOS</x:v>
       </x:c>
-      <x:c r="C15" s="75" t="n">
+      <x:c r="C15" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D15" s="75" t="n">
+      <x:c r="D15" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E15" s="75" t="n">
+      <x:c r="E15" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F15" s="75" t="n">
+      <x:c r="F15" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G15" s="75" t="n">
+      <x:c r="G15" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H15" s="75" t="n">
+      <x:c r="H15" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I15" s="75" t="n">
+      <x:c r="I15" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="75" t="n">
+      <x:c r="J15" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K15" s="75" t="n">
+      <x:c r="K15" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L15" s="76" t="n">
+      <x:c r="L15" s="94" t="n">
         <x:f>SUM(C15:K15)</x:f>
         <x:v>13</x:v>
       </x:c>
@@ -3855,34 +8448,34 @@
       <x:c r="B16" s="58" t="str">
         <x:v>PLUS</x:v>
       </x:c>
-      <x:c r="C16" s="75" t="n">
+      <x:c r="C16" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D16" s="75" t="n">
+      <x:c r="D16" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E16" s="75" t="n">
+      <x:c r="E16" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F16" s="75" t="n">
+      <x:c r="F16" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G16" s="75" t="n">
+      <x:c r="G16" s="104" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H16" s="75" t="n">
+      <x:c r="H16" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I16" s="75" t="n">
+      <x:c r="I16" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="75" t="n">
+      <x:c r="J16" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="75" t="n">
+      <x:c r="K16" s="104" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L16" s="76" t="n">
+      <x:c r="L16" s="94" t="n">
         <x:f>SUM(C16:K16)</x:f>
         <x:v>14</x:v>
       </x:c>
@@ -3897,248 +8490,738 @@
         <x:v>46238</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="33"/>
-      <x:c r="B17" s="33"/>
-      <x:c r="C17" s="33"/>
-      <x:c r="D17" s="33"/>
-      <x:c r="E17" s="33"/>
-      <x:c r="F17" s="33"/>
-      <x:c r="G17" s="33"/>
-      <x:c r="H17" s="33"/>
-      <x:c r="I17" s="33"/>
-      <x:c r="J17" s="33"/>
-      <x:c r="K17" s="33"/>
-      <x:c r="L17" s="33"/>
-      <x:c r="M17" s="33"/>
-      <x:c r="N17" s="33"/>
-      <x:c r="O17" s="33"/>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="33"/>
-      <x:c r="B18" s="33"/>
-      <x:c r="C18" s="33"/>
-      <x:c r="D18" s="33"/>
-      <x:c r="E18" s="33"/>
-      <x:c r="F18" s="33"/>
-      <x:c r="G18" s="33"/>
-      <x:c r="H18" s="33"/>
-      <x:c r="I18" s="33"/>
-      <x:c r="J18" s="33"/>
-      <x:c r="K18" s="33"/>
-      <x:c r="L18" s="33"/>
-      <x:c r="M18" s="33"/>
-      <x:c r="N18" s="33"/>
-      <x:c r="O18" s="33"/>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="36" t="str">
+    <x:row r="17" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A17" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="B17" s="58" t="str">
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="C17" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D17" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F17" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H17" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I17" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L17" s="94" t="n">
+        <x:f>SUM(C17:K17)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M17" s="28" t="str">
+        <x:f>IF(L17&gt;=12,"Candidato",IF(L17&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N17" s="58" t="str">
+        <x:v>H1: crecimiento de ingresos, ARPA, miembros, áreas nuevas, LLM referrals y litigio.</x:v>
+      </x:c>
+      <x:c r="O17" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="132" hidden="0" customHeight="1">
+      <x:c r="A18" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="B18" s="58" t="str">
+        <x:v>GAW</x:v>
+      </x:c>
+      <x:c r="C18" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D18" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F18" s="104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H18" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I18" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L18" s="94" t="n">
+        <x:f>SUM(C18:K18)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M18" s="28" t="str">
+        <x:f>IF(L18&gt;=12,"Candidato",IF(L18&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N18" s="58" t="str">
+        <x:v>Normalización del crecimiento, licencias, royalties, margen y retorno de caja al accionista.</x:v>
+      </x:c>
+      <x:c r="O18" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A19" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="B19" s="58" t="str">
+        <x:v>CCC</x:v>
+      </x:c>
+      <x:c r="C19" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D19" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F19" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G19" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H19" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I19" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L19" s="94" t="n">
+        <x:f>SUM(C19:K19)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M19" s="28" t="str">
+        <x:f>IF(L19&gt;=12,"Candidato",IF(L19&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N19" s="58" t="str">
+        <x:v>H1: Technology Sourcing, Managed Services, margen bruto, consenso y caja neta.</x:v>
+      </x:c>
+      <x:c r="O19" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="132" hidden="0" customHeight="1">
+      <x:c r="A20" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="B20" s="58" t="str">
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="C20" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D20" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F20" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G20" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H20" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I20" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K20" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L20" s="94" t="n">
+        <x:f>SUM(C20:K20)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M20" s="28" t="str">
+        <x:f>IF(L20&gt;=12,"Candidato",IF(L20&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N20" s="58" t="str">
+        <x:v>Trading update: ventas comparables, margen bruto, aperturas, vivienda y caja.</x:v>
+      </x:c>
+      <x:c r="O20" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A21" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="B21" s="58" t="str">
+        <x:v>DOM</x:v>
+      </x:c>
+      <x:c r="C21" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D21" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" s="104" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G21" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I21" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K21" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L21" s="94" t="n">
+        <x:f>SUM(C21:K21)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M21" s="28" t="str">
+        <x:f>IF(L21&gt;=12,"Candidato",IF(L21&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Vigilancia</x:v>
+      </x:c>
+      <x:c r="N21" s="58" t="str">
+        <x:v>H1: system sales, EBITDA, PBT, franquiciados, promociones y efecto del activismo.</x:v>
+      </x:c>
+      <x:c r="O21" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A22" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="B22" s="58" t="str">
+        <x:v>BWY</x:v>
+      </x:c>
+      <x:c r="C22" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E22" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F22" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H22" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I22" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K22" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L22" s="94" t="n">
+        <x:f>SUM(C22:K22)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M22" s="28" t="str">
+        <x:f>IF(L22&gt;=12,"Candidato",IF(L22&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N22" s="58" t="str">
+        <x:v>Trading update: reservas, cancelaciones, orderbook, margen, deuda y demanda hipotecaria.</x:v>
+      </x:c>
+      <x:c r="O22" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A23" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="B23" s="58" t="str">
+        <x:v>BAB</x:v>
+      </x:c>
+      <x:c r="C23" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D23" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E23" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F23" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H23" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I23" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K23" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L23" s="94" t="n">
+        <x:f>SUM(C23:K23)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M23" s="28" t="str">
+        <x:f>IF(L23&gt;=12,"Candidato",IF(L23&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N23" s="58" t="str">
+        <x:v>H1: FCF, backlog, margen, Type 31, ejecución contractual y recompra.</x:v>
+      </x:c>
+      <x:c r="O23" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A24" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="B24" s="58" t="str">
+        <x:v>OXIG</x:v>
+      </x:c>
+      <x:c r="C24" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D24" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F24" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H24" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K24" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L24" s="94" t="n">
+        <x:f>SUM(C24:K24)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M24" s="28" t="str">
+        <x:f>IF(L24&gt;=12,"Candidato",IF(L24&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N24" s="58" t="str">
+        <x:v>Interinos: convertir order intake en ventas, margen ajustado, book-to-bill y semiconductores.</x:v>
+      </x:c>
+      <x:c r="O24" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A25" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="B25" s="58" t="str">
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="C25" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D25" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F25" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G25" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H25" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K25" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L25" s="94" t="n">
+        <x:f>SUM(C25:K25)</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M25" s="28" t="str">
+        <x:f>IF(L25&gt;=12,"Candidato",IF(L25&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N25" s="58" t="str">
+        <x:v>H1: pedidos nuevos/existentes, AOV, margen, aranceles, caja y guía.</x:v>
+      </x:c>
+      <x:c r="O25" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A26" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="B26" s="58" t="str">
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="C26" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D26" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E26" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F26" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G26" s="104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H26" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I26" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J26" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K26" s="104" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L26" s="94" t="n">
+        <x:f>SUM(C26:K26)</x:f>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="M26" s="28" t="str">
+        <x:f>IF(L26&gt;=12,"Candidato",IF(L26&gt;=9,"Vigilancia","Revisar"))</x:f>
+        <x:v>Candidato</x:v>
+      </x:c>
+      <x:c r="N26" s="58" t="str">
+        <x:v>Interinos: ocupación, yield, combustible, capacidad, Gatwick, caja y recompra.</x:v>
+      </x:c>
+      <x:c r="O26" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="33"/>
+      <x:c r="B27" s="33"/>
+      <x:c r="C27" s="33"/>
+      <x:c r="D27" s="33"/>
+      <x:c r="E27" s="33"/>
+      <x:c r="F27" s="33"/>
+      <x:c r="G27" s="33"/>
+      <x:c r="H27" s="33"/>
+      <x:c r="I27" s="33"/>
+      <x:c r="J27" s="33"/>
+      <x:c r="K27" s="33"/>
+      <x:c r="L27" s="33"/>
+      <x:c r="M27" s="33"/>
+      <x:c r="N27" s="33"/>
+      <x:c r="O27" s="33"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="33"/>
+      <x:c r="B28" s="33"/>
+      <x:c r="C28" s="33"/>
+      <x:c r="D28" s="33"/>
+      <x:c r="E28" s="33"/>
+      <x:c r="F28" s="33"/>
+      <x:c r="G28" s="33"/>
+      <x:c r="H28" s="33"/>
+      <x:c r="I28" s="33"/>
+      <x:c r="J28" s="33"/>
+      <x:c r="K28" s="33"/>
+      <x:c r="L28" s="33"/>
+      <x:c r="M28" s="33"/>
+      <x:c r="N28" s="33"/>
+      <x:c r="O28" s="33"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="B19" s="36" t="str">
+      <x:c r="B29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="C19" s="36" t="str">
+      <x:c r="C29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="D19" s="36" t="str">
+      <x:c r="D29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="E19" s="36" t="str">
+      <x:c r="E29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="F19" s="36" t="str">
+      <x:c r="F29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="G19" s="36" t="str">
+      <x:c r="G29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="H19" s="36" t="str">
+      <x:c r="H29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="I19" s="36" t="str">
+      <x:c r="I29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="J19" s="36" t="str">
+      <x:c r="J29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="K19" s="36" t="str">
+      <x:c r="K29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="L19" s="36" t="str">
+      <x:c r="L29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="M19" s="36" t="str">
+      <x:c r="M29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="N19" s="36" t="str">
+      <x:c r="N29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
-      <x:c r="O19" s="36" t="str">
+      <x:c r="O29" s="36" t="str">
         <x:v>Preguntas de control antes de comprar</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="77" t="str">
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="str">
+      <x:c r="B30" s="33" t="str">
         <x:v>¿Puedo explicar cómo gana dinero en dos frases y qué variable mueve el beneficio?</x:v>
       </x:c>
-      <x:c r="C20" s="33" t="str"/>
-      <x:c r="D20" s="33" t="str"/>
-      <x:c r="E20" s="33" t="str"/>
-      <x:c r="F20" s="33" t="str"/>
-      <x:c r="G20" s="33" t="str"/>
-      <x:c r="H20" s="33" t="str"/>
-      <x:c r="I20" s="33" t="str"/>
-      <x:c r="J20" s="33" t="str"/>
-      <x:c r="K20" s="33" t="str"/>
-      <x:c r="L20" s="33" t="str"/>
-      <x:c r="M20" s="33" t="str"/>
-      <x:c r="N20" s="33" t="str"/>
-      <x:c r="O20" s="33" t="str"/>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="77" t="str">
+      <x:c r="C30" s="33" t="str"/>
+      <x:c r="D30" s="33" t="str"/>
+      <x:c r="E30" s="33" t="str"/>
+      <x:c r="F30" s="33" t="str"/>
+      <x:c r="G30" s="33" t="str"/>
+      <x:c r="H30" s="33" t="str"/>
+      <x:c r="I30" s="33" t="str"/>
+      <x:c r="J30" s="33" t="str"/>
+      <x:c r="K30" s="33" t="str"/>
+      <x:c r="L30" s="33" t="str"/>
+      <x:c r="M30" s="33" t="str"/>
+      <x:c r="N30" s="33" t="str"/>
+      <x:c r="O30" s="33" t="str"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="105" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="str">
+      <x:c r="B31" s="33" t="str">
         <x:v>¿La tesis depende de un catalizador identificable o solo de que el múltiplo se expanda?</x:v>
       </x:c>
-      <x:c r="C21" s="33" t="str"/>
-      <x:c r="D21" s="33" t="str"/>
-      <x:c r="E21" s="33" t="str"/>
-      <x:c r="F21" s="33" t="str"/>
-      <x:c r="G21" s="33" t="str"/>
-      <x:c r="H21" s="33" t="str"/>
-      <x:c r="I21" s="33" t="str"/>
-      <x:c r="J21" s="33" t="str"/>
-      <x:c r="K21" s="33" t="str"/>
-      <x:c r="L21" s="33" t="str"/>
-      <x:c r="M21" s="33" t="str"/>
-      <x:c r="N21" s="33" t="str"/>
-      <x:c r="O21" s="33" t="str"/>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="77" t="str">
+      <x:c r="C31" s="33" t="str"/>
+      <x:c r="D31" s="33" t="str"/>
+      <x:c r="E31" s="33" t="str"/>
+      <x:c r="F31" s="33" t="str"/>
+      <x:c r="G31" s="33" t="str"/>
+      <x:c r="H31" s="33" t="str"/>
+      <x:c r="I31" s="33" t="str"/>
+      <x:c r="J31" s="33" t="str"/>
+      <x:c r="K31" s="33" t="str"/>
+      <x:c r="L31" s="33" t="str"/>
+      <x:c r="M31" s="33" t="str"/>
+      <x:c r="N31" s="33" t="str"/>
+      <x:c r="O31" s="33" t="str"/>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="105" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="str">
+      <x:c r="B32" s="33" t="str">
         <x:v>¿El crecimiento llega a beneficio y caja, o solo a ingresos / métricas ajustadas?</x:v>
       </x:c>
-      <x:c r="C22" s="33" t="str"/>
-      <x:c r="D22" s="33" t="str"/>
-      <x:c r="E22" s="33" t="str"/>
-      <x:c r="F22" s="33" t="str"/>
-      <x:c r="G22" s="33" t="str"/>
-      <x:c r="H22" s="33" t="str"/>
-      <x:c r="I22" s="33" t="str"/>
-      <x:c r="J22" s="33" t="str"/>
-      <x:c r="K22" s="33" t="str"/>
-      <x:c r="L22" s="33" t="str"/>
-      <x:c r="M22" s="33" t="str"/>
-      <x:c r="N22" s="33" t="str"/>
-      <x:c r="O22" s="33" t="str"/>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="77" t="str">
+      <x:c r="C32" s="33" t="str"/>
+      <x:c r="D32" s="33" t="str"/>
+      <x:c r="E32" s="33" t="str"/>
+      <x:c r="F32" s="33" t="str"/>
+      <x:c r="G32" s="33" t="str"/>
+      <x:c r="H32" s="33" t="str"/>
+      <x:c r="I32" s="33" t="str"/>
+      <x:c r="J32" s="33" t="str"/>
+      <x:c r="K32" s="33" t="str"/>
+      <x:c r="L32" s="33" t="str"/>
+      <x:c r="M32" s="33" t="str"/>
+      <x:c r="N32" s="33" t="str"/>
+      <x:c r="O32" s="33" t="str"/>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="105" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="str">
+      <x:c r="B33" s="33" t="str">
         <x:v>¿Qué PER pagaría por beneficios normalizados y qué precio ofrece margen de seguridad?</x:v>
       </x:c>
-      <x:c r="C23" s="33" t="str"/>
-      <x:c r="D23" s="33" t="str"/>
-      <x:c r="E23" s="33" t="str"/>
-      <x:c r="F23" s="33" t="str"/>
-      <x:c r="G23" s="33" t="str"/>
-      <x:c r="H23" s="33" t="str"/>
-      <x:c r="I23" s="33" t="str"/>
-      <x:c r="J23" s="33" t="str"/>
-      <x:c r="K23" s="33" t="str"/>
-      <x:c r="L23" s="33" t="str"/>
-      <x:c r="M23" s="33" t="str"/>
-      <x:c r="N23" s="33" t="str"/>
-      <x:c r="O23" s="33" t="str"/>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="77" t="str">
+      <x:c r="C33" s="33" t="str"/>
+      <x:c r="D33" s="33" t="str"/>
+      <x:c r="E33" s="33" t="str"/>
+      <x:c r="F33" s="33" t="str"/>
+      <x:c r="G33" s="33" t="str"/>
+      <x:c r="H33" s="33" t="str"/>
+      <x:c r="I33" s="33" t="str"/>
+      <x:c r="J33" s="33" t="str"/>
+      <x:c r="K33" s="33" t="str"/>
+      <x:c r="L33" s="33" t="str"/>
+      <x:c r="M33" s="33" t="str"/>
+      <x:c r="N33" s="33" t="str"/>
+      <x:c r="O33" s="33" t="str"/>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="105" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="str">
+      <x:c r="B34" s="33" t="str">
         <x:v>¿Qué dato invalidaría la tesis? Escríbelo antes de comprar.</x:v>
       </x:c>
-      <x:c r="C24" s="33" t="str"/>
-      <x:c r="D24" s="33" t="str"/>
-      <x:c r="E24" s="33" t="str"/>
-      <x:c r="F24" s="33" t="str"/>
-      <x:c r="G24" s="33" t="str"/>
-      <x:c r="H24" s="33" t="str"/>
-      <x:c r="I24" s="33" t="str"/>
-      <x:c r="J24" s="33" t="str"/>
-      <x:c r="K24" s="33" t="str"/>
-      <x:c r="L24" s="33" t="str"/>
-      <x:c r="M24" s="33" t="str"/>
-      <x:c r="N24" s="33" t="str"/>
-      <x:c r="O24" s="33" t="str"/>
-    </x:row>
-    <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="77" t="str">
+      <x:c r="C34" s="33" t="str"/>
+      <x:c r="D34" s="33" t="str"/>
+      <x:c r="E34" s="33" t="str"/>
+      <x:c r="F34" s="33" t="str"/>
+      <x:c r="G34" s="33" t="str"/>
+      <x:c r="H34" s="33" t="str"/>
+      <x:c r="I34" s="33" t="str"/>
+      <x:c r="J34" s="33" t="str"/>
+      <x:c r="K34" s="33" t="str"/>
+      <x:c r="L34" s="33" t="str"/>
+      <x:c r="M34" s="33" t="str"/>
+      <x:c r="N34" s="33" t="str"/>
+      <x:c r="O34" s="33" t="str"/>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="105" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="str">
+      <x:c r="B35" s="33" t="str">
         <x:v>¿He leído el último informe, las notas de deuda/dilución y la remuneración directiva?</x:v>
       </x:c>
-      <x:c r="C25" s="33" t="str"/>
-      <x:c r="D25" s="33" t="str"/>
-      <x:c r="E25" s="33" t="str"/>
-      <x:c r="F25" s="33" t="str"/>
-      <x:c r="G25" s="33" t="str"/>
-      <x:c r="H25" s="33" t="str"/>
-      <x:c r="I25" s="33" t="str"/>
-      <x:c r="J25" s="33" t="str"/>
-      <x:c r="K25" s="33" t="str"/>
-      <x:c r="L25" s="33" t="str"/>
-      <x:c r="M25" s="33" t="str"/>
-      <x:c r="N25" s="33" t="str"/>
-      <x:c r="O25" s="33" t="str"/>
+      <x:c r="C35" s="33" t="str"/>
+      <x:c r="D35" s="33" t="str"/>
+      <x:c r="E35" s="33" t="str"/>
+      <x:c r="F35" s="33" t="str"/>
+      <x:c r="G35" s="33" t="str"/>
+      <x:c r="H35" s="33" t="str"/>
+      <x:c r="I35" s="33" t="str"/>
+      <x:c r="J35" s="33" t="str"/>
+      <x:c r="K35" s="33" t="str"/>
+      <x:c r="L35" s="33" t="str"/>
+      <x:c r="M35" s="33" t="str"/>
+      <x:c r="N35" s="33" t="str"/>
+      <x:c r="O35" s="33" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:O1"/>
     <x:mergeCell ref="A2:O2"/>
-    <x:mergeCell ref="A19:O19"/>
-    <x:mergeCell ref="B20:O20"/>
-    <x:mergeCell ref="B21:O21"/>
-    <x:mergeCell ref="B22:O22"/>
-    <x:mergeCell ref="B23:O23"/>
-    <x:mergeCell ref="B24:O24"/>
-    <x:mergeCell ref="B25:O25"/>
+    <x:mergeCell ref="A29:O29"/>
+    <x:mergeCell ref="B30:O30"/>
+    <x:mergeCell ref="B31:O31"/>
+    <x:mergeCell ref="B32:O32"/>
+    <x:mergeCell ref="B33:O33"/>
+    <x:mergeCell ref="B34:O34"/>
+    <x:mergeCell ref="B35:O35"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:M16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThanOrEqual">
+  <x:conditionalFormatting sqref="A5:M26">
+    <x:cfRule type="cellIs" dxfId="8" priority="1" operator="greaterThanOrEqual">
       <x:formula>12</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
-    <x:dataValidation operator="between" sqref="C5:K16">
+    <x:dataValidation operator="between" sqref="C5:K26">
       <x:formula1>0</x:formula1>
       <x:formula2>2</x:formula2>
     </x:dataValidation>
-    <x:dataValidation operator="between" sqref="H5:I16">
+    <x:dataValidation operator="between" sqref="H5:I26">
       <x:formula1>0</x:formula1>
       <x:formula2>1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cbffa00cde14c20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0b91c6df3204c81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5266,24 +10349,478 @@
         <x:v>Trading update; resultados H1 completos el 10-ago-2026</x:v>
       </x:c>
     </x:row>
+    <x:row r="26" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A26" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="B26" s="58" t="str">
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="C26" s="58" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="D26" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E26" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F26" s="61" t="n">
+        <x:v>425.1</x:v>
+      </x:c>
+      <x:c r="G26" s="63" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="H26" s="61" t="n">
+        <x:v>297.7</x:v>
+      </x:c>
+      <x:c r="I26" s="63" t="n">
+        <x:v>0.09</x:v>
+      </x:c>
+      <x:c r="J26" s="61"/>
+      <x:c r="K26" s="61" t="n">
+        <x:v>0.281</x:v>
+      </x:c>
+      <x:c r="L26" s="61"/>
+      <x:c r="M26" s="61" t="n">
+        <x:v>-29.6</x:v>
+      </x:c>
+      <x:c r="N26" s="58" t="str">
+        <x:v>Membresía ~+1%; ARPA y áreas de crecimiento estratégico</x:v>
+      </x:c>
+      <x:c r="O26" s="58" t="str">
+        <x:v>RMV-FY25</x:v>
+      </x:c>
+      <x:c r="P26" s="58" t="str">
+        <x:v>Beneficio operativo subyacente; revisar caja neta en el informe anual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="132" hidden="0" customHeight="1">
+      <x:c r="A27" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="B27" s="58" t="str">
+        <x:v>GAW</x:v>
+      </x:c>
+      <x:c r="C27" s="58" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="D27" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E27" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F27" s="61" t="n">
+        <x:v>659.7</x:v>
+      </x:c>
+      <x:c r="G27" s="63" t="n">
+        <x:v>0.068</x:v>
+      </x:c>
+      <x:c r="H27" s="61" t="n">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="I27" s="63" t="n">
+        <x:v>0.052</x:v>
+      </x:c>
+      <x:c r="J27" s="61"/>
+      <x:c r="K27" s="61" t="n">
+        <x:v>6.24</x:v>
+      </x:c>
+      <x:c r="L27" s="61" t="n">
+        <x:v>210.3</x:v>
+      </x:c>
+      <x:c r="M27" s="61"/>
+      <x:c r="N27" s="58" t="str">
+        <x:v>Core revenue 626.8m; licensing 32.9m; balance sin deuda</x:v>
+      </x:c>
+      <x:c r="O27" s="58" t="str">
+        <x:v>GAW-FY26</x:v>
+      </x:c>
+      <x:c r="P27" s="58" t="str">
+        <x:v>Caja aumentó 210.3m antes de dividendos; no sustituye a FCF comparable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A28" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="B28" s="58" t="str">
+        <x:v>CCC</x:v>
+      </x:c>
+      <x:c r="C28" s="58" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="D28" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E28" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F28" s="61" t="n">
+        <x:v>9193.9</x:v>
+      </x:c>
+      <x:c r="G28" s="63" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="H28" s="61" t="n">
+        <x:v>274.7</x:v>
+      </x:c>
+      <x:c r="I28" s="63" t="n">
+        <x:v>0.113</x:v>
+      </x:c>
+      <x:c r="J28" s="61"/>
+      <x:c r="K28" s="61" t="n">
+        <x:v>1.751</x:v>
+      </x:c>
+      <x:c r="L28" s="61"/>
+      <x:c r="M28" s="61" t="n">
+        <x:v>-606</x:v>
+      </x:c>
+      <x:c r="N28" s="58" t="str">
+        <x:v>Technology Sourcing +40.9%; Managed Services -2.4% CC</x:v>
+      </x:c>
+      <x:c r="O28" s="58" t="str">
+        <x:v>CCC-FY25</x:v>
+      </x:c>
+      <x:c r="P28" s="58" t="str">
+        <x:v>Cifras ajustadas; net funds no es FCF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A29" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="B29" s="58" t="str">
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="C29" s="58" t="str">
+        <x:v>H1 2026</x:v>
+      </x:c>
+      <x:c r="D29" s="58" t="str">
+        <x:v>Semestral</x:v>
+      </x:c>
+      <x:c r="E29" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F29" s="61" t="n">
+        <x:v>1030.6</x:v>
+      </x:c>
+      <x:c r="G29" s="63" t="n">
+        <x:v>0.033</x:v>
+      </x:c>
+      <x:c r="H29" s="61" t="n">
+        <x:v>128.1</x:v>
+      </x:c>
+      <x:c r="I29" s="63" t="n">
+        <x:v>0.055</x:v>
+      </x:c>
+      <x:c r="J29" s="61"/>
+      <x:c r="K29" s="61" t="n">
+        <x:v>0.173</x:v>
+      </x:c>
+      <x:c r="L29" s="61"/>
+      <x:c r="M29" s="61" t="n">
+        <x:v>-332.8</x:v>
+      </x:c>
+      <x:c r="N29" s="58" t="str">
+        <x:v>Margen bruto 62.8%; ventas ajustadas +3.7%</x:v>
+      </x:c>
+      <x:c r="O29" s="58" t="str">
+        <x:v>HWDN-H1-26</x:v>
+      </x:c>
+      <x:c r="P29" s="58" t="str">
+        <x:v>Cifras subyacentes; caja al cierre de semestre</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="132" hidden="0" customHeight="1">
+      <x:c r="A30" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="B30" s="58" t="str">
+        <x:v>DOM</x:v>
+      </x:c>
+      <x:c r="C30" s="58" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="D30" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E30" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F30" s="61" t="n">
+        <x:v>685.4</x:v>
+      </x:c>
+      <x:c r="G30" s="63" t="n">
+        <x:v>0.031</x:v>
+      </x:c>
+      <x:c r="H30" s="61" t="n">
+        <x:v>133.9</x:v>
+      </x:c>
+      <x:c r="I30" s="63" t="n">
+        <x:v>-0.066</x:v>
+      </x:c>
+      <x:c r="J30" s="61"/>
+      <x:c r="K30" s="61" t="n">
+        <x:v>0.176</x:v>
+      </x:c>
+      <x:c r="L30" s="61"/>
+      <x:c r="M30" s="61"/>
+      <x:c r="N30" s="58" t="str">
+        <x:v>System sales 1,595.6m +1.5%; primeras 9 semanas de 2026 positivas</x:v>
+      </x:c>
+      <x:c r="O30" s="58" t="str">
+        <x:v>DOM-FY25</x:v>
+      </x:c>
+      <x:c r="P30" s="58" t="str">
+        <x:v>El beneficio operativo usa EBITDA subyacente; H1 se publica el 04-ago-2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="132" hidden="0" customHeight="1">
+      <x:c r="A31" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="B31" s="58" t="str">
+        <x:v>BWY</x:v>
+      </x:c>
+      <x:c r="C31" s="58" t="str">
+        <x:v>FY2026 guía</x:v>
+      </x:c>
+      <x:c r="D31" s="58" t="str">
+        <x:v>Guía</x:v>
+      </x:c>
+      <x:c r="E31" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F31" s="61"/>
+      <x:c r="G31" s="63"/>
+      <x:c r="H31" s="61" t="n">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="I31" s="63"/>
+      <x:c r="J31" s="61"/>
+      <x:c r="K31" s="61" t="n">
+        <x:v>1.328</x:v>
+      </x:c>
+      <x:c r="L31" s="61"/>
+      <x:c r="M31" s="61" t="n">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="N31" s="58" t="str">
+        <x:v>Orderbook 5,345 viviendas / 1,570m; volumen guiado 9,300–9,500</x:v>
+      </x:c>
+      <x:c r="O31" s="58" t="str">
+        <x:v>BWY-TRD</x:v>
+      </x:c>
+      <x:c r="P31" s="58" t="str">
+        <x:v>Guía de beneficio operativo, no resultado cerrado; deuda neta al 29-may-2026</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A32" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="B32" s="58" t="str">
+        <x:v>BAB</x:v>
+      </x:c>
+      <x:c r="C32" s="58" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="D32" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E32" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F32" s="61" t="n">
+        <x:v>5273</x:v>
+      </x:c>
+      <x:c r="G32" s="63" t="n">
+        <x:v>0.091</x:v>
+      </x:c>
+      <x:c r="H32" s="61" t="n">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="I32" s="63" t="n">
+        <x:v>0.192</x:v>
+      </x:c>
+      <x:c r="J32" s="61"/>
+      <x:c r="K32" s="61" t="n">
+        <x:v>0.605</x:v>
+      </x:c>
+      <x:c r="L32" s="61" t="n">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="M32" s="61" t="n">
+        <x:v>-23</x:v>
+      </x:c>
+      <x:c r="N32" s="58" t="str">
+        <x:v>Backlog 9.8bn; FCF 262m; recompra FY27 200m</x:v>
+      </x:c>
+      <x:c r="O32" s="58" t="str">
+        <x:v>BAB-FY26</x:v>
+      </x:c>
+      <x:c r="P32" s="58" t="str">
+        <x:v>Métricas subyacentes; Type 31 produjo un cargo extraordinario</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="132" hidden="0" customHeight="1">
+      <x:c r="A33" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="B33" s="58" t="str">
+        <x:v>OXIG</x:v>
+      </x:c>
+      <x:c r="C33" s="58" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="D33" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E33" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F33" s="61" t="n">
+        <x:v>423.2</x:v>
+      </x:c>
+      <x:c r="G33" s="63" t="n">
+        <x:v>-0.046</x:v>
+      </x:c>
+      <x:c r="H33" s="61" t="n">
+        <x:v>73.7</x:v>
+      </x:c>
+      <x:c r="I33" s="63" t="n">
+        <x:v>-0.073</x:v>
+      </x:c>
+      <x:c r="J33" s="61"/>
+      <x:c r="K33" s="61" t="n">
+        <x:v>1.007</x:v>
+      </x:c>
+      <x:c r="L33" s="61"/>
+      <x:c r="M33" s="61" t="n">
+        <x:v>-94</x:v>
+      </x:c>
+      <x:c r="N33" s="58" t="str">
+        <x:v>Order intake 450.4m +6.4%; book-to-bill 1.067</x:v>
+      </x:c>
+      <x:c r="O33" s="58" t="str">
+        <x:v>OXIG-FY26</x:v>
+      </x:c>
+      <x:c r="P33" s="58" t="str">
+        <x:v>Margen y EPS ajustados; el beneficio reportado creció por efecto comparativo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="132" hidden="0" customHeight="1">
+      <x:c r="A34" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="B34" s="58" t="str">
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="C34" s="58" t="str">
+        <x:v>FY2025</x:v>
+      </x:c>
+      <x:c r="D34" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E34" s="58" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="F34" s="61" t="n">
+        <x:v>1346.8</x:v>
+      </x:c>
+      <x:c r="G34" s="63" t="n">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="H34" s="61" t="n">
+        <x:v>145.2</x:v>
+      </x:c>
+      <x:c r="I34" s="63" t="n">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="J34" s="61"/>
+      <x:c r="K34" s="61" t="n">
+        <x:v>4.044</x:v>
+      </x:c>
+      <x:c r="L34" s="61"/>
+      <x:c r="M34" s="61" t="n">
+        <x:v>-132.8</x:v>
+      </x:c>
+      <x:c r="N34" s="58" t="str">
+        <x:v>Pedidos 2.06m -3%; pedidos de clientes existentes planos; nuevos -12%</x:v>
+      </x:c>
+      <x:c r="O34" s="58" t="str">
+        <x:v>FOUR-FY25</x:v>
+      </x:c>
+      <x:c r="P34" s="58" t="str">
+        <x:v>Cifras de resultados en USD; cotización/dividendo de la watchlist en GBX</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A35" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="B35" s="58" t="str">
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="C35" s="58" t="str">
+        <x:v>FY2026</x:v>
+      </x:c>
+      <x:c r="D35" s="58" t="str">
+        <x:v>Anual</x:v>
+      </x:c>
+      <x:c r="E35" s="58" t="str">
+        <x:v>GBP</x:v>
+      </x:c>
+      <x:c r="F35" s="61" t="n">
+        <x:v>7482.1</x:v>
+      </x:c>
+      <x:c r="G35" s="63" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="H35" s="61" t="n">
+        <x:v>439.6</x:v>
+      </x:c>
+      <x:c r="I35" s="63" t="n">
+        <x:v>-0.02</x:v>
+      </x:c>
+      <x:c r="J35" s="61"/>
+      <x:c r="K35" s="61" t="n">
+        <x:v>2.112</x:v>
+      </x:c>
+      <x:c r="L35" s="61"/>
+      <x:c r="M35" s="61" t="n">
+        <x:v>-2012.9</x:v>
+      </x:c>
+      <x:c r="N35" s="58" t="str">
+        <x:v>Pasajeros 20.83m +5%; capacidad verano 2026 +7.7%</x:v>
+      </x:c>
+      <x:c r="O35" s="58" t="str">
+        <x:v>JET2-FY26</x:v>
+      </x:c>
+      <x:c r="P35" s="58" t="str">
+        <x:v>Caja neta; resultado sensible a combustible, divisa y calendario</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:P1"/>
     <x:mergeCell ref="A2:P2"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="G5:I25">
-    <x:cfRule type="cellIs" dxfId="3" priority="1" operator="lessThan">
+  <x:conditionalFormatting sqref="G5:I35">
+    <x:cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc31271e200f643f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R81f6902fefa44220"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -5496,10 +11033,10 @@
       <x:c r="D13" s="35" t="str">
         <x:v>¿Qué hace?</x:v>
       </x:c>
-      <x:c r="E13" s="96" t="str"/>
-      <x:c r="F13" s="96" t="str"/>
-      <x:c r="G13" s="96" t="str"/>
-      <x:c r="H13" s="96" t="str"/>
+      <x:c r="E13" s="122" t="str"/>
+      <x:c r="F13" s="122" t="str"/>
+      <x:c r="G13" s="122" t="str"/>
+      <x:c r="H13" s="122" t="str"/>
     </x:row>
     <x:row r="14" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A14" s="35" t="str">
@@ -5510,26 +11047,26 @@
       <x:c r="D14" s="35" t="str">
         <x:v>¿Por qué puede crecer?</x:v>
       </x:c>
-      <x:c r="E14" s="96" t="str"/>
-      <x:c r="F14" s="96" t="str"/>
-      <x:c r="G14" s="96" t="str"/>
-      <x:c r="H14" s="96" t="str"/>
+      <x:c r="E14" s="122" t="str"/>
+      <x:c r="F14" s="122" t="str"/>
+      <x:c r="G14" s="122" t="str"/>
+      <x:c r="H14" s="122" t="str"/>
     </x:row>
     <x:row r="15" ht="52.79999923706055" hidden="0" customHeight="1">
       <x:c r="A15" s="35" t="str">
         <x:v>PER calculado</x:v>
       </x:c>
-      <x:c r="B15" s="97" t="str">
+      <x:c r="B15" s="71" t="str">
         <x:f>IFERROR(B13/B14,"")</x:f>
       </x:c>
       <x:c r="C15" s="33"/>
       <x:c r="D15" s="35" t="str">
         <x:v>¿Cuál es el catalizador?</x:v>
       </x:c>
-      <x:c r="E15" s="96" t="str"/>
-      <x:c r="F15" s="96" t="str"/>
-      <x:c r="G15" s="96" t="str"/>
-      <x:c r="H15" s="96" t="str"/>
+      <x:c r="E15" s="122" t="str"/>
+      <x:c r="F15" s="122" t="str"/>
+      <x:c r="G15" s="122" t="str"/>
+      <x:c r="H15" s="122" t="str"/>
     </x:row>
     <x:row r="16" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A16" s="35" t="str">
@@ -5540,10 +11077,10 @@
       <x:c r="D16" s="35" t="str">
         <x:v>¿Qué puede salir mal?</x:v>
       </x:c>
-      <x:c r="E16" s="96" t="str"/>
-      <x:c r="F16" s="96" t="str"/>
-      <x:c r="G16" s="96" t="str"/>
-      <x:c r="H16" s="96" t="str"/>
+      <x:c r="E16" s="122" t="str"/>
+      <x:c r="F16" s="122" t="str"/>
+      <x:c r="G16" s="122" t="str"/>
+      <x:c r="H16" s="122" t="str"/>
     </x:row>
     <x:row r="17" ht="66" hidden="0" customHeight="1">
       <x:c r="A17" s="35" t="str">
@@ -5556,10 +11093,10 @@
       <x:c r="D17" s="35" t="str">
         <x:v>¿Qué precio sería razonable?</x:v>
       </x:c>
-      <x:c r="E17" s="96" t="str"/>
-      <x:c r="F17" s="96" t="str"/>
-      <x:c r="G17" s="96" t="str"/>
-      <x:c r="H17" s="96" t="str"/>
+      <x:c r="E17" s="122" t="str"/>
+      <x:c r="F17" s="122" t="str"/>
+      <x:c r="G17" s="122" t="str"/>
+      <x:c r="H17" s="122" t="str"/>
     </x:row>
     <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" s="35" t="str">
@@ -5570,10 +11107,10 @@
       <x:c r="D18" s="35" t="str">
         <x:v>¿Qué dato invalida la tesis?</x:v>
       </x:c>
-      <x:c r="E18" s="96" t="str"/>
-      <x:c r="F18" s="96" t="str"/>
-      <x:c r="G18" s="96" t="str"/>
-      <x:c r="H18" s="96" t="str"/>
+      <x:c r="E18" s="122" t="str"/>
+      <x:c r="F18" s="122" t="str"/>
+      <x:c r="G18" s="122" t="str"/>
+      <x:c r="H18" s="122" t="str"/>
     </x:row>
     <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A19" s="35" t="str">
@@ -5584,26 +11121,26 @@
       <x:c r="D19" s="35" t="str">
         <x:v>¿Qué dice la dirección?</x:v>
       </x:c>
-      <x:c r="E19" s="96" t="str"/>
-      <x:c r="F19" s="96" t="str"/>
-      <x:c r="G19" s="96" t="str"/>
-      <x:c r="H19" s="96" t="str"/>
+      <x:c r="E19" s="122" t="str"/>
+      <x:c r="F19" s="122" t="str"/>
+      <x:c r="G19" s="122" t="str"/>
+      <x:c r="H19" s="122" t="str"/>
     </x:row>
     <x:row r="20" ht="66" hidden="0" customHeight="1">
       <x:c r="A20" s="35" t="str">
         <x:v>FCF yield</x:v>
       </x:c>
-      <x:c r="B20" s="98" t="str">
+      <x:c r="B20" s="72" t="str">
         <x:f>IFERROR(B18/B19,"")</x:f>
       </x:c>
       <x:c r="C20" s="33"/>
       <x:c r="D20" s="35" t="str">
         <x:v>¿Qué dicen insiders/accionistas?</x:v>
       </x:c>
-      <x:c r="E20" s="96" t="str"/>
-      <x:c r="F20" s="96" t="str"/>
-      <x:c r="G20" s="96" t="str"/>
-      <x:c r="H20" s="96" t="str"/>
+      <x:c r="E20" s="122" t="str"/>
+      <x:c r="F20" s="122" t="str"/>
+      <x:c r="G20" s="122" t="str"/>
+      <x:c r="H20" s="122" t="str"/>
     </x:row>
     <x:row r="21" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A21" s="35" t="str">
@@ -5614,10 +11151,10 @@
       <x:c r="D21" s="35" t="str">
         <x:v>Próxima revisión</x:v>
       </x:c>
-      <x:c r="E21" s="99" t="str"/>
-      <x:c r="F21" s="96" t="str"/>
-      <x:c r="G21" s="96" t="str"/>
-      <x:c r="H21" s="96" t="str"/>
+      <x:c r="E21" s="123" t="str"/>
+      <x:c r="F21" s="122" t="str"/>
+      <x:c r="G21" s="122" t="str"/>
+      <x:c r="H21" s="122" t="str"/>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="33"/>
@@ -5685,73 +11222,73 @@
       <x:c r="A26" s="58" t="str">
         <x:v>Negocio comprensible</x:v>
       </x:c>
-      <x:c r="B26" s="75" t="str"/>
-      <x:c r="C26" s="100" t="str"/>
-      <x:c r="D26" s="100" t="str"/>
-      <x:c r="E26" s="100" t="str"/>
-      <x:c r="F26" s="100" t="str"/>
-      <x:c r="G26" s="100" t="str"/>
-      <x:c r="H26" s="100" t="str"/>
+      <x:c r="B26" s="104" t="str"/>
+      <x:c r="C26" s="124" t="str"/>
+      <x:c r="D26" s="124" t="str"/>
+      <x:c r="E26" s="124" t="str"/>
+      <x:c r="F26" s="124" t="str"/>
+      <x:c r="G26" s="124" t="str"/>
+      <x:c r="H26" s="124" t="str"/>
     </x:row>
     <x:row r="27" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A27" s="58" t="str">
         <x:v>Historia / catalizador</x:v>
       </x:c>
-      <x:c r="B27" s="75" t="str"/>
-      <x:c r="C27" s="100" t="str"/>
-      <x:c r="D27" s="100" t="str"/>
-      <x:c r="E27" s="100" t="str"/>
-      <x:c r="F27" s="100" t="str"/>
-      <x:c r="G27" s="100" t="str"/>
-      <x:c r="H27" s="100"/>
+      <x:c r="B27" s="104" t="str"/>
+      <x:c r="C27" s="124" t="str"/>
+      <x:c r="D27" s="124" t="str"/>
+      <x:c r="E27" s="124" t="str"/>
+      <x:c r="F27" s="124" t="str"/>
+      <x:c r="G27" s="124" t="str"/>
+      <x:c r="H27" s="124"/>
     </x:row>
     <x:row r="28" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A28" s="58" t="str">
         <x:v>Crecimiento</x:v>
       </x:c>
-      <x:c r="B28" s="75" t="str"/>
-      <x:c r="C28" s="100" t="str"/>
-      <x:c r="D28" s="100" t="str"/>
-      <x:c r="E28" s="100" t="str"/>
-      <x:c r="F28" s="100" t="str"/>
-      <x:c r="G28" s="100" t="str"/>
-      <x:c r="H28" s="100"/>
+      <x:c r="B28" s="104" t="str"/>
+      <x:c r="C28" s="124" t="str"/>
+      <x:c r="D28" s="124" t="str"/>
+      <x:c r="E28" s="124" t="str"/>
+      <x:c r="F28" s="124" t="str"/>
+      <x:c r="G28" s="124" t="str"/>
+      <x:c r="H28" s="124"/>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="58" t="str">
         <x:v>Valoración</x:v>
       </x:c>
-      <x:c r="B29" s="75" t="str"/>
-      <x:c r="C29" s="100" t="str"/>
-      <x:c r="D29" s="100" t="str"/>
-      <x:c r="E29" s="100" t="str"/>
-      <x:c r="F29" s="100" t="str"/>
-      <x:c r="G29" s="100" t="str"/>
-      <x:c r="H29" s="100"/>
+      <x:c r="B29" s="104" t="str"/>
+      <x:c r="C29" s="124" t="str"/>
+      <x:c r="D29" s="124" t="str"/>
+      <x:c r="E29" s="124" t="str"/>
+      <x:c r="F29" s="124" t="str"/>
+      <x:c r="G29" s="124" t="str"/>
+      <x:c r="H29" s="124"/>
     </x:row>
     <x:row r="30" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A30" s="58" t="str">
         <x:v>Balance / caja</x:v>
       </x:c>
-      <x:c r="B30" s="75" t="str"/>
-      <x:c r="C30" s="100" t="str"/>
-      <x:c r="D30" s="100" t="str"/>
-      <x:c r="E30" s="100" t="str"/>
-      <x:c r="F30" s="100" t="str"/>
-      <x:c r="G30" s="100" t="str"/>
-      <x:c r="H30" s="100"/>
+      <x:c r="B30" s="104" t="str"/>
+      <x:c r="C30" s="124" t="str"/>
+      <x:c r="D30" s="124" t="str"/>
+      <x:c r="E30" s="124" t="str"/>
+      <x:c r="F30" s="124" t="str"/>
+      <x:c r="G30" s="124" t="str"/>
+      <x:c r="H30" s="124"/>
     </x:row>
     <x:row r="31" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A31" s="58" t="str">
         <x:v>Riesgos manejables</x:v>
       </x:c>
-      <x:c r="B31" s="75" t="str"/>
-      <x:c r="C31" s="100" t="str"/>
-      <x:c r="D31" s="100" t="str"/>
-      <x:c r="E31" s="100" t="str"/>
-      <x:c r="F31" s="100" t="str"/>
-      <x:c r="G31" s="100" t="str"/>
-      <x:c r="H31" s="100"/>
+      <x:c r="B31" s="104" t="str"/>
+      <x:c r="C31" s="124" t="str"/>
+      <x:c r="D31" s="124" t="str"/>
+      <x:c r="E31" s="124" t="str"/>
+      <x:c r="F31" s="124" t="str"/>
+      <x:c r="G31" s="124" t="str"/>
+      <x:c r="H31" s="124"/>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="33"/>
@@ -5844,186 +11381,186 @@
       <x:c r="H37" s="20" t="str"/>
     </x:row>
     <x:row r="38" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A38" s="77" t="n">
+      <x:c r="A38" s="105" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B38" s="28" t="str">
         <x:v>Nombre o historia poco glamourosa, fácil de pasar por alto.</x:v>
       </x:c>
-      <x:c r="C38" s="96" t="str"/>
-      <x:c r="D38" s="96" t="str"/>
-      <x:c r="E38" s="96" t="str"/>
-      <x:c r="F38" s="96" t="str"/>
-      <x:c r="G38" s="96" t="str"/>
-      <x:c r="H38" s="96" t="str"/>
+      <x:c r="C38" s="122" t="str"/>
+      <x:c r="D38" s="122" t="str"/>
+      <x:c r="E38" s="122" t="str"/>
+      <x:c r="F38" s="122" t="str"/>
+      <x:c r="G38" s="122" t="str"/>
+      <x:c r="H38" s="122" t="str"/>
     </x:row>
     <x:row r="39" ht="66" hidden="0" customHeight="1">
-      <x:c r="A39" s="77" t="n">
+      <x:c r="A39" s="105" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B39" s="28" t="str">
         <x:v>Hace algo aburrido, rutinario o poco mediático.</x:v>
       </x:c>
-      <x:c r="C39" s="96" t="str"/>
-      <x:c r="D39" s="96" t="str"/>
-      <x:c r="E39" s="96" t="str"/>
-      <x:c r="F39" s="96" t="str"/>
-      <x:c r="G39" s="96" t="str"/>
-      <x:c r="H39" s="96" t="str"/>
+      <x:c r="C39" s="122" t="str"/>
+      <x:c r="D39" s="122" t="str"/>
+      <x:c r="E39" s="122" t="str"/>
+      <x:c r="F39" s="122" t="str"/>
+      <x:c r="G39" s="122" t="str"/>
+      <x:c r="H39" s="122" t="str"/>
     </x:row>
     <x:row r="40" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A40" s="77" t="n">
+      <x:c r="A40" s="105" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B40" s="28" t="str">
         <x:v>Hace algo desagradable que mantiene alejados a los competidores.</x:v>
       </x:c>
-      <x:c r="C40" s="96" t="str"/>
-      <x:c r="D40" s="96" t="str"/>
-      <x:c r="E40" s="96" t="str"/>
-      <x:c r="F40" s="96" t="str"/>
-      <x:c r="G40" s="96" t="str"/>
-      <x:c r="H40" s="96" t="str"/>
+      <x:c r="C40" s="122" t="str"/>
+      <x:c r="D40" s="122" t="str"/>
+      <x:c r="E40" s="122" t="str"/>
+      <x:c r="F40" s="122" t="str"/>
+      <x:c r="G40" s="122" t="str"/>
+      <x:c r="H40" s="122" t="str"/>
     </x:row>
     <x:row r="41" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A41" s="77" t="n">
+      <x:c r="A41" s="105" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B41" s="28" t="str">
         <x:v>Es una escisión reciente o una parte separada de otra empresa.</x:v>
       </x:c>
-      <x:c r="C41" s="96" t="str"/>
-      <x:c r="D41" s="96" t="str"/>
-      <x:c r="E41" s="96" t="str"/>
-      <x:c r="F41" s="96" t="str"/>
-      <x:c r="G41" s="96" t="str"/>
-      <x:c r="H41" s="96" t="str"/>
+      <x:c r="C41" s="122" t="str"/>
+      <x:c r="D41" s="122" t="str"/>
+      <x:c r="E41" s="122" t="str"/>
+      <x:c r="F41" s="122" t="str"/>
+      <x:c r="G41" s="122" t="str"/>
+      <x:c r="H41" s="122" t="str"/>
     </x:row>
     <x:row r="42" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A42" s="77" t="n">
+      <x:c r="A42" s="105" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B42" s="28" t="str">
         <x:v>Tiene poca cobertura institucional o pocos analistas siguiéndola.</x:v>
       </x:c>
-      <x:c r="C42" s="96" t="str"/>
-      <x:c r="D42" s="96" t="str"/>
-      <x:c r="E42" s="96" t="str"/>
-      <x:c r="F42" s="96" t="str"/>
-      <x:c r="G42" s="96" t="str"/>
-      <x:c r="H42" s="96" t="str"/>
+      <x:c r="C42" s="122" t="str"/>
+      <x:c r="D42" s="122" t="str"/>
+      <x:c r="E42" s="122" t="str"/>
+      <x:c r="F42" s="122" t="str"/>
+      <x:c r="G42" s="122" t="str"/>
+      <x:c r="H42" s="122" t="str"/>
     </x:row>
     <x:row r="43" ht="132" hidden="0" customHeight="1">
-      <x:c r="A43" s="77" t="n">
+      <x:c r="A43" s="105" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B43" s="28" t="str">
         <x:v>Arrastra rumores o un estigma que puede mantener baja la valoración.</x:v>
       </x:c>
-      <x:c r="C43" s="96" t="str"/>
-      <x:c r="D43" s="96" t="str"/>
-      <x:c r="E43" s="96" t="str"/>
-      <x:c r="F43" s="96" t="str"/>
-      <x:c r="G43" s="96" t="str"/>
-      <x:c r="H43" s="96" t="str"/>
+      <x:c r="C43" s="122" t="str"/>
+      <x:c r="D43" s="122" t="str"/>
+      <x:c r="E43" s="122" t="str"/>
+      <x:c r="F43" s="122" t="str"/>
+      <x:c r="G43" s="122" t="str"/>
+      <x:c r="H43" s="122" t="str"/>
     </x:row>
     <x:row r="44" ht="92.4000015258789" hidden="0" customHeight="1">
-      <x:c r="A44" s="77" t="n">
+      <x:c r="A44" s="105" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="28" t="str">
         <x:v>Opera en un sector deprimente o impopular, pero necesario.</x:v>
       </x:c>
-      <x:c r="C44" s="96" t="str"/>
-      <x:c r="D44" s="96" t="str"/>
-      <x:c r="E44" s="96" t="str"/>
-      <x:c r="F44" s="96" t="str"/>
-      <x:c r="G44" s="96" t="str"/>
-      <x:c r="H44" s="96" t="str"/>
+      <x:c r="C44" s="122" t="str"/>
+      <x:c r="D44" s="122" t="str"/>
+      <x:c r="E44" s="122" t="str"/>
+      <x:c r="F44" s="122" t="str"/>
+      <x:c r="G44" s="122" t="str"/>
+      <x:c r="H44" s="122" t="str"/>
     </x:row>
     <x:row r="45" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A45" s="77" t="n">
+      <x:c r="A45" s="105" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B45" s="28" t="str">
         <x:v>Está en un sector de poco crecimiento donde aún puede ganar cuota.</x:v>
       </x:c>
-      <x:c r="C45" s="96" t="str"/>
-      <x:c r="D45" s="96" t="str"/>
-      <x:c r="E45" s="96" t="str"/>
-      <x:c r="F45" s="96" t="str"/>
-      <x:c r="G45" s="96" t="str"/>
-      <x:c r="H45" s="96" t="str"/>
+      <x:c r="C45" s="122" t="str"/>
+      <x:c r="D45" s="122" t="str"/>
+      <x:c r="E45" s="122" t="str"/>
+      <x:c r="F45" s="122" t="str"/>
+      <x:c r="G45" s="122" t="str"/>
+      <x:c r="H45" s="122" t="str"/>
     </x:row>
     <x:row r="46" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A46" s="77" t="n">
+      <x:c r="A46" s="105" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B46" s="28" t="str">
         <x:v>Tiene un nicho, franquicia, marca, licencia o ventaja difícil de replicar.</x:v>
       </x:c>
-      <x:c r="C46" s="96" t="str"/>
-      <x:c r="D46" s="96" t="str"/>
-      <x:c r="E46" s="96" t="str"/>
-      <x:c r="F46" s="96" t="str"/>
-      <x:c r="G46" s="96" t="str"/>
-      <x:c r="H46" s="96" t="str"/>
+      <x:c r="C46" s="122" t="str"/>
+      <x:c r="D46" s="122" t="str"/>
+      <x:c r="E46" s="122" t="str"/>
+      <x:c r="F46" s="122" t="str"/>
+      <x:c r="G46" s="122" t="str"/>
+      <x:c r="H46" s="122" t="str"/>
     </x:row>
     <x:row r="47" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A47" s="77" t="n">
+      <x:c r="A47" s="105" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="28" t="str">
         <x:v>El cliente vuelve a comprar el producto/servicio de forma recurrente.</x:v>
       </x:c>
-      <x:c r="C47" s="96" t="str"/>
-      <x:c r="D47" s="96" t="str"/>
-      <x:c r="E47" s="96" t="str"/>
-      <x:c r="F47" s="96" t="str"/>
-      <x:c r="G47" s="96" t="str"/>
-      <x:c r="H47" s="96" t="str"/>
+      <x:c r="C47" s="122" t="str"/>
+      <x:c r="D47" s="122" t="str"/>
+      <x:c r="E47" s="122" t="str"/>
+      <x:c r="F47" s="122" t="str"/>
+      <x:c r="G47" s="122" t="str"/>
+      <x:c r="H47" s="122" t="str"/>
     </x:row>
     <x:row r="48" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A48" s="77" t="n">
+      <x:c r="A48" s="105" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B48" s="28" t="str">
         <x:v>Usa la tecnología para ahorrar costes o mejorar un negocio sencillo.</x:v>
       </x:c>
-      <x:c r="C48" s="96" t="str"/>
-      <x:c r="D48" s="96" t="str"/>
-      <x:c r="E48" s="96" t="str"/>
-      <x:c r="F48" s="96" t="str"/>
-      <x:c r="G48" s="96" t="str"/>
-      <x:c r="H48" s="96" t="str"/>
+      <x:c r="C48" s="122" t="str"/>
+      <x:c r="D48" s="122" t="str"/>
+      <x:c r="E48" s="122" t="str"/>
+      <x:c r="F48" s="122" t="str"/>
+      <x:c r="G48" s="122" t="str"/>
+      <x:c r="H48" s="122" t="str"/>
     </x:row>
     <x:row r="49" ht="118.80000305175781" hidden="0" customHeight="1">
-      <x:c r="A49" s="77" t="n">
+      <x:c r="A49" s="105" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B49" s="28" t="str">
         <x:v>La gente de dentro compra acciones y está alineada con accionistas.</x:v>
       </x:c>
-      <x:c r="C49" s="96" t="str"/>
-      <x:c r="D49" s="96" t="str"/>
-      <x:c r="E49" s="96" t="str"/>
-      <x:c r="F49" s="96" t="str"/>
-      <x:c r="G49" s="96" t="str"/>
-      <x:c r="H49" s="96" t="str"/>
+      <x:c r="C49" s="122" t="str"/>
+      <x:c r="D49" s="122" t="str"/>
+      <x:c r="E49" s="122" t="str"/>
+      <x:c r="F49" s="122" t="str"/>
+      <x:c r="G49" s="122" t="str"/>
+      <x:c r="H49" s="122" t="str"/>
     </x:row>
     <x:row r="50" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A50" s="77" t="n">
+      <x:c r="A50" s="105" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B50" s="28" t="str">
         <x:v>Recompra acciones de forma efectiva y evita la dilución innecesaria.</x:v>
       </x:c>
-      <x:c r="C50" s="96" t="str"/>
-      <x:c r="D50" s="96" t="str"/>
-      <x:c r="E50" s="96" t="str"/>
-      <x:c r="F50" s="96" t="str"/>
-      <x:c r="G50" s="96" t="str"/>
-      <x:c r="H50" s="96" t="str"/>
+      <x:c r="C50" s="122" t="str"/>
+      <x:c r="D50" s="122" t="str"/>
+      <x:c r="E50" s="122" t="str"/>
+      <x:c r="F50" s="122" t="str"/>
+      <x:c r="G50" s="122" t="str"/>
+      <x:c r="H50" s="122" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -6075,7 +11612,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -7316,6 +12853,719 @@
         <x:v>Fecha confirmada por la compañía.</x:v>
       </x:c>
     </x:row>
+    <x:row r="55" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A55" s="58" t="str">
+        <x:v>RMV-MKT</x:v>
+      </x:c>
+      <x:c r="B55" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="C55" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D55" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E55" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F55" s="40" t="str">
+        <x:v>https://www.lse.co.uk/ShareFundamentals.html?share=rightmove&amp;shareprice=RMV</x:v>
+      </x:c>
+      <x:c r="G55" s="58" t="str">
+        <x:v>Snapshot actualizado; el PER 16.90x usa EPS FY25 de 28.10p.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A56" s="58" t="str">
+        <x:v>RMV-FY25</x:v>
+      </x:c>
+      <x:c r="B56" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="C56" s="59" t="n">
+        <x:v>46080</x:v>
+      </x:c>
+      <x:c r="D56" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E56" s="58" t="str">
+        <x:v>FY25 ingresos, beneficio operativo, EPS y guía 2026</x:v>
+      </x:c>
+      <x:c r="F56" s="40" t="str">
+        <x:v>https://plc.rightmove.co.uk/content/uploads/2026/02/Rightmove-RNS-27.02.26.pdf</x:v>
+      </x:c>
+      <x:c r="G56" s="58" t="str">
+        <x:v>Resultados oficiales; H1 2026 publicado el 31-jul-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A57" s="58" t="str">
+        <x:v>RMV-CONS</x:v>
+      </x:c>
+      <x:c r="B57" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="C57" s="59" t="n">
+        <x:v>46230</x:v>
+      </x:c>
+      <x:c r="D57" s="58" t="str">
+        <x:v>Consenso</x:v>
+      </x:c>
+      <x:c r="E57" s="58" t="str">
+        <x:v>Consenso H1/FY26-FY28 de ingresos, EBIT y EPS</x:v>
+      </x:c>
+      <x:c r="F57" s="40" t="str">
+        <x:v>https://plc.rightmove.co.uk/content/uploads/2026/07/Rightmove_Modular-Finance-IR-Consensus.pdf</x:v>
+      </x:c>
+      <x:c r="G57" s="58" t="str">
+        <x:v>Estimaciones sell-side; no son guidance de la compañía.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="66" hidden="0" customHeight="1">
+      <x:c r="A58" s="58" t="str">
+        <x:v>RMV-CAL</x:v>
+      </x:c>
+      <x:c r="B58" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="C58" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D58" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E58" s="58" t="str">
+        <x:v>IR, resultados y trading updates</x:v>
+      </x:c>
+      <x:c r="F58" s="40" t="str">
+        <x:v>https://plc.rightmove.co.uk/</x:v>
+      </x:c>
+      <x:c r="G58" s="58" t="str">
+        <x:v>Confirmar la siguiente fecha tras H1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="132" hidden="0" customHeight="1">
+      <x:c r="A59" s="58" t="str">
+        <x:v>GAW-MKT</x:v>
+      </x:c>
+      <x:c r="B59" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="C59" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D59" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E59" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F59" s="40" t="str">
+        <x:v>https://www.lse.co.uk/ShareFundamentals.html?share=Games-Workshop&amp;shareprice=GAW</x:v>
+      </x:c>
+      <x:c r="G59" s="58" t="str">
+        <x:v>Snapshot de mercado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="198" hidden="0" customHeight="1">
+      <x:c r="A60" s="58" t="str">
+        <x:v>GAW-FY26</x:v>
+      </x:c>
+      <x:c r="B60" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="C60" s="59" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="D60" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E60" s="58" t="str">
+        <x:v>FY26 ingresos, beneficio, EPS, caja y balance</x:v>
+      </x:c>
+      <x:c r="F60" s="40" t="str">
+        <x:v>https://assets.ctfassets.net/ost7hseic9hc/6nI9MLA7hoRBfs2OA1oE5R/a17f82fdef64028ff1f03f03c4dc4cbf/Press_Statement_2025-26_FINAL_v3.pdf</x:v>
+      </x:c>
+      <x:c r="G60" s="58" t="str">
+        <x:v>Press statement oficial; ejercicio terminado el 31-may-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A61" s="58" t="str">
+        <x:v>GAW-CAL</x:v>
+      </x:c>
+      <x:c r="B61" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="C61" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D61" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E61" s="58" t="str">
+        <x:v>Fecha de resultados FY26 y calendario de inversores</x:v>
+      </x:c>
+      <x:c r="F61" s="40" t="str">
+        <x:v>https://investor.games-workshop.com/financial-calendar</x:v>
+      </x:c>
+      <x:c r="G61" s="58" t="str">
+        <x:v>Usar noviembre como revisión tentativa de trading.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A62" s="58" t="str">
+        <x:v>CCC-MKT</x:v>
+      </x:c>
+      <x:c r="B62" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="C62" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D62" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E62" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F62" s="40" t="str">
+        <x:v>https://www.lse.co.uk/SharePrice.html?shareprice=CCC</x:v>
+      </x:c>
+      <x:c r="G62" s="58" t="str">
+        <x:v>Snapshot de mercado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A63" s="58" t="str">
+        <x:v>CCC-FY25</x:v>
+      </x:c>
+      <x:c r="B63" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="C63" s="59" t="n">
+        <x:v>46093</x:v>
+      </x:c>
+      <x:c r="D63" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E63" s="58" t="str">
+        <x:v>FY25 ingresos, beneficio operativo, EPS y net funds</x:v>
+      </x:c>
+      <x:c r="F63" s="40" t="str">
+        <x:v>https://investors.computacenter.com/news-releases/news-release-details/computacenter-final-results-2025</x:v>
+      </x:c>
+      <x:c r="G63" s="58" t="str">
+        <x:v>Resultados oficiales; cifras ajustadas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A64" s="58" t="str">
+        <x:v>CCC-Q1-26</x:v>
+      </x:c>
+      <x:c r="B64" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="C64" s="59" t="n">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="D64" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E64" s="58" t="str">
+        <x:v>Q1 2026, trading, consenso y próximo H1</x:v>
+      </x:c>
+      <x:c r="F64" s="40" t="str">
+        <x:v>https://investors.computacenter.com/node/15316/pdf</x:v>
+      </x:c>
+      <x:c r="G64" s="58" t="str">
+        <x:v>Actualización oficial; H1 el 08-sep-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="132" hidden="0" customHeight="1">
+      <x:c r="A65" s="58" t="str">
+        <x:v>HWDN-MKT</x:v>
+      </x:c>
+      <x:c r="B65" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="C65" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D65" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E65" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F65" s="40" t="str">
+        <x:v>https://www.lse.co.uk/ShareFundamentals.html?share=Howden-Joinery&amp;shareprice=HWDN</x:v>
+      </x:c>
+      <x:c r="G65" s="58" t="str">
+        <x:v>Snapshot actualizado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A66" s="58" t="str">
+        <x:v>HWDN-H1-26</x:v>
+      </x:c>
+      <x:c r="B66" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="C66" s="59" t="n">
+        <x:v>46226</x:v>
+      </x:c>
+      <x:c r="D66" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E66" s="58" t="str">
+        <x:v>H1 2026 ventas, margen, EBIT, EPS y caja</x:v>
+      </x:c>
+      <x:c r="F66" s="40" t="str">
+        <x:v>https://www.lse.co.uk/rns/half-year-report-71qu4k9hnaywgyi.html</x:v>
+      </x:c>
+      <x:c r="G66" s="58" t="str">
+        <x:v>Comunicado oficial distribuido por RNS.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A67" s="58" t="str">
+        <x:v>HWDN-CAL</x:v>
+      </x:c>
+      <x:c r="B67" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="C67" s="59" t="n">
+        <x:v>46079</x:v>
+      </x:c>
+      <x:c r="D67" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E67" s="58" t="str">
+        <x:v>Trading update y resultados H1 2026</x:v>
+      </x:c>
+      <x:c r="F67" s="40" t="str">
+        <x:v>https://www.howdenjoinerygroupplc.com/media-centre/archive/2026/260226.asp</x:v>
+      </x:c>
+      <x:c r="G67" s="58" t="str">
+        <x:v>La compañía señaló trading update el 05-nov-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A68" s="58" t="str">
+        <x:v>DOM-MKT</x:v>
+      </x:c>
+      <x:c r="B68" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="C68" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D68" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E68" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F68" s="40" t="str">
+        <x:v>https://www.lse.co.uk/SharePrice.html?share=DOM&amp;shareprice=DOM</x:v>
+      </x:c>
+      <x:c r="G68" s="58" t="str">
+        <x:v>Snapshot de mercado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A69" s="58" t="str">
+        <x:v>DOM-FY25</x:v>
+      </x:c>
+      <x:c r="B69" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="C69" s="59" t="n">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="D69" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E69" s="58" t="str">
+        <x:v>FY25 ventas, EBITDA, PBT, EPS, dividendo y primeras semanas de 2026</x:v>
+      </x:c>
+      <x:c r="F69" s="40" t="str">
+        <x:v>https://investors.dominos.co.uk/media/news/preliminary-results-52-weeks-ended-28-december-2025</x:v>
+      </x:c>
+      <x:c r="G69" s="58" t="str">
+        <x:v>Resultados oficiales; H1 2026 el 04-ago-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A70" s="58" t="str">
+        <x:v>DOM-CAL</x:v>
+      </x:c>
+      <x:c r="B70" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="C70" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D70" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E70" s="58" t="str">
+        <x:v>Resultados H1 2026</x:v>
+      </x:c>
+      <x:c r="F70" s="40" t="str">
+        <x:v>https://investors.dominos.co.uk/investors/overview/financial-calendar</x:v>
+      </x:c>
+      <x:c r="G70" s="58" t="str">
+        <x:v>Fecha confirmada; revisar el día siguiente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A71" s="58" t="str">
+        <x:v>BWY-MKT</x:v>
+      </x:c>
+      <x:c r="B71" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="C71" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D71" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E71" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F71" s="40" t="str">
+        <x:v>https://www.lse.co.uk/ShareFundamentals.html?shareprice=BWY</x:v>
+      </x:c>
+      <x:c r="G71" s="58" t="str">
+        <x:v>Snapshot de mercado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A72" s="58" t="str">
+        <x:v>BWY-TRD</x:v>
+      </x:c>
+      <x:c r="B72" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="C72" s="59" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="D72" s="58" t="str">
+        <x:v>Trading update</x:v>
+      </x:c>
+      <x:c r="E72" s="58" t="str">
+        <x:v>Guía FY26, orderbook, deuda neta, volúmenes y próximo update</x:v>
+      </x:c>
+      <x:c r="F72" s="40" t="str">
+        <x:v>https://www.lse.co.uk/rns/BWY/trading-update-l3zs9rgixwf4hq0.html</x:v>
+      </x:c>
+      <x:c r="G72" s="58" t="str">
+        <x:v>Comunicado oficial; próximo trading update 11-ago-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A73" s="58" t="str">
+        <x:v>BWY-CAL</x:v>
+      </x:c>
+      <x:c r="B73" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="C73" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D73" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E73" s="58" t="str">
+        <x:v>Trading update 11-ago-2026 y resultados FY26 13-oct-2026</x:v>
+      </x:c>
+      <x:c r="F73" s="40" t="str">
+        <x:v>https://www.bellwayplc.co.uk/investor-centre/financial-calendar</x:v>
+      </x:c>
+      <x:c r="G73" s="58" t="str">
+        <x:v>Fechas confirmadas por la compañía.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A74" s="58" t="str">
+        <x:v>BAB-MKT</x:v>
+      </x:c>
+      <x:c r="B74" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="C74" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D74" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E74" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F74" s="40" t="str">
+        <x:v>https://www.lse.co.uk/rns/BAB/</x:v>
+      </x:c>
+      <x:c r="G74" s="58" t="str">
+        <x:v>Snapshot RNS; PER calculado sobre EPS subyacente.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A75" s="58" t="str">
+        <x:v>BAB-FY26</x:v>
+      </x:c>
+      <x:c r="B75" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="C75" s="59" t="n">
+        <x:v>46195</x:v>
+      </x:c>
+      <x:c r="D75" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E75" s="58" t="str">
+        <x:v>FY26 ingresos, beneficio, EPS, FCF, backlog, deuda y recompra</x:v>
+      </x:c>
+      <x:c r="F75" s="40" t="str">
+        <x:v>https://www.babcockinternational.com/wp-content/uploads/2026/06/Babcock-FY26-results-presentation-22.06.26.pdf</x:v>
+      </x:c>
+      <x:c r="G75" s="58" t="str">
+        <x:v>Presentación oficial; Type 31 genera cargo extraordinario.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A76" s="58" t="str">
+        <x:v>BAB-CAL</x:v>
+      </x:c>
+      <x:c r="B76" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="C76" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D76" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E76" s="58" t="str">
+        <x:v>Resultados y reporting de inversores</x:v>
+      </x:c>
+      <x:c r="F76" s="40" t="str">
+        <x:v>https://www.babcockinternational.com/investors/results-and-reporting/</x:v>
+      </x:c>
+      <x:c r="G76" s="58" t="str">
+        <x:v>Confirmar fecha de H1 FY27.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A77" s="58" t="str">
+        <x:v>OXIG-MKT</x:v>
+      </x:c>
+      <x:c r="B77" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="C77" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D77" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E77" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F77" s="40" t="str">
+        <x:v>https://www.lse.co.uk/SharePrice.html?share=Oxford-Instruments&amp;shareprice=OXIG</x:v>
+      </x:c>
+      <x:c r="G77" s="58" t="str">
+        <x:v>Snapshot de mercado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A78" s="58" t="str">
+        <x:v>OXIG-FY26</x:v>
+      </x:c>
+      <x:c r="B78" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="C78" s="59" t="n">
+        <x:v>46182</x:v>
+      </x:c>
+      <x:c r="D78" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E78" s="58" t="str">
+        <x:v>FY26 ingresos, margen, EPS, caja, order intake y book-to-bill</x:v>
+      </x:c>
+      <x:c r="F78" s="40" t="str">
+        <x:v>https://www.oxinst.com/assets/uploads/Oxford_Instruments_plc_preliminary_FY26_results_9_June_2026.pdf</x:v>
+      </x:c>
+      <x:c r="G78" s="58" t="str">
+        <x:v>Resultados preliminares oficiales.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="92.4000015258789" hidden="0" customHeight="1">
+      <x:c r="A79" s="58" t="str">
+        <x:v>OXIG-CAL</x:v>
+      </x:c>
+      <x:c r="B79" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="C79" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D79" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E79" s="58" t="str">
+        <x:v>Resultados financieros y presentaciones</x:v>
+      </x:c>
+      <x:c r="F79" s="40" t="str">
+        <x:v>https://www.oxinst.com/investors/financial-reports-and-presentations</x:v>
+      </x:c>
+      <x:c r="G79" s="58" t="str">
+        <x:v>Usar noviembre como revisión tentativa de interinos.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="132" hidden="0" customHeight="1">
+      <x:c r="A80" s="58" t="str">
+        <x:v>FOUR-MKT</x:v>
+      </x:c>
+      <x:c r="B80" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="C80" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D80" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E80" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F80" s="40" t="str">
+        <x:v>https://www.lse.co.uk/SharePrice.html?share=4imprint-Grp&amp;shareprice=FOUR</x:v>
+      </x:c>
+      <x:c r="G80" s="58" t="str">
+        <x:v>Snapshot actualizado; la cuenta de resultados está en USD y la cotización/EPS LSE en GBX.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A81" s="58" t="str">
+        <x:v>FOUR-FY25</x:v>
+      </x:c>
+      <x:c r="B81" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="C81" s="59" t="n">
+        <x:v>46084</x:v>
+      </x:c>
+      <x:c r="D81" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E81" s="58" t="str">
+        <x:v>FY25 ventas, beneficio, EPS, pedidos, caja y dividendos</x:v>
+      </x:c>
+      <x:c r="F81" s="40" t="str">
+        <x:v>https://investors.4imprint.com/investors/latest-news/2026/final-results-for-the-period-ended-27-december-2025/</x:v>
+      </x:c>
+      <x:c r="G81" s="58" t="str">
+        <x:v>Resultados oficiales; primeros dos meses de 2026 débiles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A82" s="58" t="str">
+        <x:v>FOUR-CAL</x:v>
+      </x:c>
+      <x:c r="B82" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="C82" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D82" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E82" s="58" t="str">
+        <x:v>Resultados H1 2026</x:v>
+      </x:c>
+      <x:c r="F82" s="40" t="str">
+        <x:v>https://investors.4imprint.com/investors/financial-calendar/</x:v>
+      </x:c>
+      <x:c r="G82" s="58" t="str">
+        <x:v>Fecha confirmada: 05-ago-2026.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A83" s="58" t="str">
+        <x:v>JET2-MKT</x:v>
+      </x:c>
+      <x:c r="B83" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="C83" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D83" s="58" t="str">
+        <x:v>Mercado</x:v>
+      </x:c>
+      <x:c r="E83" s="58" t="str">
+        <x:v>Precio, capitalización, PER, EPS, dividendo y yield</x:v>
+      </x:c>
+      <x:c r="F83" s="40" t="str">
+        <x:v>https://www.lse.co.uk/SharePrice.html?share=Jet2-Plc&amp;shareprice=JET2</x:v>
+      </x:c>
+      <x:c r="G83" s="58" t="str">
+        <x:v>Snapshot actualizado; actualizar antes de decidir.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A84" s="58" t="str">
+        <x:v>JET2-FY26</x:v>
+      </x:c>
+      <x:c r="B84" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="C84" s="59" t="n">
+        <x:v>46233</x:v>
+      </x:c>
+      <x:c r="D84" s="58" t="str">
+        <x:v>Resultados</x:v>
+      </x:c>
+      <x:c r="E84" s="58" t="str">
+        <x:v>FY26 ingresos, beneficio, EPS, pasajeros, caja y capacidad 2026</x:v>
+      </x:c>
+      <x:c r="F84" s="40" t="str">
+        <x:v>https://www.jet2.com/news/2026/07/-/media/Jet2/Jet2plc/Jet2Plc_Redesign2025/Reports/2026/Preliminary-results-2026/Jet2-plc-Preliminary-Results-2026.pdf</x:v>
+      </x:c>
+      <x:c r="G84" s="58" t="str">
+        <x:v>Resultados preliminares oficiales.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A85" s="58" t="str">
+        <x:v>JET2-CAL</x:v>
+      </x:c>
+      <x:c r="B85" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="C85" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D85" s="58" t="str">
+        <x:v>Calendario</x:v>
+      </x:c>
+      <x:c r="E85" s="58" t="str">
+        <x:v>Resultados preliminares FY26 y noticias de inversores</x:v>
+      </x:c>
+      <x:c r="F85" s="40" t="str">
+        <x:v>https://www.jet2.com/news/2026/07/Jet2_PLC_Publishes_Preliminary_Results_2026</x:v>
+      </x:c>
+      <x:c r="G85" s="58" t="str">
+        <x:v>Usar noviembre como revisión post-temporada; confirmar calendario H1.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
@@ -7323,12 +13573,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d59cea838cb4f68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f1876c282e84626"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -7508,7 +13758,7 @@
       <x:c r="K5" s="58" t="str">
         <x:v>ATYM-FY25 / ATYM-Q2-26</x:v>
       </x:c>
-      <x:c r="L5" s="103" t="str">
+      <x:c r="L5" s="126" t="str">
         <x:f>IF(D5&lt;=DATE(2026,8,4),"REVISAR YA",IF(D5&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7547,7 +13797,7 @@
       <x:c r="K6" s="58" t="str">
         <x:v>RIO-H1-26</x:v>
       </x:c>
-      <x:c r="L6" s="103" t="str">
+      <x:c r="L6" s="126" t="str">
         <x:f>IF(D6&lt;=DATE(2026,8,4),"REVISAR YA",IF(D6&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7586,7 +13836,7 @@
       <x:c r="K7" s="58" t="str">
         <x:v>ETOR-Q1-26</x:v>
       </x:c>
-      <x:c r="L7" s="103" t="str">
+      <x:c r="L7" s="126" t="str">
         <x:f>IF(D7&lt;=DATE(2026,8,4),"REVISAR YA",IF(D7&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PRÓXIMA</x:v>
       </x:c>
@@ -7625,7 +13875,7 @@
       <x:c r="K8" s="58" t="str">
         <x:v>HBX-H1-26</x:v>
       </x:c>
-      <x:c r="L8" s="103" t="str">
+      <x:c r="L8" s="126" t="str">
         <x:f>IF(D8&lt;=DATE(2026,8,4),"REVISAR YA",IF(D8&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7664,7 +13914,7 @@
       <x:c r="K9" s="58" t="str">
         <x:v>FIG-Q2</x:v>
       </x:c>
-      <x:c r="L9" s="103" t="str">
+      <x:c r="L9" s="126" t="str">
         <x:f>IF(D9&lt;=DATE(2026,8,4),"REVISAR YA",IF(D9&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PRÓXIMA</x:v>
       </x:c>
@@ -7703,7 +13953,7 @@
       <x:c r="K10" s="58" t="str">
         <x:v>JD-FY26 / JD-BB</x:v>
       </x:c>
-      <x:c r="L10" s="103" t="str">
+      <x:c r="L10" s="126" t="str">
         <x:f>IF(D10&lt;=DATE(2026,8,4),"REVISAR YA",IF(D10&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PRÓXIMA</x:v>
       </x:c>
@@ -7742,7 +13992,7 @@
       <x:c r="K11" s="58" t="str">
         <x:v>PYPL-Q1-26</x:v>
       </x:c>
-      <x:c r="L11" s="103" t="str">
+      <x:c r="L11" s="126" t="str">
         <x:f>IF(D11&lt;=DATE(2026,8,4),"REVISAR YA",IF(D11&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7781,7 +14031,7 @@
       <x:c r="K12" s="58" t="str">
         <x:v>WISE-Q1-27 / WISE-CAL</x:v>
       </x:c>
-      <x:c r="L12" s="103" t="str">
+      <x:c r="L12" s="126" t="str">
         <x:f>IF(D12&lt;=DATE(2026,8,4),"REVISAR YA",IF(D12&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7820,7 +14070,7 @@
       <x:c r="K13" s="58" t="str">
         <x:v>AUTO-FY26 / AUTO-CAL</x:v>
       </x:c>
-      <x:c r="L13" s="103" t="str">
+      <x:c r="L13" s="126" t="str">
         <x:f>IF(D13&lt;=DATE(2026,8,4),"REVISAR YA",IF(D13&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7859,7 +14109,7 @@
       <x:c r="K14" s="58" t="str">
         <x:v>BME-Q1-27 / BME-CAL</x:v>
       </x:c>
-      <x:c r="L14" s="103" t="str">
+      <x:c r="L14" s="126" t="str">
         <x:f>IF(D14&lt;=DATE(2026,8,4),"REVISAR YA",IF(D14&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7898,7 +14148,7 @@
       <x:c r="K15" s="58" t="str">
         <x:v>KNOS-FY26 / KNOS-CAL</x:v>
       </x:c>
-      <x:c r="L15" s="103" t="str">
+      <x:c r="L15" s="126" t="str">
         <x:f>IF(D15&lt;=DATE(2026,8,4),"REVISAR YA",IF(D15&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PROGRAMADA</x:v>
       </x:c>
@@ -7937,569 +14187,576 @@
       <x:c r="K16" s="58" t="str">
         <x:v>PLUS-H1-26 / PLUS-CAL</x:v>
       </x:c>
-      <x:c r="L16" s="103" t="str">
+      <x:c r="L16" s="126" t="str">
         <x:f>IF(D16&lt;=DATE(2026,8,4),"REVISAR YA",IF(D16&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
         <x:v>PRÓXIMA</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="33"/>
-      <x:c r="B17" s="33"/>
-      <x:c r="C17" s="33"/>
-      <x:c r="D17" s="33"/>
-      <x:c r="E17" s="33"/>
-      <x:c r="F17" s="33"/>
-      <x:c r="G17" s="33"/>
-      <x:c r="H17" s="33"/>
-      <x:c r="I17" s="33"/>
-      <x:c r="J17" s="33"/>
-      <x:c r="K17" s="33"/>
-      <x:c r="L17" s="33"/>
-    </x:row>
-    <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="33"/>
-      <x:c r="B18" s="33"/>
-      <x:c r="C18" s="33"/>
-      <x:c r="D18" s="33"/>
-      <x:c r="E18" s="33"/>
-      <x:c r="F18" s="33"/>
-      <x:c r="G18" s="33"/>
-      <x:c r="H18" s="33"/>
-      <x:c r="I18" s="33"/>
-      <x:c r="J18" s="33"/>
-      <x:c r="K18" s="33"/>
-      <x:c r="L18" s="33"/>
-    </x:row>
-    <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="36" t="str">
+    <x:row r="17" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A17" s="58" t="str">
+        <x:v>Rightmove</x:v>
+      </x:c>
+      <x:c r="B17" s="58" t="str">
+        <x:v>RMV</x:v>
+      </x:c>
+      <x:c r="C17" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D17" s="59" t="n">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="E17" s="58" t="str">
+        <x:v>Calidad / marketplace</x:v>
+      </x:c>
+      <x:c r="F17" s="58" t="str">
+        <x:v>Ingresos, EPS, ARPA, miembros, áreas nuevas, LLM referrals, margen y caja</x:v>
+      </x:c>
+      <x:c r="G17" s="58" t="str">
+        <x:v>PER 16.90x; FY25 EPS 28.10p; consenso FY26 EPS 30.02p</x:v>
+      </x:c>
+      <x:c r="H17" s="58" t="str">
+        <x:v>Guía 2026 de ingresos +8–10% y crecimiento de comercial, hipotecas y alquileres</x:v>
+      </x:c>
+      <x:c r="I17" s="58" t="str">
+        <x:v>Menor crecimiento, membresía negativa, litigio/regulación o gasto que erosione el margen</x:v>
+      </x:c>
+      <x:c r="J17" s="58" t="str">
+        <x:v>Leer H1; actualizar el caso base y el precio de entrada de Analisis_Prioritario</x:v>
+      </x:c>
+      <x:c r="K17" s="58" t="str">
+        <x:v>RMV-FY25 / RMV-CONS</x:v>
+      </x:c>
+      <x:c r="L17" s="126" t="str">
+        <x:f>IF(D17&lt;=DATE(2026,8,4),"REVISAR YA",IF(D17&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PRÓXIMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A18" s="58" t="str">
+        <x:v>Games Workshop</x:v>
+      </x:c>
+      <x:c r="B18" s="58" t="str">
+        <x:v>GAW</x:v>
+      </x:c>
+      <x:c r="C18" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D18" s="59" t="n">
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="E18" s="58" t="str">
+        <x:v>Calidad / IP y nicho</x:v>
+      </x:c>
+      <x:c r="F18" s="58" t="str">
+        <x:v>Core revenue, licencias, margen, royalties, caja y dividendos</x:v>
+      </x:c>
+      <x:c r="G18" s="58" t="str">
+        <x:v>PER 33.52x; FY26 ingresos +6.8%; EPS 624p; sin deuda</x:v>
+      </x:c>
+      <x:c r="H18" s="58" t="str">
+        <x:v>Warhammer/IP sigue creciendo y la caja se transforma en dividendos sin deuda</x:v>
+      </x:c>
+      <x:c r="I18" s="58" t="str">
+        <x:v>Crecimiento core se normaliza, licencias caen o el PER exige más de lo que entrega</x:v>
+      </x:c>
+      <x:c r="J18" s="58" t="str">
+        <x:v>Revisar trading; recalcular precio razonable con crecimiento normalizado</x:v>
+      </x:c>
+      <x:c r="K18" s="58" t="str">
+        <x:v>GAW-FY26 / GAW-CAL</x:v>
+      </x:c>
+      <x:c r="L18" s="126" t="str">
+        <x:f>IF(D18&lt;=DATE(2026,8,4),"REVISAR YA",IF(D18&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PROGRAMADA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A19" s="58" t="str">
+        <x:v>Computacenter</x:v>
+      </x:c>
+      <x:c r="B19" s="58" t="str">
+        <x:v>CCC</x:v>
+      </x:c>
+      <x:c r="C19" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D19" s="59" t="n">
+        <x:v>46273</x:v>
+      </x:c>
+      <x:c r="E19" s="58" t="str">
+        <x:v>Crecimiento / servicios IT</x:v>
+      </x:c>
+      <x:c r="F19" s="58" t="str">
+        <x:v>Technology Sourcing, Managed Services, margen bruto, consenso y caja</x:v>
+      </x:c>
+      <x:c r="G19" s="58" t="str">
+        <x:v>PER 32.89x; FY25 ingresos +32%; net funds 606m</x:v>
+      </x:c>
+      <x:c r="H19" s="58" t="str">
+        <x:v>Q1 fuerte debe convertirse en beneficio y mantener el consenso FY26</x:v>
+      </x:c>
+      <x:c r="I19" s="58" t="str">
+        <x:v>Margen sigue cayendo, Managed Services no recupera o se paga demasiado por el crecimiento</x:v>
+      </x:c>
+      <x:c r="J19" s="58" t="str">
+        <x:v>Leer H1; comparar adjusted PBT contra consenso y actualizar valoración</x:v>
+      </x:c>
+      <x:c r="K19" s="58" t="str">
+        <x:v>CCC-Q1-26</x:v>
+      </x:c>
+      <x:c r="L19" s="126" t="str">
+        <x:f>IF(D19&lt;=DATE(2026,8,4),"REVISAR YA",IF(D19&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PROGRAMADA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A20" s="58" t="str">
+        <x:v>Howdens Joinery</x:v>
+      </x:c>
+      <x:c r="B20" s="58" t="str">
+        <x:v>HWDN</x:v>
+      </x:c>
+      <x:c r="C20" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D20" s="59" t="n">
+        <x:v>46331</x:v>
+      </x:c>
+      <x:c r="E20" s="58" t="str">
+        <x:v>Calidad / cíclica</x:v>
+      </x:c>
+      <x:c r="F20" s="58" t="str">
+        <x:v>Ventas comparables, margen bruto, aperturas, vivienda, DIY Kitchens y caja</x:v>
+      </x:c>
+      <x:c r="G20" s="58" t="str">
+        <x:v>PER 16.70x; H1 ventas +3.3%; EBIT subyacente +5.5%; caja 332.8m</x:v>
+      </x:c>
+      <x:c r="H20" s="58" t="str">
+        <x:v>Mantener margen y convertir recuperación de vivienda en crecimiento rentable</x:v>
+      </x:c>
+      <x:c r="I20" s="58" t="str">
+        <x:v>LFL negativo, margen cae, adquisición sin retorno o caja no cubre capex/inventario</x:v>
+      </x:c>
+      <x:c r="J20" s="58" t="str">
+        <x:v>Leer trading update; actualizar EPS normalizado y precio de entrada</x:v>
+      </x:c>
+      <x:c r="K20" s="58" t="str">
+        <x:v>HWDN-H1-26 / HWDN-CAL</x:v>
+      </x:c>
+      <x:c r="L20" s="126" t="str">
+        <x:f>IF(D20&lt;=DATE(2026,8,4),"REVISAR YA",IF(D20&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PROGRAMADA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A21" s="58" t="str">
+        <x:v>Domino's Pizza Group</x:v>
+      </x:c>
+      <x:c r="B21" s="58" t="str">
+        <x:v>DOM</x:v>
+      </x:c>
+      <x:c r="C21" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D21" s="59" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="E21" s="58" t="str">
+        <x:v>Madura / recuperable</x:v>
+      </x:c>
+      <x:c r="F21" s="58" t="str">
+        <x:v>System sales, EBITDA, PBT, franquiciados, promociones y caja</x:v>
+      </x:c>
+      <x:c r="G21" s="58" t="str">
+        <x:v>PER 13.35x; yield 5.5%; FY25 EBITDA -6.6%; primeras 9 semanas positivas</x:v>
+      </x:c>
+      <x:c r="H21" s="58" t="str">
+        <x:v>H1 debe confirmar momentum, disciplina promocional y estabilización de beneficios</x:v>
+      </x:c>
+      <x:c r="I21" s="58" t="str">
+        <x:v>EBITDA/PBT siguen cayendo, franquiciados pierden atractivo o activismo fuerza mala asignación</x:v>
+      </x:c>
+      <x:c r="J21" s="58" t="str">
+        <x:v>Leer resultados del 04-ago; actualizar tesis al día siguiente</x:v>
+      </x:c>
+      <x:c r="K21" s="58" t="str">
+        <x:v>DOM-FY25 / DOM-CAL</x:v>
+      </x:c>
+      <x:c r="L21" s="126" t="str">
+        <x:f>IF(D21&lt;=DATE(2026,8,4),"REVISAR YA",IF(D21&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PRÓXIMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A22" s="58" t="str">
+        <x:v>Bellway</x:v>
+      </x:c>
+      <x:c r="B22" s="58" t="str">
+        <x:v>BWY</x:v>
+      </x:c>
+      <x:c r="C22" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D22" s="59" t="n">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="E22" s="58" t="str">
+        <x:v>Existente / cíclica</x:v>
+      </x:c>
+      <x:c r="F22" s="58" t="str">
+        <x:v>Reservas, cancelaciones, orderbook, margen, deuda y demanda hipotecaria</x:v>
+      </x:c>
+      <x:c r="G22" s="58" t="str">
+        <x:v>PER 14.73x; beneficio FY26 guiado 320–330m; orderbook 1.57bn</x:v>
+      </x:c>
+      <x:c r="H22" s="58" t="str">
+        <x:v>Demanda y margen deben sostener guía sin aumentar deuda</x:v>
+      </x:c>
+      <x:c r="I22" s="58" t="str">
+        <x:v>Tipos/demanda empeoran, cancelaciones suben o el orderbook no convierte en entregas</x:v>
+      </x:c>
+      <x:c r="J22" s="58" t="str">
+        <x:v>Leer trading update; revisar si el descuento cíclico ofrece margen de seguridad</x:v>
+      </x:c>
+      <x:c r="K22" s="58" t="str">
+        <x:v>BWY-TRD / BWY-CAL</x:v>
+      </x:c>
+      <x:c r="L22" s="126" t="str">
+        <x:f>IF(D22&lt;=DATE(2026,8,4),"REVISAR YA",IF(D22&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PRÓXIMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="132" hidden="0" customHeight="1">
+      <x:c r="A23" s="58" t="str">
+        <x:v>Babcock International</x:v>
+      </x:c>
+      <x:c r="B23" s="58" t="str">
+        <x:v>BAB</x:v>
+      </x:c>
+      <x:c r="C23" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D23" s="59" t="n">
+        <x:v>46346</x:v>
+      </x:c>
+      <x:c r="E23" s="58" t="str">
+        <x:v>Defensa / turnaround</x:v>
+      </x:c>
+      <x:c r="F23" s="58" t="str">
+        <x:v>FCF, backlog, margen, Type 31, ejecución contractual y recompra</x:v>
+      </x:c>
+      <x:c r="G23" s="58" t="str">
+        <x:v>PER subyacente 18.53x; FCF 262m; backlog 9.8bn; caja neta 23m</x:v>
+      </x:c>
+      <x:c r="H23" s="58" t="str">
+        <x:v>El backlog debe convertirse en caja y el cargo Type 31 quedar aislado</x:v>
+      </x:c>
+      <x:c r="I23" s="58" t="str">
+        <x:v>Nuevo sobrecoste, FCF débil, deuda sube o se deteriora la calidad contractual</x:v>
+      </x:c>
+      <x:c r="J23" s="58" t="str">
+        <x:v>Confirmar fecha H1; comparar FCF y margen contra FY26</x:v>
+      </x:c>
+      <x:c r="K23" s="58" t="str">
+        <x:v>BAB-FY26 / BAB-CAL</x:v>
+      </x:c>
+      <x:c r="L23" s="126" t="str">
+        <x:f>IF(D23&lt;=DATE(2026,8,4),"REVISAR YA",IF(D23&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PROGRAMADA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="132" hidden="0" customHeight="1">
+      <x:c r="A24" s="58" t="str">
+        <x:v>Oxford Instruments</x:v>
+      </x:c>
+      <x:c r="B24" s="58" t="str">
+        <x:v>OXIG</x:v>
+      </x:c>
+      <x:c r="C24" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D24" s="59" t="n">
+        <x:v>46338</x:v>
+      </x:c>
+      <x:c r="E24" s="58" t="str">
+        <x:v>Nicho / tecnología</x:v>
+      </x:c>
+      <x:c r="F24" s="58" t="str">
+        <x:v>Order intake, book-to-bill, ventas, margen ajustado, semiconductores y caja</x:v>
+      </x:c>
+      <x:c r="G24" s="58" t="str">
+        <x:v>PER 33.81x; ingresos FY26 -4.6%; order intake +6.4%; caja 94m</x:v>
+      </x:c>
+      <x:c r="H24" s="58" t="str">
+        <x:v>Los pedidos deben convertirse en ingresos y recuperar margen sin nueva dilución</x:v>
+      </x:c>
+      <x:c r="I24" s="58" t="str">
+        <x:v>Book-to-bill cae, ingresos no recuperan o el múltiplo no deja margen</x:v>
+      </x:c>
+      <x:c r="J24" s="58" t="str">
+        <x:v>Leer interinos; actualizar conversión de pedidos y precio razonable</x:v>
+      </x:c>
+      <x:c r="K24" s="58" t="str">
+        <x:v>OXIG-FY26 / OXIG-CAL</x:v>
+      </x:c>
+      <x:c r="L24" s="126" t="str">
+        <x:f>IF(D24&lt;=DATE(2026,8,4),"REVISAR YA",IF(D24&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PROGRAMADA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="132" hidden="0" customHeight="1">
+      <x:c r="A25" s="58" t="str">
+        <x:v>4imprint Group</x:v>
+      </x:c>
+      <x:c r="B25" s="58" t="str">
+        <x:v>FOUR</x:v>
+      </x:c>
+      <x:c r="C25" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D25" s="59" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="E25" s="58" t="str">
+        <x:v>Madura / calidad con descuento</x:v>
+      </x:c>
+      <x:c r="F25" s="58" t="str">
+        <x:v>Pedidos nuevos/existentes, AOV, margen, aranceles, caja y guía</x:v>
+      </x:c>
+      <x:c r="G25" s="58" t="str">
+        <x:v>PER 14.62x; yield 4.2%; pedidos FY25 -3%; caja 132.8m USD</x:v>
+      </x:c>
+      <x:c r="H25" s="58" t="str">
+        <x:v>H1 debe distinguir bache temporal de pérdida estructural de clientes nuevos</x:v>
+      </x:c>
+      <x:c r="I25" s="58" t="str">
+        <x:v>Pedidos y margen siguen bajando, aranceles erosionan beneficio o caja se consume</x:v>
+      </x:c>
+      <x:c r="J25" s="58" t="str">
+        <x:v>Leer H1; recalcular beneficio normalizado y sensibilidad a pedidos</x:v>
+      </x:c>
+      <x:c r="K25" s="58" t="str">
+        <x:v>FOUR-FY25 / FOUR-CAL</x:v>
+      </x:c>
+      <x:c r="L25" s="126" t="str">
+        <x:f>IF(D25&lt;=DATE(2026,8,4),"REVISAR YA",IF(D25&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PRÓXIMA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="118.80000305175781" hidden="0" customHeight="1">
+      <x:c r="A26" s="58" t="str">
+        <x:v>Jet2</x:v>
+      </x:c>
+      <x:c r="B26" s="58" t="str">
+        <x:v>JET2</x:v>
+      </x:c>
+      <x:c r="C26" s="59" t="n">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="D26" s="59" t="n">
+        <x:v>46343</x:v>
+      </x:c>
+      <x:c r="E26" s="58" t="str">
+        <x:v>Cíclica / crecimiento</x:v>
+      </x:c>
+      <x:c r="F26" s="58" t="str">
+        <x:v>Ocupación, yield, combustible, capacidad, Gatwick, caja y recompra</x:v>
+      </x:c>
+      <x:c r="G26" s="58" t="str">
+        <x:v>PER 7.29x; caja neta 2,012.9m; pasajeros +5%; capacidad verano +7.7%</x:v>
+      </x:c>
+      <x:c r="H26" s="58" t="str">
+        <x:v>Crecimiento de capacidad y Gatwick deben mantener ROCE sin destruir caja</x:v>
+      </x:c>
+      <x:c r="I26" s="58" t="str">
+        <x:v>Combustible/geopolítica, demanda débil, margen cae o la caja se usa mal</x:v>
+      </x:c>
+      <x:c r="J26" s="58" t="str">
+        <x:v>Revisar tras verano; actualizar PER con resultados H1 y reservas</x:v>
+      </x:c>
+      <x:c r="K26" s="58" t="str">
+        <x:v>JET2-FY26 / JET2-CAL</x:v>
+      </x:c>
+      <x:c r="L26" s="126" t="str">
+        <x:f>IF(D26&lt;=DATE(2026,8,4),"REVISAR YA",IF(D26&lt;=DATE(2026,9,3),"PRÓXIMA","PROGRAMADA"))</x:f>
+        <x:v>PROGRAMADA</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="33"/>
+      <x:c r="B27" s="33"/>
+      <x:c r="C27" s="33"/>
+      <x:c r="D27" s="33"/>
+      <x:c r="E27" s="33"/>
+      <x:c r="F27" s="33"/>
+      <x:c r="G27" s="33"/>
+      <x:c r="H27" s="33"/>
+      <x:c r="I27" s="33"/>
+      <x:c r="J27" s="33"/>
+      <x:c r="K27" s="33"/>
+      <x:c r="L27" s="33"/>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="33"/>
+      <x:c r="B28" s="33"/>
+      <x:c r="C28" s="33"/>
+      <x:c r="D28" s="33"/>
+      <x:c r="E28" s="33"/>
+      <x:c r="F28" s="33"/>
+      <x:c r="G28" s="33"/>
+      <x:c r="H28" s="33"/>
+      <x:c r="I28" s="33"/>
+      <x:c r="J28" s="33"/>
+      <x:c r="K28" s="33"/>
+      <x:c r="L28" s="33"/>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="B19" s="36" t="str">
+      <x:c r="B29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="C19" s="36" t="str">
+      <x:c r="C29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="D19" s="36" t="str">
+      <x:c r="D29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="E19" s="36" t="str">
+      <x:c r="E29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="F19" s="36" t="str">
+      <x:c r="F29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="G19" s="36" t="str">
+      <x:c r="G29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="H19" s="36" t="str">
+      <x:c r="H29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="I19" s="36" t="str">
+      <x:c r="I29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="J19" s="36" t="str">
+      <x:c r="J29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="K19" s="36" t="str">
+      <x:c r="K29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
-      <x:c r="L19" s="36" t="str">
+      <x:c r="L29" s="36" t="str">
         <x:v>Protocolo de revisión</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="77" t="str">
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="105" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="str">
+      <x:c r="B30" s="33" t="str">
         <x:v>Cuando llegue la fecha, consulta primero el comunicado oficial y la presentación de resultados.</x:v>
       </x:c>
-      <x:c r="C20" s="33"/>
-      <x:c r="D20" s="33"/>
-      <x:c r="E20" s="33"/>
-      <x:c r="F20" s="33"/>
-      <x:c r="G20" s="33"/>
-      <x:c r="H20" s="33"/>
-      <x:c r="I20" s="33"/>
-      <x:c r="J20" s="33"/>
-      <x:c r="K20" s="33"/>
-      <x:c r="L20" s="33"/>
-    </x:row>
-    <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="77" t="str">
+      <x:c r="C30" s="33"/>
+      <x:c r="D30" s="33"/>
+      <x:c r="E30" s="33"/>
+      <x:c r="F30" s="33"/>
+      <x:c r="G30" s="33"/>
+      <x:c r="H30" s="33"/>
+      <x:c r="I30" s="33"/>
+      <x:c r="J30" s="33"/>
+      <x:c r="K30" s="33"/>
+      <x:c r="L30" s="33"/>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="105" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="str">
+      <x:c r="B31" s="33" t="str">
         <x:v>Copia una nueva fila en Historial: no sobreescribas el periodo anterior.</x:v>
       </x:c>
-      <x:c r="C21" s="33"/>
-      <x:c r="D21" s="33"/>
-      <x:c r="E21" s="33"/>
-      <x:c r="F21" s="33"/>
-      <x:c r="G21" s="33"/>
-      <x:c r="H21" s="33"/>
-      <x:c r="I21" s="33"/>
-      <x:c r="J21" s="33"/>
-      <x:c r="K21" s="33"/>
-      <x:c r="L21" s="33"/>
-    </x:row>
-    <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="77" t="str">
+      <x:c r="C31" s="33"/>
+      <x:c r="D31" s="33"/>
+      <x:c r="E31" s="33"/>
+      <x:c r="F31" s="33"/>
+      <x:c r="G31" s="33"/>
+      <x:c r="H31" s="33"/>
+      <x:c r="I31" s="33"/>
+      <x:c r="J31" s="33"/>
+      <x:c r="K31" s="33"/>
+      <x:c r="L31" s="33"/>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="105" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="str">
+      <x:c r="B32" s="33" t="str">
         <x:v>Actualiza precio, PER, EPS, ventas, crecimiento, FCF, deuda/caja y el dato operativo clave.</x:v>
       </x:c>
-      <x:c r="C22" s="33"/>
-      <x:c r="D22" s="33"/>
-      <x:c r="E22" s="33"/>
-      <x:c r="F22" s="33"/>
-      <x:c r="G22" s="33"/>
-      <x:c r="H22" s="33"/>
-      <x:c r="I22" s="33"/>
-      <x:c r="J22" s="33"/>
-      <x:c r="K22" s="33"/>
-      <x:c r="L22" s="33"/>
-    </x:row>
-    <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="77" t="str">
+      <x:c r="C32" s="33"/>
+      <x:c r="D32" s="33"/>
+      <x:c r="E32" s="33"/>
+      <x:c r="F32" s="33"/>
+      <x:c r="G32" s="33"/>
+      <x:c r="H32" s="33"/>
+      <x:c r="I32" s="33"/>
+      <x:c r="J32" s="33"/>
+      <x:c r="K32" s="33"/>
+      <x:c r="L32" s="33"/>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="105" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="str">
+      <x:c r="B33" s="33" t="str">
         <x:v>Compara el dato nuevo con Qué debe mejorar y Condición de invalidación.</x:v>
       </x:c>
-      <x:c r="C23" s="33"/>
-      <x:c r="D23" s="33"/>
-      <x:c r="E23" s="33"/>
-      <x:c r="F23" s="33"/>
-      <x:c r="G23" s="33"/>
-      <x:c r="H23" s="33"/>
-      <x:c r="I23" s="33"/>
-      <x:c r="J23" s="33"/>
-      <x:c r="K23" s="33"/>
-      <x:c r="L23" s="33"/>
-    </x:row>
-    <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="77" t="str">
+      <x:c r="C33" s="33"/>
+      <x:c r="D33" s="33"/>
+      <x:c r="E33" s="33"/>
+      <x:c r="F33" s="33"/>
+      <x:c r="G33" s="33"/>
+      <x:c r="H33" s="33"/>
+      <x:c r="I33" s="33"/>
+      <x:c r="J33" s="33"/>
+      <x:c r="K33" s="33"/>
+      <x:c r="L33" s="33"/>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="105" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="str">
+      <x:c r="B34" s="33" t="str">
         <x:v>Solo después cambia el veredicto/prioridad y deja constancia de la fuente y fecha.</x:v>
       </x:c>
-      <x:c r="C24" s="33"/>
-      <x:c r="D24" s="33"/>
-      <x:c r="E24" s="33"/>
-      <x:c r="F24" s="33"/>
-      <x:c r="G24" s="33"/>
-      <x:c r="H24" s="33"/>
-      <x:c r="I24" s="33"/>
-      <x:c r="J24" s="33"/>
-      <x:c r="K24" s="33"/>
-      <x:c r="L24" s="33"/>
+      <x:c r="C34" s="33"/>
+      <x:c r="D34" s="33"/>
+      <x:c r="E34" s="33"/>
+      <x:c r="F34" s="33"/>
+      <x:c r="G34" s="33"/>
+      <x:c r="H34" s="33"/>
+      <x:c r="I34" s="33"/>
+      <x:c r="J34" s="33"/>
+      <x:c r="K34" s="33"/>
+      <x:c r="L34" s="33"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
     <x:mergeCell ref="A2:L2"/>
-    <x:mergeCell ref="A19:L19"/>
-    <x:mergeCell ref="B20:L20"/>
-    <x:mergeCell ref="B21:L21"/>
-    <x:mergeCell ref="B22:L22"/>
-    <x:mergeCell ref="B23:L23"/>
-    <x:mergeCell ref="B24:L24"/>
+    <x:mergeCell ref="A29:L29"/>
+    <x:mergeCell ref="B30:L30"/>
+    <x:mergeCell ref="B31:L31"/>
+    <x:mergeCell ref="B32:L32"/>
+    <x:mergeCell ref="B33:L33"/>
+    <x:mergeCell ref="B34:L34"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:L16">
-    <x:cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="REVISAR YA"/>
-    <x:cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="PRÓXIMA"/>
-    <x:cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="PROGRAMADA"/>
+  <x:conditionalFormatting sqref="A5:L26">
+    <x:cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="REVISAR YA"/>
+    <x:cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="PRÓXIMA"/>
+    <x:cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="PROGRAMADA"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbb44965d0784938"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="66" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
-      <x:c r="A1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="B1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="C1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="D1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="E1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="F1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="G1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="H1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="I1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-      <x:c r="J1" s="34" t="str">
-        <x:v>Ideas cribadas pero no seleccionadas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="24" hidden="0" customHeight="1">
-      <x:c r="A2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="F2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="G2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="H2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="I2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-      <x:c r="J2" s="8" t="str">
-        <x:v>No significa que sean malas empresas: indica que hoy no superan el filtro de precio, riesgo o evidencia para nuestra lista inicial.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-      <x:c r="E3" s="33"/>
-      <x:c r="F3" s="33"/>
-      <x:c r="G3" s="33"/>
-      <x:c r="H3" s="33"/>
-      <x:c r="I3" s="33"/>
-      <x:c r="J3" s="33"/>
-    </x:row>
-    <x:row r="4" ht="36" hidden="0" customHeight="1">
-      <x:c r="A4" s="20" t="str">
-        <x:v>Empresa</x:v>
-      </x:c>
-      <x:c r="B4" s="20" t="str">
-        <x:v>Ticker</x:v>
-      </x:c>
-      <x:c r="C4" s="20" t="str">
-        <x:v>Fecha salida</x:v>
-      </x:c>
-      <x:c r="D4" s="20" t="str">
-        <x:v>Precio</x:v>
-      </x:c>
-      <x:c r="E4" s="20" t="str">
-        <x:v>PER</x:v>
-      </x:c>
-      <x:c r="F4" s="20" t="str">
-        <x:v>Rent. 1 año</x:v>
-      </x:c>
-      <x:c r="G4" s="20" t="str">
-        <x:v>Ventas FY25 (m)</x:v>
-      </x:c>
-      <x:c r="H4" s="20" t="str">
-        <x:v>Crec. ventas</x:v>
-      </x:c>
-      <x:c r="I4" s="20" t="str">
-        <x:v>FCF FY25 (m)</x:v>
-      </x:c>
-      <x:c r="J4" s="20" t="str">
-        <x:v>Motivo de no selección</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="250.8000030517578" hidden="0" customHeight="1">
-      <x:c r="A5" s="58" t="str">
-        <x:v>Applied Nutrition</x:v>
-      </x:c>
-      <x:c r="B5" s="58" t="str">
-        <x:v>APN</x:v>
-      </x:c>
-      <x:c r="C5" s="59" t="n">
-        <x:v>45589</x:v>
-      </x:c>
-      <x:c r="D5" s="60" t="n">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="E5" s="62" t="n">
-        <x:v>39.17</x:v>
-      </x:c>
-      <x:c r="F5" s="63" t="n">
-        <x:v>1.4962</x:v>
-      </x:c>
-      <x:c r="G5" s="58" t="n">
-        <x:v>107.1</x:v>
-      </x:c>
-      <x:c r="H5" s="63" t="n">
-        <x:v>0.242</x:v>
-      </x:c>
-      <x:c r="I5" s="58" t="n">
-        <x:v>16.5</x:v>
-      </x:c>
-      <x:c r="J5" s="58" t="str">
-        <x:v>Crecimiento y caja interesantes, pero el precio ya descuenta mucho: +150% en un año, PER ~39x y sin dividendo. Volver a mirar si el crecimiento acelera o corrige la cotización.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:J1"/>
-    <x:mergeCell ref="A2:J2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e595bf2401c4c44"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="19.200000762939453" hidden="0" customHeight="1">
-      <x:c r="A1" s="34" t="str">
-        <x:v>Checks del modelo</x:v>
-      </x:c>
-      <x:c r="B1" s="34" t="str">
-        <x:v>Checks del modelo</x:v>
-      </x:c>
-      <x:c r="C1" s="34" t="str">
-        <x:v>Checks del modelo</x:v>
-      </x:c>
-      <x:c r="D1" s="34" t="str">
-        <x:v>Checks del modelo</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="48" hidden="0" customHeight="1">
-      <x:c r="A2" s="8" t="str">
-        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
-        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
-      </x:c>
-      <x:c r="C2" s="8" t="str">
-        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
-        <x:v>Estas comprobaciones son visibles para detectar una watchlist incompleta. La búsqueda de errores de fórmula se ejecuta también al exportar.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="33"/>
-      <x:c r="B3" s="33"/>
-      <x:c r="C3" s="33"/>
-      <x:c r="D3" s="33"/>
-    </x:row>
-    <x:row r="4" ht="24" hidden="0" customHeight="1">
-      <x:c r="A4" s="20" t="str">
-        <x:v>Comprobación</x:v>
-      </x:c>
-      <x:c r="B4" s="20" t="str">
-        <x:v>Valor</x:v>
-      </x:c>
-      <x:c r="C4" s="20" t="str">
-        <x:v>Estado</x:v>
-      </x:c>
-      <x:c r="D4" s="20" t="str">
-        <x:v>Qué significa</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A5" s="35" t="str">
-        <x:v>Filas de watchlist</x:v>
-      </x:c>
-      <x:c r="B5" s="28" t="n">
-        <x:f>COUNTA('Watchlist'!A5:A16)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="103" t="str">
-        <x:f>IF(B5=12,"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D5" s="33" t="str">
-        <x:v>Debe haber 12 compañías seleccionadas.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A6" s="35" t="str">
-        <x:v>Totales de checklist</x:v>
-      </x:c>
-      <x:c r="B6" s="28" t="n">
-        <x:f>COUNT('Checklist_Lynch'!L5:L16)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="103" t="str">
-        <x:f>IF(B6=12,"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D6" s="33" t="str">
-        <x:v>Cada empresa debe tener un total calculado.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A7" s="35" t="str">
-        <x:v>Fuentes de mercado y resultados</x:v>
-      </x:c>
-      <x:c r="B7" s="28" t="n">
-        <x:f>COUNTIF('Watchlist'!Y5:Y16,"&lt;&gt;")+COUNTIF('Watchlist'!Z5:Z16,"&lt;&gt;")</x:f>
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="103" t="str">
-        <x:f>IF(B7=24,"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D7" s="33" t="str">
-        <x:v>Cada fila principal debe tener ambos IDs.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A8" s="35" t="str">
-        <x:v>Celdas de score vacías</x:v>
-      </x:c>
-      <x:c r="B8" s="28" t="n">
-        <x:f>COUNTBLANK('Watchlist'!AA5:AA16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="103" t="str">
-        <x:f>IF(B8=0,"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>No debe faltar el enlace al total de Checklist_Lynch.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="52.79999923706055" hidden="0" customHeight="1">
-      <x:c r="A9" s="35" t="str">
-        <x:v>Escala máxima</x:v>
-      </x:c>
-      <x:c r="B9" s="28" t="n">
-        <x:f>MAX('Checklist_Lynch'!L5:L16)</x:f>
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C9" s="103" t="str">
-        <x:f>IF(B9&lt;=16,"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>El máximo permitido por fila es 16.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A10" s="35" t="str">
-        <x:v>Modelo</x:v>
-      </x:c>
-      <x:c r="B10" s="28" t="n">
-        <x:f>COUNTIF(C5:C9,"REVISAR")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="103" t="str">
-        <x:f>IF(B10=0,"MODELO OK","HAY QUE REVISAR")</x:f>
-        <x:v>MODELO OK</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>Resumen de las comprobaciones anteriores.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="66" hidden="0" customHeight="1">
-      <x:c r="A11" s="35" t="str">
-        <x:v>Fecha de corte</x:v>
-      </x:c>
-      <x:c r="B11" s="107" t="n">
-        <x:v>46238</x:v>
-      </x:c>
-      <x:c r="C11" s="103" t="str">
-        <x:f>IF(B11=DATE(2026,8,4),"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="str">
-        <x:v>Actualiza esta fecha cuando refresques los datos.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="105.5999984741211" hidden="0" customHeight="1">
-      <x:c r="A12" s="35" t="str">
-        <x:v>Recordatorio</x:v>
-      </x:c>
-      <x:c r="B12" s="28" t="str">
-        <x:v>No es recomendación</x:v>
-      </x:c>
-      <x:c r="C12" s="103" t="str">
-        <x:v>INFO</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="str">
-        <x:v>Verifica siempre fuentes, precio, impuestos, divisa y tu perfil de riesgo.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="79.19999694824219" hidden="0" customHeight="1">
-      <x:c r="A13" s="35" t="str">
-        <x:v>Filas de seguimiento</x:v>
-      </x:c>
-      <x:c r="B13" s="28" t="n">
-        <x:f>COUNTA('Seguimiento'!A5:A16)</x:f>
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="103" t="str">
-        <x:f>IF(B13=12,"OK","REVISAR")</x:f>
-        <x:v>OK</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="str">
-        <x:v>Cada compañía debe tener una próxima revisión.</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="C5:C13">
-    <x:cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="OK"/>
-    <x:cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="REVISAR"/>
-  </x:conditionalFormatting>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red749d5370804c65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R505e10085b0043ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>